--- a/artfynd/A 24579-2025 artfynd.xlsx
+++ b/artfynd/A 24579-2025 artfynd.xlsx
@@ -772,10 +772,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>126379432</v>
+        <v>126379452</v>
       </c>
       <c r="B3" t="n">
-        <v>57656</v>
+        <v>91260</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -783,42 +783,34 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
-      <c r="K3" t="inlineStr"/>
-      <c r="L3" t="inlineStr"/>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
           <t>Bergmyran, Vb</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>718387</v>
+        <v>718194</v>
       </c>
       <c r="R3" t="n">
-        <v>7234490</v>
+        <v>7234461</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -851,11 +843,6 @@
       <c r="AA3" t="inlineStr">
         <is>
           <t>2025-07-02</t>
-        </is>
-      </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -882,7 +869,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>126379431</v>
+        <v>126379432</v>
       </c>
       <c r="B4" t="n">
         <v>57656</v>
@@ -911,16 +898,24 @@
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
+      <c r="K4" t="inlineStr"/>
+      <c r="L4" t="inlineStr"/>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
           <t>Bergmyran, Vb</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>718398</v>
+        <v>718387</v>
       </c>
       <c r="R4" t="n">
-        <v>7234399</v>
+        <v>7234490</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -984,7 +979,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>126379440</v>
+        <v>126379431</v>
       </c>
       <c r="B5" t="n">
         <v>57656</v>
@@ -1013,24 +1008,16 @@
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
-      <c r="K5" t="inlineStr"/>
-      <c r="L5" t="inlineStr"/>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
           <t>Bergmyran, Vb</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>718336</v>
+        <v>718398</v>
       </c>
       <c r="R5" t="n">
-        <v>7234249</v>
+        <v>7234399</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1057,17 +1044,17 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2025-07-01</t>
+          <t>2025-07-02</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2025-07-01</t>
+          <t>2025-07-02</t>
         </is>
       </c>
       <c r="AC5" t="inlineStr">
         <is>
-          <t>Färska ringhack</t>
+          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1094,10 +1081,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>126379452</v>
+        <v>126379440</v>
       </c>
       <c r="B6" t="n">
-        <v>91260</v>
+        <v>57656</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1105,34 +1092,42 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
+      <c r="K6" t="inlineStr"/>
+      <c r="L6" t="inlineStr"/>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
           <t>Bergmyran, Vb</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>718194</v>
+        <v>718336</v>
       </c>
       <c r="R6" t="n">
-        <v>7234461</v>
+        <v>7234249</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1159,12 +1154,17 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2025-07-02</t>
+          <t>2025-07-01</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2025-07-02</t>
+          <t>2025-07-01</t>
+        </is>
+      </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1699,48 +1699,45 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>126379451</v>
+        <v>126379463</v>
       </c>
       <c r="B12" t="n">
-        <v>79165</v>
+        <v>78977</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>230552</v>
+        <v>6425</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Gropig skägglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Usnea barbata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(L.) Weber ex F.H.Wigg.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
-      <c r="J12" t="inlineStr"/>
-      <c r="K12" t="inlineStr"/>
-      <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
           <t>Bergmyran, Vb</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>717977</v>
+        <v>718526</v>
       </c>
       <c r="R12" t="n">
-        <v>7234425</v>
+        <v>7234595</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1775,18 +1772,12 @@
           <t>2025-07-02</t>
         </is>
       </c>
-      <c r="AC12" t="inlineStr">
-        <is>
-          <t>Måste efterforska</t>
-        </is>
-      </c>
       <c r="AD12" t="b">
         <v>0</v>
       </c>
       <c r="AE12" t="b">
         <v>0</v>
       </c>
-      <c r="AF12" t="inlineStr"/>
       <c r="AG12" t="b">
         <v>0</v>
       </c>
@@ -2130,45 +2121,48 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>126379463</v>
+        <v>126379451</v>
       </c>
       <c r="B16" t="n">
-        <v>78977</v>
+        <v>79165</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6425</v>
+        <v>230552</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Gropig skägglav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Usnea barbata</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Weber ex F.H.Wigg.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
+      <c r="J16" t="inlineStr"/>
+      <c r="K16" t="inlineStr"/>
+      <c r="N16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
           <t>Bergmyran, Vb</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>718526</v>
+        <v>717977</v>
       </c>
       <c r="R16" t="n">
-        <v>7234595</v>
+        <v>7234425</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2203,12 +2197,18 @@
           <t>2025-07-02</t>
         </is>
       </c>
+      <c r="AC16" t="inlineStr">
+        <is>
+          <t>Måste efterforska</t>
+        </is>
+      </c>
       <c r="AD16" t="b">
         <v>0</v>
       </c>
       <c r="AE16" t="b">
         <v>0</v>
       </c>
+      <c r="AF16" t="inlineStr"/>
       <c r="AG16" t="b">
         <v>0</v>
       </c>
@@ -2824,32 +2824,32 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>126379446</v>
+        <v>126379468</v>
       </c>
       <c r="B23" t="n">
-        <v>80108</v>
+        <v>78977</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>6461</v>
+        <v>6425</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Norrlandslav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Nephroma arcticum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(L.) Torss.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -2859,10 +2859,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>718189</v>
+        <v>718577</v>
       </c>
       <c r="R23" t="n">
-        <v>7234350</v>
+        <v>7234539</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2921,7 +2921,7 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>126379468</v>
+        <v>126379481</v>
       </c>
       <c r="B24" t="n">
         <v>78977</v>
@@ -2956,10 +2956,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>718577</v>
+        <v>718217</v>
       </c>
       <c r="R24" t="n">
-        <v>7234539</v>
+        <v>7234406</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3018,32 +3018,32 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>126379481</v>
+        <v>126379424</v>
       </c>
       <c r="B25" t="n">
-        <v>78977</v>
+        <v>91207</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>6425</v>
+        <v>5447</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3053,10 +3053,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>718217</v>
+        <v>718450</v>
       </c>
       <c r="R25" t="n">
-        <v>7234406</v>
+        <v>7234710</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3115,10 +3115,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>126379447</v>
+        <v>126379478</v>
       </c>
       <c r="B26" t="n">
-        <v>80080</v>
+        <v>78977</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3126,21 +3126,21 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3150,10 +3150,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>718536</v>
+        <v>718319</v>
       </c>
       <c r="R26" t="n">
-        <v>7234545</v>
+        <v>7234335</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3186,6 +3186,11 @@
       <c r="AA26" t="inlineStr">
         <is>
           <t>2025-07-02</t>
+        </is>
+      </c>
+      <c r="AC26" t="inlineStr">
+        <is>
+          <t>Långa bålar</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3212,32 +3217,32 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>126379424</v>
+        <v>126379457</v>
       </c>
       <c r="B27" t="n">
-        <v>91207</v>
+        <v>78977</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>5447</v>
+        <v>6425</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3250,7 +3255,7 @@
         <v>718450</v>
       </c>
       <c r="R27" t="n">
-        <v>7234710</v>
+        <v>7234706</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3309,32 +3314,32 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>126379478</v>
+        <v>126379446</v>
       </c>
       <c r="B28" t="n">
-        <v>78977</v>
+        <v>80108</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>6425</v>
+        <v>6461</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Norrlandslav</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma arcticum</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Torss.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3344,10 +3349,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>718319</v>
+        <v>718189</v>
       </c>
       <c r="R28" t="n">
-        <v>7234335</v>
+        <v>7234350</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3380,11 +3385,6 @@
       <c r="AA28" t="inlineStr">
         <is>
           <t>2025-07-02</t>
-        </is>
-      </c>
-      <c r="AC28" t="inlineStr">
-        <is>
-          <t>Långa bålar</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3411,10 +3411,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>126379457</v>
+        <v>126379447</v>
       </c>
       <c r="B29" t="n">
-        <v>78977</v>
+        <v>80080</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3422,21 +3422,21 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3446,10 +3446,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>718450</v>
+        <v>718536</v>
       </c>
       <c r="R29" t="n">
-        <v>7234706</v>
+        <v>7234545</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3508,10 +3508,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>126379437</v>
+        <v>126379470</v>
       </c>
       <c r="B30" t="n">
-        <v>57656</v>
+        <v>78977</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3519,42 +3519,34 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
-      <c r="K30" t="inlineStr"/>
-      <c r="L30" t="inlineStr"/>
-      <c r="M30" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
           <t>Bergmyran, Vb</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>718001</v>
+        <v>718088</v>
       </c>
       <c r="R30" t="n">
-        <v>7234400</v>
+        <v>7234482</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3587,11 +3579,6 @@
       <c r="AA30" t="inlineStr">
         <is>
           <t>2025-07-02</t>
-        </is>
-      </c>
-      <c r="AC30" t="inlineStr">
-        <is>
-          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3618,32 +3605,32 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>126379470</v>
+        <v>126379491</v>
       </c>
       <c r="B31" t="n">
-        <v>78977</v>
+        <v>92532</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>6425</v>
+        <v>4364</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -3653,10 +3640,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>718088</v>
+        <v>718094</v>
       </c>
       <c r="R31" t="n">
-        <v>7234482</v>
+        <v>7234481</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3715,45 +3702,53 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>126379491</v>
+        <v>126379437</v>
       </c>
       <c r="B32" t="n">
-        <v>92532</v>
+        <v>57656</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>4364</v>
+        <v>100109</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
+      <c r="K32" t="inlineStr"/>
+      <c r="L32" t="inlineStr"/>
+      <c r="M32" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N32" t="inlineStr"/>
       <c r="P32" t="inlineStr">
         <is>
           <t>Bergmyran, Vb</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>718094</v>
+        <v>718001</v>
       </c>
       <c r="R32" t="n">
-        <v>7234481</v>
+        <v>7234400</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3786,6 +3781,11 @@
       <c r="AA32" t="inlineStr">
         <is>
           <t>2025-07-02</t>
+        </is>
+      </c>
+      <c r="AC32" t="inlineStr">
+        <is>
+          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4006,32 +4006,32 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>126379489</v>
+        <v>126379467</v>
       </c>
       <c r="B35" t="n">
-        <v>92532</v>
+        <v>78977</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>4364</v>
+        <v>6425</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -4041,10 +4041,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>718427</v>
+        <v>718635</v>
       </c>
       <c r="R35" t="n">
-        <v>7234679</v>
+        <v>7234620</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4103,32 +4103,32 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>126379467</v>
+        <v>126379489</v>
       </c>
       <c r="B36" t="n">
-        <v>78977</v>
+        <v>92532</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>6425</v>
+        <v>4364</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4138,10 +4138,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>718635</v>
+        <v>718427</v>
       </c>
       <c r="R36" t="n">
-        <v>7234620</v>
+        <v>7234679</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4399,32 +4399,32 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>126379475</v>
+        <v>126379490</v>
       </c>
       <c r="B39" t="n">
-        <v>78977</v>
+        <v>92532</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>6425</v>
+        <v>4364</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
@@ -4434,10 +4434,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>718346</v>
+        <v>718545</v>
       </c>
       <c r="R39" t="n">
-        <v>7234422</v>
+        <v>7234655</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4496,32 +4496,32 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>126379490</v>
+        <v>126379475</v>
       </c>
       <c r="B40" t="n">
-        <v>92532</v>
+        <v>78977</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>4364</v>
+        <v>6425</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
@@ -4531,10 +4531,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>718545</v>
+        <v>718346</v>
       </c>
       <c r="R40" t="n">
-        <v>7234655</v>
+        <v>7234422</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4889,10 +4889,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>126379436</v>
+        <v>126379485</v>
       </c>
       <c r="B44" t="n">
-        <v>57656</v>
+        <v>78977</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -4900,42 +4900,34 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
-      <c r="K44" t="inlineStr"/>
-      <c r="L44" t="inlineStr"/>
-      <c r="M44" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N44" t="inlineStr"/>
       <c r="P44" t="inlineStr">
         <is>
           <t>Bergmyran, Vb</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>718009</v>
+        <v>718173</v>
       </c>
       <c r="R44" t="n">
-        <v>7234441</v>
+        <v>7234351</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -4972,7 +4964,7 @@
       </c>
       <c r="AC44" t="inlineStr">
         <is>
-          <t>Äldre ringhack</t>
+          <t>Fertil</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5109,10 +5101,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>126379485</v>
+        <v>126379436</v>
       </c>
       <c r="B46" t="n">
-        <v>78977</v>
+        <v>57656</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5120,34 +5112,42 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
+      <c r="K46" t="inlineStr"/>
+      <c r="L46" t="inlineStr"/>
+      <c r="M46" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N46" t="inlineStr"/>
       <c r="P46" t="inlineStr">
         <is>
           <t>Bergmyran, Vb</t>
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>718173</v>
+        <v>718009</v>
       </c>
       <c r="R46" t="n">
-        <v>7234351</v>
+        <v>7234441</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5184,7 +5184,7 @@
       </c>
       <c r="AC46" t="inlineStr">
         <is>
-          <t>Fertil</t>
+          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -5816,10 +5816,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>126379435</v>
+        <v>126379474</v>
       </c>
       <c r="B53" t="n">
-        <v>57656</v>
+        <v>78977</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -5827,42 +5827,34 @@
         </is>
       </c>
       <c r="E53" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
-      <c r="K53" t="inlineStr"/>
-      <c r="L53" t="inlineStr"/>
-      <c r="M53" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N53" t="inlineStr"/>
       <c r="P53" t="inlineStr">
         <is>
           <t>Bergmyran, Vb</t>
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>718107</v>
+        <v>718328</v>
       </c>
       <c r="R53" t="n">
-        <v>7234326</v>
+        <v>7234423</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -5895,11 +5887,6 @@
       <c r="AA53" t="inlineStr">
         <is>
           <t>2025-07-02</t>
-        </is>
-      </c>
-      <c r="AC53" t="inlineStr">
-        <is>
-          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD53" t="b">
@@ -5926,7 +5913,7 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>126379474</v>
+        <v>126379455</v>
       </c>
       <c r="B54" t="n">
         <v>78977</v>
@@ -5961,10 +5948,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>718328</v>
+        <v>718524</v>
       </c>
       <c r="R54" t="n">
-        <v>7234423</v>
+        <v>7234543</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -6023,7 +6010,7 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>126379455</v>
+        <v>126379456</v>
       </c>
       <c r="B55" t="n">
         <v>78977</v>
@@ -6058,10 +6045,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>718524</v>
+        <v>718493</v>
       </c>
       <c r="R55" t="n">
-        <v>7234543</v>
+        <v>7234644</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -6120,10 +6107,10 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>126379456</v>
+        <v>126379435</v>
       </c>
       <c r="B56" t="n">
-        <v>78977</v>
+        <v>57656</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6131,34 +6118,42 @@
         </is>
       </c>
       <c r="E56" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
+      <c r="K56" t="inlineStr"/>
+      <c r="L56" t="inlineStr"/>
+      <c r="M56" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N56" t="inlineStr"/>
       <c r="P56" t="inlineStr">
         <is>
           <t>Bergmyran, Vb</t>
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>718493</v>
+        <v>718107</v>
       </c>
       <c r="R56" t="n">
-        <v>7234644</v>
+        <v>7234326</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -6191,6 +6186,11 @@
       <c r="AA56" t="inlineStr">
         <is>
           <t>2025-07-02</t>
+        </is>
+      </c>
+      <c r="AC56" t="inlineStr">
+        <is>
+          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD56" t="b">
@@ -6702,10 +6702,10 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>126379442</v>
+        <v>126379438</v>
       </c>
       <c r="B62" t="n">
-        <v>57816</v>
+        <v>57656</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -6713,21 +6713,21 @@
         </is>
       </c>
       <c r="E62" t="n">
-        <v>103021</v>
+        <v>100109</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
@@ -6735,7 +6735,7 @@
       <c r="L62" t="inlineStr"/>
       <c r="M62" t="inlineStr">
         <is>
-          <t>upprörd, varnande</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="N62" t="inlineStr"/>
@@ -6745,10 +6745,10 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>718338</v>
+        <v>718061</v>
       </c>
       <c r="R62" t="n">
-        <v>7234424</v>
+        <v>7234332</v>
       </c>
       <c r="S62" t="n">
         <v>10</v>
@@ -6775,12 +6775,17 @@
       </c>
       <c r="Y62" t="inlineStr">
         <is>
-          <t>2025-07-02</t>
+          <t>2025-07-01</t>
         </is>
       </c>
       <c r="AA62" t="inlineStr">
         <is>
-          <t>2025-07-02</t>
+          <t>2025-07-01</t>
+        </is>
+      </c>
+      <c r="AC62" t="inlineStr">
+        <is>
+          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD62" t="b">
@@ -7001,10 +7006,10 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>126379438</v>
+        <v>126379462</v>
       </c>
       <c r="B65" t="n">
-        <v>57656</v>
+        <v>78977</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -7012,42 +7017,34 @@
         </is>
       </c>
       <c r="E65" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
-      <c r="K65" t="inlineStr"/>
-      <c r="L65" t="inlineStr"/>
-      <c r="M65" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N65" t="inlineStr"/>
       <c r="P65" t="inlineStr">
         <is>
           <t>Bergmyran, Vb</t>
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>718061</v>
+        <v>718535</v>
       </c>
       <c r="R65" t="n">
-        <v>7234332</v>
+        <v>7234587</v>
       </c>
       <c r="S65" t="n">
         <v>10</v>
@@ -7074,17 +7071,17 @@
       </c>
       <c r="Y65" t="inlineStr">
         <is>
-          <t>2025-07-01</t>
+          <t>2025-07-02</t>
         </is>
       </c>
       <c r="AA65" t="inlineStr">
         <is>
-          <t>2025-07-01</t>
+          <t>2025-07-02</t>
         </is>
       </c>
       <c r="AC65" t="inlineStr">
         <is>
-          <t>Äldre ringhack</t>
+          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD65" t="b">
@@ -7111,10 +7108,10 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>126379462</v>
+        <v>126379442</v>
       </c>
       <c r="B66" t="n">
-        <v>78977</v>
+        <v>57816</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -7122,34 +7119,42 @@
         </is>
       </c>
       <c r="E66" t="n">
-        <v>6425</v>
+        <v>103021</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I66" t="inlineStr"/>
+      <c r="K66" t="inlineStr"/>
+      <c r="L66" t="inlineStr"/>
+      <c r="M66" t="inlineStr">
+        <is>
+          <t>upprörd, varnande</t>
+        </is>
+      </c>
+      <c r="N66" t="inlineStr"/>
       <c r="P66" t="inlineStr">
         <is>
           <t>Bergmyran, Vb</t>
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>718535</v>
+        <v>718338</v>
       </c>
       <c r="R66" t="n">
-        <v>7234587</v>
+        <v>7234424</v>
       </c>
       <c r="S66" t="n">
         <v>10</v>
@@ -7182,11 +7187,6 @@
       <c r="AA66" t="inlineStr">
         <is>
           <t>2025-07-02</t>
-        </is>
-      </c>
-      <c r="AC66" t="inlineStr">
-        <is>
-          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD66" t="b">

--- a/artfynd/A 24579-2025 artfynd.xlsx
+++ b/artfynd/A 24579-2025 artfynd.xlsx
@@ -1301,10 +1301,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>126379471</v>
+        <v>126379488</v>
       </c>
       <c r="B8" t="n">
-        <v>78977</v>
+        <v>78644</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1312,21 +1312,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6425</v>
+        <v>353</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1336,10 +1336,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>718115</v>
+        <v>718044</v>
       </c>
       <c r="R8" t="n">
-        <v>7234496</v>
+        <v>7234385</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1372,11 +1372,6 @@
       <c r="AA8" t="inlineStr">
         <is>
           <t>2025-07-02</t>
-        </is>
-      </c>
-      <c r="AC8" t="inlineStr">
-        <is>
-          <t>Långa bålar</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1403,32 +1398,32 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>126379425</v>
+        <v>126379471</v>
       </c>
       <c r="B9" t="n">
-        <v>91207</v>
+        <v>78977</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>5447</v>
+        <v>6425</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1438,10 +1433,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>717969</v>
+        <v>718115</v>
       </c>
       <c r="R9" t="n">
-        <v>7234409</v>
+        <v>7234496</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1474,6 +1469,11 @@
       <c r="AA9" t="inlineStr">
         <is>
           <t>2025-07-02</t>
+        </is>
+      </c>
+      <c r="AC9" t="inlineStr">
+        <is>
+          <t>Långa bålar</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1500,32 +1500,32 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>126379484</v>
+        <v>126379425</v>
       </c>
       <c r="B10" t="n">
-        <v>78977</v>
+        <v>91207</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6425</v>
+        <v>5447</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1535,10 +1535,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>718212</v>
+        <v>717969</v>
       </c>
       <c r="R10" t="n">
-        <v>7234353</v>
+        <v>7234409</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1571,11 +1571,6 @@
       <c r="AA10" t="inlineStr">
         <is>
           <t>2025-07-02</t>
-        </is>
-      </c>
-      <c r="AC10" t="inlineStr">
-        <is>
-          <t>Med apothecier</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1602,10 +1597,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>126379488</v>
+        <v>126379484</v>
       </c>
       <c r="B11" t="n">
-        <v>78644</v>
+        <v>78977</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1613,21 +1608,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>353</v>
+        <v>6425</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1637,10 +1632,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>718044</v>
+        <v>718212</v>
       </c>
       <c r="R11" t="n">
-        <v>7234385</v>
+        <v>7234353</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1673,6 +1668,11 @@
       <c r="AA11" t="inlineStr">
         <is>
           <t>2025-07-02</t>
+        </is>
+      </c>
+      <c r="AC11" t="inlineStr">
+        <is>
+          <t>Med apothecier</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -4889,45 +4889,53 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>126379485</v>
+        <v>126379441</v>
       </c>
       <c r="B44" t="n">
-        <v>78977</v>
+        <v>56848</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>6425</v>
+        <v>100138</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
+      <c r="K44" t="inlineStr"/>
+      <c r="L44" t="inlineStr"/>
+      <c r="M44" t="inlineStr">
+        <is>
+          <t>äldre spillning</t>
+        </is>
+      </c>
+      <c r="N44" t="inlineStr"/>
       <c r="P44" t="inlineStr">
         <is>
           <t>Bergmyran, Vb</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>718173</v>
+        <v>718148</v>
       </c>
       <c r="R44" t="n">
-        <v>7234351</v>
+        <v>7234311</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -4964,7 +4972,7 @@
       </c>
       <c r="AC44" t="inlineStr">
         <is>
-          <t>Fertil</t>
+          <t>Spillning</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -4991,32 +4999,32 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>126379441</v>
+        <v>126379436</v>
       </c>
       <c r="B45" t="n">
-        <v>56848</v>
+        <v>57656</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>100138</v>
+        <v>100109</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
@@ -5024,7 +5032,7 @@
       <c r="L45" t="inlineStr"/>
       <c r="M45" t="inlineStr">
         <is>
-          <t>äldre spillning</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="N45" t="inlineStr"/>
@@ -5034,10 +5042,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>718148</v>
+        <v>718009</v>
       </c>
       <c r="R45" t="n">
-        <v>7234311</v>
+        <v>7234441</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5074,7 +5082,7 @@
       </c>
       <c r="AC45" t="inlineStr">
         <is>
-          <t>Spillning</t>
+          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5101,10 +5109,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>126379436</v>
+        <v>126379485</v>
       </c>
       <c r="B46" t="n">
-        <v>57656</v>
+        <v>78977</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5112,42 +5120,34 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
-      <c r="K46" t="inlineStr"/>
-      <c r="L46" t="inlineStr"/>
-      <c r="M46" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N46" t="inlineStr"/>
       <c r="P46" t="inlineStr">
         <is>
           <t>Bergmyran, Vb</t>
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>718009</v>
+        <v>718173</v>
       </c>
       <c r="R46" t="n">
-        <v>7234441</v>
+        <v>7234351</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5184,7 +5184,7 @@
       </c>
       <c r="AC46" t="inlineStr">
         <is>
-          <t>Äldre ringhack</t>
+          <t>Fertil</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -5211,10 +5211,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>126379465</v>
+        <v>126379423</v>
       </c>
       <c r="B47" t="n">
-        <v>78977</v>
+        <v>79009</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5222,21 +5222,21 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>6425</v>
+        <v>185</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
@@ -5246,10 +5246,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>718515</v>
+        <v>718221</v>
       </c>
       <c r="R47" t="n">
-        <v>7234673</v>
+        <v>7234403</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5282,11 +5282,6 @@
       <c r="AA47" t="inlineStr">
         <is>
           <t>2025-07-02</t>
-        </is>
-      </c>
-      <c r="AC47" t="inlineStr">
-        <is>
-          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -5313,10 +5308,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>126379423</v>
+        <v>126379465</v>
       </c>
       <c r="B48" t="n">
-        <v>79009</v>
+        <v>78977</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5324,21 +5319,21 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>185</v>
+        <v>6425</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
@@ -5348,10 +5343,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>718221</v>
+        <v>718515</v>
       </c>
       <c r="R48" t="n">
-        <v>7234403</v>
+        <v>7234673</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5384,6 +5379,11 @@
       <c r="AA48" t="inlineStr">
         <is>
           <t>2025-07-02</t>
+        </is>
+      </c>
+      <c r="AC48" t="inlineStr">
+        <is>
+          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -5609,53 +5609,45 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>126379439</v>
+        <v>126379444</v>
       </c>
       <c r="B51" t="n">
-        <v>57656</v>
+        <v>98373</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>100109</v>
+        <v>221952</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
-      <c r="K51" t="inlineStr"/>
-      <c r="L51" t="inlineStr"/>
-      <c r="M51" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N51" t="inlineStr"/>
       <c r="P51" t="inlineStr">
         <is>
           <t>Bergmyran, Vb</t>
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>718038</v>
+        <v>717964</v>
       </c>
       <c r="R51" t="n">
-        <v>7234341</v>
+        <v>7234394</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -5682,17 +5674,12 @@
       </c>
       <c r="Y51" t="inlineStr">
         <is>
-          <t>2025-07-01</t>
+          <t>2025-07-02</t>
         </is>
       </c>
       <c r="AA51" t="inlineStr">
         <is>
-          <t>2025-07-01</t>
-        </is>
-      </c>
-      <c r="AC51" t="inlineStr">
-        <is>
-          <t>Äldre ringhack</t>
+          <t>2025-07-02</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -5719,45 +5706,53 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>126379444</v>
+        <v>126379439</v>
       </c>
       <c r="B52" t="n">
-        <v>98373</v>
+        <v>57656</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E52" t="n">
-        <v>221952</v>
+        <v>100109</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
+      <c r="K52" t="inlineStr"/>
+      <c r="L52" t="inlineStr"/>
+      <c r="M52" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N52" t="inlineStr"/>
       <c r="P52" t="inlineStr">
         <is>
           <t>Bergmyran, Vb</t>
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>717964</v>
+        <v>718038</v>
       </c>
       <c r="R52" t="n">
-        <v>7234394</v>
+        <v>7234341</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -5784,12 +5779,17 @@
       </c>
       <c r="Y52" t="inlineStr">
         <is>
-          <t>2025-07-02</t>
+          <t>2025-07-01</t>
         </is>
       </c>
       <c r="AA52" t="inlineStr">
         <is>
-          <t>2025-07-02</t>
+          <t>2025-07-01</t>
+        </is>
+      </c>
+      <c r="AC52" t="inlineStr">
+        <is>
+          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD52" t="b">
@@ -6702,10 +6702,10 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>126379438</v>
+        <v>126379459</v>
       </c>
       <c r="B62" t="n">
-        <v>57656</v>
+        <v>78977</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -6713,42 +6713,34 @@
         </is>
       </c>
       <c r="E62" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
-      <c r="K62" t="inlineStr"/>
-      <c r="L62" t="inlineStr"/>
-      <c r="M62" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N62" t="inlineStr"/>
       <c r="P62" t="inlineStr">
         <is>
           <t>Bergmyran, Vb</t>
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>718061</v>
+        <v>718274</v>
       </c>
       <c r="R62" t="n">
-        <v>7234332</v>
+        <v>7234439</v>
       </c>
       <c r="S62" t="n">
         <v>10</v>
@@ -6775,17 +6767,12 @@
       </c>
       <c r="Y62" t="inlineStr">
         <is>
-          <t>2025-07-01</t>
+          <t>2025-07-02</t>
         </is>
       </c>
       <c r="AA62" t="inlineStr">
         <is>
-          <t>2025-07-01</t>
-        </is>
-      </c>
-      <c r="AC62" t="inlineStr">
-        <is>
-          <t>Äldre ringhack</t>
+          <t>2025-07-02</t>
         </is>
       </c>
       <c r="AD62" t="b">
@@ -6812,7 +6799,7 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>126379459</v>
+        <v>126379464</v>
       </c>
       <c r="B63" t="n">
         <v>78977</v>
@@ -6847,10 +6834,10 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>718274</v>
+        <v>718427</v>
       </c>
       <c r="R63" t="n">
-        <v>7234439</v>
+        <v>7234679</v>
       </c>
       <c r="S63" t="n">
         <v>10</v>
@@ -6909,7 +6896,7 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>126379464</v>
+        <v>126379462</v>
       </c>
       <c r="B64" t="n">
         <v>78977</v>
@@ -6944,10 +6931,10 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>718427</v>
+        <v>718535</v>
       </c>
       <c r="R64" t="n">
-        <v>7234679</v>
+        <v>7234587</v>
       </c>
       <c r="S64" t="n">
         <v>10</v>
@@ -6980,6 +6967,11 @@
       <c r="AA64" t="inlineStr">
         <is>
           <t>2025-07-02</t>
+        </is>
+      </c>
+      <c r="AC64" t="inlineStr">
+        <is>
+          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD64" t="b">
@@ -7006,10 +6998,10 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>126379462</v>
+        <v>126379438</v>
       </c>
       <c r="B65" t="n">
-        <v>78977</v>
+        <v>57656</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -7017,34 +7009,42 @@
         </is>
       </c>
       <c r="E65" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
+      <c r="K65" t="inlineStr"/>
+      <c r="L65" t="inlineStr"/>
+      <c r="M65" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N65" t="inlineStr"/>
       <c r="P65" t="inlineStr">
         <is>
           <t>Bergmyran, Vb</t>
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>718535</v>
+        <v>718061</v>
       </c>
       <c r="R65" t="n">
-        <v>7234587</v>
+        <v>7234332</v>
       </c>
       <c r="S65" t="n">
         <v>10</v>
@@ -7071,17 +7071,17 @@
       </c>
       <c r="Y65" t="inlineStr">
         <is>
-          <t>2025-07-02</t>
+          <t>2025-07-01</t>
         </is>
       </c>
       <c r="AA65" t="inlineStr">
         <is>
-          <t>2025-07-02</t>
+          <t>2025-07-01</t>
         </is>
       </c>
       <c r="AC65" t="inlineStr">
         <is>
-          <t>Rikligt</t>
+          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD65" t="b">

--- a/artfynd/A 24579-2025 artfynd.xlsx
+++ b/artfynd/A 24579-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>126379461</v>
       </c>
       <c r="B2" t="n">
-        <v>78977</v>
+        <v>78980</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -775,7 +775,7 @@
         <v>126379452</v>
       </c>
       <c r="B3" t="n">
-        <v>91260</v>
+        <v>91263</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -872,7 +872,7 @@
         <v>126379432</v>
       </c>
       <c r="B4" t="n">
-        <v>57656</v>
+        <v>57657</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -982,7 +982,7 @@
         <v>126379431</v>
       </c>
       <c r="B5" t="n">
-        <v>57656</v>
+        <v>57657</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1084,7 +1084,7 @@
         <v>126379440</v>
       </c>
       <c r="B6" t="n">
-        <v>57656</v>
+        <v>57657</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1194,7 +1194,7 @@
         <v>126379433</v>
       </c>
       <c r="B7" t="n">
-        <v>57656</v>
+        <v>57657</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1301,10 +1301,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>126379488</v>
+        <v>126379471</v>
       </c>
       <c r="B8" t="n">
-        <v>78644</v>
+        <v>78980</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1312,21 +1312,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>353</v>
+        <v>6425</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1336,10 +1336,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>718044</v>
+        <v>718115</v>
       </c>
       <c r="R8" t="n">
-        <v>7234385</v>
+        <v>7234496</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1372,6 +1372,11 @@
       <c r="AA8" t="inlineStr">
         <is>
           <t>2025-07-02</t>
+        </is>
+      </c>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>Långa bålar</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1398,32 +1403,32 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>126379471</v>
+        <v>126379425</v>
       </c>
       <c r="B9" t="n">
-        <v>78977</v>
+        <v>91210</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6425</v>
+        <v>5447</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1433,10 +1438,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>718115</v>
+        <v>717969</v>
       </c>
       <c r="R9" t="n">
-        <v>7234496</v>
+        <v>7234409</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1469,11 +1474,6 @@
       <c r="AA9" t="inlineStr">
         <is>
           <t>2025-07-02</t>
-        </is>
-      </c>
-      <c r="AC9" t="inlineStr">
-        <is>
-          <t>Långa bålar</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1500,32 +1500,32 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>126379425</v>
+        <v>126379484</v>
       </c>
       <c r="B10" t="n">
-        <v>91207</v>
+        <v>78980</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>5447</v>
+        <v>6425</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1535,10 +1535,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>717969</v>
+        <v>718212</v>
       </c>
       <c r="R10" t="n">
-        <v>7234409</v>
+        <v>7234353</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1571,6 +1571,11 @@
       <c r="AA10" t="inlineStr">
         <is>
           <t>2025-07-02</t>
+        </is>
+      </c>
+      <c r="AC10" t="inlineStr">
+        <is>
+          <t>Med apothecier</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1597,10 +1602,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>126379484</v>
+        <v>126379488</v>
       </c>
       <c r="B11" t="n">
-        <v>78977</v>
+        <v>78647</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1608,21 +1613,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6425</v>
+        <v>353</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1632,10 +1637,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>718212</v>
+        <v>718044</v>
       </c>
       <c r="R11" t="n">
-        <v>7234353</v>
+        <v>7234385</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1668,11 +1673,6 @@
       <c r="AA11" t="inlineStr">
         <is>
           <t>2025-07-02</t>
-        </is>
-      </c>
-      <c r="AC11" t="inlineStr">
-        <is>
-          <t>Med apothecier</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1699,10 +1699,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>126379463</v>
+        <v>126379430</v>
       </c>
       <c r="B12" t="n">
-        <v>78977</v>
+        <v>57657</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1710,34 +1710,42 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
+      <c r="K12" t="inlineStr"/>
+      <c r="L12" t="inlineStr"/>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
           <t>Bergmyran, Vb</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>718526</v>
+        <v>718154</v>
       </c>
       <c r="R12" t="n">
-        <v>7234595</v>
+        <v>7234509</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1770,6 +1778,11 @@
       <c r="AA12" t="inlineStr">
         <is>
           <t>2025-07-02</t>
+        </is>
+      </c>
+      <c r="AC12" t="inlineStr">
+        <is>
+          <t>Färskt ringhack</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1796,10 +1809,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>126379430</v>
+        <v>126379443</v>
       </c>
       <c r="B13" t="n">
-        <v>57656</v>
+        <v>57817</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1807,21 +1820,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>100109</v>
+        <v>103021</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1829,7 +1842,7 @@
       <c r="L13" t="inlineStr"/>
       <c r="M13" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>upprörd, varnande</t>
         </is>
       </c>
       <c r="N13" t="inlineStr"/>
@@ -1839,10 +1852,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>718154</v>
+        <v>718294</v>
       </c>
       <c r="R13" t="n">
-        <v>7234509</v>
+        <v>7234414</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1875,11 +1888,6 @@
       <c r="AA13" t="inlineStr">
         <is>
           <t>2025-07-02</t>
-        </is>
-      </c>
-      <c r="AC13" t="inlineStr">
-        <is>
-          <t>Färskt ringhack</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1906,10 +1914,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>126379434</v>
+        <v>126379463</v>
       </c>
       <c r="B14" t="n">
-        <v>57656</v>
+        <v>78980</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1917,42 +1925,34 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
-      <c r="K14" t="inlineStr"/>
-      <c r="L14" t="inlineStr"/>
-      <c r="M14" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
           <t>Bergmyran, Vb</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>718150</v>
+        <v>718526</v>
       </c>
       <c r="R14" t="n">
-        <v>7234307</v>
+        <v>7234595</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -1985,11 +1985,6 @@
       <c r="AA14" t="inlineStr">
         <is>
           <t>2025-07-02</t>
-        </is>
-      </c>
-      <c r="AC14" t="inlineStr">
-        <is>
-          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2016,10 +2011,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>126379443</v>
+        <v>126379434</v>
       </c>
       <c r="B15" t="n">
-        <v>57816</v>
+        <v>57657</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2027,21 +2022,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>103021</v>
+        <v>100109</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2049,7 +2044,7 @@
       <c r="L15" t="inlineStr"/>
       <c r="M15" t="inlineStr">
         <is>
-          <t>upprörd, varnande</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N15" t="inlineStr"/>
@@ -2059,10 +2054,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>718294</v>
+        <v>718150</v>
       </c>
       <c r="R15" t="n">
-        <v>7234414</v>
+        <v>7234307</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2095,6 +2090,11 @@
       <c r="AA15" t="inlineStr">
         <is>
           <t>2025-07-02</t>
+        </is>
+      </c>
+      <c r="AC15" t="inlineStr">
+        <is>
+          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2124,7 +2124,7 @@
         <v>126379451</v>
       </c>
       <c r="B16" t="n">
-        <v>79165</v>
+        <v>79168</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2230,7 +2230,7 @@
         <v>126379487</v>
       </c>
       <c r="B17" t="n">
-        <v>78977</v>
+        <v>78980</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2332,7 +2332,7 @@
         <v>126379469</v>
       </c>
       <c r="B18" t="n">
-        <v>78977</v>
+        <v>78980</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2429,7 +2429,7 @@
         <v>126379458</v>
       </c>
       <c r="B19" t="n">
-        <v>78977</v>
+        <v>78980</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2531,7 +2531,7 @@
         <v>126379428</v>
       </c>
       <c r="B20" t="n">
-        <v>79595</v>
+        <v>79598</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2628,7 +2628,7 @@
         <v>126379454</v>
       </c>
       <c r="B21" t="n">
-        <v>78977</v>
+        <v>78980</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2730,7 +2730,7 @@
         <v>126379427</v>
       </c>
       <c r="B22" t="n">
-        <v>79595</v>
+        <v>79598</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2827,7 +2827,7 @@
         <v>126379468</v>
       </c>
       <c r="B23" t="n">
-        <v>78977</v>
+        <v>78980</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2924,7 +2924,7 @@
         <v>126379481</v>
       </c>
       <c r="B24" t="n">
-        <v>78977</v>
+        <v>78980</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3021,7 +3021,7 @@
         <v>126379424</v>
       </c>
       <c r="B25" t="n">
-        <v>91207</v>
+        <v>91210</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3118,7 +3118,7 @@
         <v>126379478</v>
       </c>
       <c r="B26" t="n">
-        <v>78977</v>
+        <v>78980</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3220,7 +3220,7 @@
         <v>126379457</v>
       </c>
       <c r="B27" t="n">
-        <v>78977</v>
+        <v>78980</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3317,7 +3317,7 @@
         <v>126379446</v>
       </c>
       <c r="B28" t="n">
-        <v>80108</v>
+        <v>80111</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3414,7 +3414,7 @@
         <v>126379447</v>
       </c>
       <c r="B29" t="n">
-        <v>80080</v>
+        <v>80083</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3511,7 +3511,7 @@
         <v>126379470</v>
       </c>
       <c r="B30" t="n">
-        <v>78977</v>
+        <v>78980</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3605,10 +3605,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>126379491</v>
+        <v>126379448</v>
       </c>
       <c r="B31" t="n">
-        <v>92532</v>
+        <v>80119</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3616,21 +3616,21 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>4364</v>
+        <v>6464</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -3640,10 +3640,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>718094</v>
+        <v>718195</v>
       </c>
       <c r="R31" t="n">
-        <v>7234481</v>
+        <v>7234369</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3702,53 +3702,45 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>126379437</v>
+        <v>126379491</v>
       </c>
       <c r="B32" t="n">
-        <v>57656</v>
+        <v>92535</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>100109</v>
+        <v>4364</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
-      <c r="K32" t="inlineStr"/>
-      <c r="L32" t="inlineStr"/>
-      <c r="M32" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N32" t="inlineStr"/>
       <c r="P32" t="inlineStr">
         <is>
           <t>Bergmyran, Vb</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>718001</v>
+        <v>718094</v>
       </c>
       <c r="R32" t="n">
-        <v>7234400</v>
+        <v>7234481</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3781,11 +3773,6 @@
       <c r="AA32" t="inlineStr">
         <is>
           <t>2025-07-02</t>
-        </is>
-      </c>
-      <c r="AC32" t="inlineStr">
-        <is>
-          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -3812,45 +3799,53 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>126379448</v>
+        <v>126379437</v>
       </c>
       <c r="B33" t="n">
-        <v>80116</v>
+        <v>57657</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>6464</v>
+        <v>100109</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
+      <c r="K33" t="inlineStr"/>
+      <c r="L33" t="inlineStr"/>
+      <c r="M33" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N33" t="inlineStr"/>
       <c r="P33" t="inlineStr">
         <is>
           <t>Bergmyran, Vb</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>718195</v>
+        <v>718001</v>
       </c>
       <c r="R33" t="n">
-        <v>7234369</v>
+        <v>7234400</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -3883,6 +3878,11 @@
       <c r="AA33" t="inlineStr">
         <is>
           <t>2025-07-02</t>
+        </is>
+      </c>
+      <c r="AC33" t="inlineStr">
+        <is>
+          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -3912,7 +3912,7 @@
         <v>126379486</v>
       </c>
       <c r="B34" t="n">
-        <v>78977</v>
+        <v>78980</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4009,7 +4009,7 @@
         <v>126379467</v>
       </c>
       <c r="B35" t="n">
-        <v>78977</v>
+        <v>78980</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4106,7 +4106,7 @@
         <v>126379489</v>
       </c>
       <c r="B36" t="n">
-        <v>92532</v>
+        <v>92535</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4203,7 +4203,7 @@
         <v>126379482</v>
       </c>
       <c r="B37" t="n">
-        <v>78977</v>
+        <v>78980</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4305,7 +4305,7 @@
         <v>126379480</v>
       </c>
       <c r="B38" t="n">
-        <v>78977</v>
+        <v>78980</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4399,32 +4399,32 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>126379490</v>
+        <v>126379475</v>
       </c>
       <c r="B39" t="n">
-        <v>92532</v>
+        <v>78980</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>4364</v>
+        <v>6425</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
@@ -4434,10 +4434,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>718545</v>
+        <v>718346</v>
       </c>
       <c r="R39" t="n">
-        <v>7234655</v>
+        <v>7234422</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4496,10 +4496,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>126379475</v>
+        <v>126379453</v>
       </c>
       <c r="B40" t="n">
-        <v>78977</v>
+        <v>91263</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4507,21 +4507,21 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>6425</v>
+        <v>5432</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
@@ -4531,10 +4531,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>718346</v>
+        <v>718212</v>
       </c>
       <c r="R40" t="n">
-        <v>7234422</v>
+        <v>7234351</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4593,32 +4593,32 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>126379453</v>
+        <v>126379490</v>
       </c>
       <c r="B41" t="n">
-        <v>91260</v>
+        <v>92535</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>5432</v>
+        <v>4364</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
@@ -4628,10 +4628,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>718212</v>
+        <v>718545</v>
       </c>
       <c r="R41" t="n">
-        <v>7234351</v>
+        <v>7234655</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -4693,7 +4693,7 @@
         <v>126379476</v>
       </c>
       <c r="B42" t="n">
-        <v>78977</v>
+        <v>78980</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -4795,7 +4795,7 @@
         <v>126379460</v>
       </c>
       <c r="B43" t="n">
-        <v>78977</v>
+        <v>78980</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -4889,53 +4889,45 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>126379441</v>
+        <v>126379485</v>
       </c>
       <c r="B44" t="n">
-        <v>56848</v>
+        <v>78980</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>100138</v>
+        <v>6425</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
-      <c r="K44" t="inlineStr"/>
-      <c r="L44" t="inlineStr"/>
-      <c r="M44" t="inlineStr">
-        <is>
-          <t>äldre spillning</t>
-        </is>
-      </c>
-      <c r="N44" t="inlineStr"/>
       <c r="P44" t="inlineStr">
         <is>
           <t>Bergmyran, Vb</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>718148</v>
+        <v>718173</v>
       </c>
       <c r="R44" t="n">
-        <v>7234311</v>
+        <v>7234351</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -4972,7 +4964,7 @@
       </c>
       <c r="AC44" t="inlineStr">
         <is>
-          <t>Spillning</t>
+          <t>Fertil</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -4999,32 +4991,32 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>126379436</v>
+        <v>126379441</v>
       </c>
       <c r="B45" t="n">
-        <v>57656</v>
+        <v>56849</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>100109</v>
+        <v>100138</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
@@ -5032,7 +5024,7 @@
       <c r="L45" t="inlineStr"/>
       <c r="M45" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>äldre spillning</t>
         </is>
       </c>
       <c r="N45" t="inlineStr"/>
@@ -5042,10 +5034,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>718009</v>
+        <v>718148</v>
       </c>
       <c r="R45" t="n">
-        <v>7234441</v>
+        <v>7234311</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5082,7 +5074,7 @@
       </c>
       <c r="AC45" t="inlineStr">
         <is>
-          <t>Äldre ringhack</t>
+          <t>Spillning</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5109,10 +5101,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>126379485</v>
+        <v>126379436</v>
       </c>
       <c r="B46" t="n">
-        <v>78977</v>
+        <v>57657</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5120,34 +5112,42 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
+      <c r="K46" t="inlineStr"/>
+      <c r="L46" t="inlineStr"/>
+      <c r="M46" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N46" t="inlineStr"/>
       <c r="P46" t="inlineStr">
         <is>
           <t>Bergmyran, Vb</t>
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>718173</v>
+        <v>718009</v>
       </c>
       <c r="R46" t="n">
-        <v>7234351</v>
+        <v>7234441</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5184,7 +5184,7 @@
       </c>
       <c r="AC46" t="inlineStr">
         <is>
-          <t>Fertil</t>
+          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -5214,7 +5214,7 @@
         <v>126379423</v>
       </c>
       <c r="B47" t="n">
-        <v>79009</v>
+        <v>79012</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5311,7 +5311,7 @@
         <v>126379465</v>
       </c>
       <c r="B48" t="n">
-        <v>78977</v>
+        <v>78980</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5413,7 +5413,7 @@
         <v>126379483</v>
       </c>
       <c r="B49" t="n">
-        <v>78977</v>
+        <v>78980</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5515,7 +5515,7 @@
         <v>126379479</v>
       </c>
       <c r="B50" t="n">
-        <v>78977</v>
+        <v>78980</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5609,45 +5609,53 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>126379444</v>
+        <v>126379439</v>
       </c>
       <c r="B51" t="n">
-        <v>98373</v>
+        <v>57657</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>221952</v>
+        <v>100109</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
+      <c r="K51" t="inlineStr"/>
+      <c r="L51" t="inlineStr"/>
+      <c r="M51" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N51" t="inlineStr"/>
       <c r="P51" t="inlineStr">
         <is>
           <t>Bergmyran, Vb</t>
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>717964</v>
+        <v>718038</v>
       </c>
       <c r="R51" t="n">
-        <v>7234394</v>
+        <v>7234341</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -5674,12 +5682,17 @@
       </c>
       <c r="Y51" t="inlineStr">
         <is>
-          <t>2025-07-02</t>
+          <t>2025-07-01</t>
         </is>
       </c>
       <c r="AA51" t="inlineStr">
         <is>
-          <t>2025-07-02</t>
+          <t>2025-07-01</t>
+        </is>
+      </c>
+      <c r="AC51" t="inlineStr">
+        <is>
+          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -5706,53 +5719,45 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>126379439</v>
+        <v>126379444</v>
       </c>
       <c r="B52" t="n">
-        <v>57656</v>
+        <v>98382</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E52" t="n">
-        <v>100109</v>
+        <v>221952</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
-      <c r="K52" t="inlineStr"/>
-      <c r="L52" t="inlineStr"/>
-      <c r="M52" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N52" t="inlineStr"/>
       <c r="P52" t="inlineStr">
         <is>
           <t>Bergmyran, Vb</t>
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>718038</v>
+        <v>717964</v>
       </c>
       <c r="R52" t="n">
-        <v>7234341</v>
+        <v>7234394</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -5779,17 +5784,12 @@
       </c>
       <c r="Y52" t="inlineStr">
         <is>
-          <t>2025-07-01</t>
+          <t>2025-07-02</t>
         </is>
       </c>
       <c r="AA52" t="inlineStr">
         <is>
-          <t>2025-07-01</t>
-        </is>
-      </c>
-      <c r="AC52" t="inlineStr">
-        <is>
-          <t>Äldre ringhack</t>
+          <t>2025-07-02</t>
         </is>
       </c>
       <c r="AD52" t="b">
@@ -5819,7 +5819,7 @@
         <v>126379474</v>
       </c>
       <c r="B53" t="n">
-        <v>78977</v>
+        <v>78980</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -5916,7 +5916,7 @@
         <v>126379455</v>
       </c>
       <c r="B54" t="n">
-        <v>78977</v>
+        <v>78980</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6013,7 +6013,7 @@
         <v>126379456</v>
       </c>
       <c r="B55" t="n">
-        <v>78977</v>
+        <v>78980</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6110,7 +6110,7 @@
         <v>126379435</v>
       </c>
       <c r="B56" t="n">
-        <v>57656</v>
+        <v>57657</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6217,32 +6217,32 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>126379492</v>
+        <v>126379473</v>
       </c>
       <c r="B57" t="n">
-        <v>92532</v>
+        <v>78980</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E57" t="n">
-        <v>4364</v>
+        <v>6425</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
@@ -6252,10 +6252,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>718282</v>
+        <v>718327</v>
       </c>
       <c r="R57" t="n">
-        <v>7234434</v>
+        <v>7234412</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -6317,7 +6317,7 @@
         <v>126379426</v>
       </c>
       <c r="B58" t="n">
-        <v>79595</v>
+        <v>79598</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -6411,32 +6411,32 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>126379473</v>
+        <v>126379492</v>
       </c>
       <c r="B59" t="n">
-        <v>78977</v>
+        <v>92535</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E59" t="n">
-        <v>6425</v>
+        <v>4364</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
@@ -6446,10 +6446,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>718327</v>
+        <v>718282</v>
       </c>
       <c r="R59" t="n">
-        <v>7234412</v>
+        <v>7234434</v>
       </c>
       <c r="S59" t="n">
         <v>10</v>
@@ -6511,7 +6511,7 @@
         <v>126379472</v>
       </c>
       <c r="B60" t="n">
-        <v>78977</v>
+        <v>78980</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -6608,7 +6608,7 @@
         <v>126379466</v>
       </c>
       <c r="B61" t="n">
-        <v>78977</v>
+        <v>78980</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -6702,10 +6702,10 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>126379459</v>
+        <v>126379438</v>
       </c>
       <c r="B62" t="n">
-        <v>78977</v>
+        <v>57657</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -6713,34 +6713,42 @@
         </is>
       </c>
       <c r="E62" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
+      <c r="K62" t="inlineStr"/>
+      <c r="L62" t="inlineStr"/>
+      <c r="M62" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N62" t="inlineStr"/>
       <c r="P62" t="inlineStr">
         <is>
           <t>Bergmyran, Vb</t>
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>718274</v>
+        <v>718061</v>
       </c>
       <c r="R62" t="n">
-        <v>7234439</v>
+        <v>7234332</v>
       </c>
       <c r="S62" t="n">
         <v>10</v>
@@ -6767,12 +6775,17 @@
       </c>
       <c r="Y62" t="inlineStr">
         <is>
-          <t>2025-07-02</t>
+          <t>2025-07-01</t>
         </is>
       </c>
       <c r="AA62" t="inlineStr">
         <is>
-          <t>2025-07-02</t>
+          <t>2025-07-01</t>
+        </is>
+      </c>
+      <c r="AC62" t="inlineStr">
+        <is>
+          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD62" t="b">
@@ -6799,10 +6812,10 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>126379464</v>
+        <v>126379459</v>
       </c>
       <c r="B63" t="n">
-        <v>78977</v>
+        <v>78980</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -6834,10 +6847,10 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>718427</v>
+        <v>718274</v>
       </c>
       <c r="R63" t="n">
-        <v>7234679</v>
+        <v>7234439</v>
       </c>
       <c r="S63" t="n">
         <v>10</v>
@@ -6896,10 +6909,10 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>126379462</v>
+        <v>126379464</v>
       </c>
       <c r="B64" t="n">
-        <v>78977</v>
+        <v>78980</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -6931,10 +6944,10 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>718535</v>
+        <v>718427</v>
       </c>
       <c r="R64" t="n">
-        <v>7234587</v>
+        <v>7234679</v>
       </c>
       <c r="S64" t="n">
         <v>10</v>
@@ -6967,11 +6980,6 @@
       <c r="AA64" t="inlineStr">
         <is>
           <t>2025-07-02</t>
-        </is>
-      </c>
-      <c r="AC64" t="inlineStr">
-        <is>
-          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD64" t="b">
@@ -6998,10 +7006,10 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>126379438</v>
+        <v>126379462</v>
       </c>
       <c r="B65" t="n">
-        <v>57656</v>
+        <v>78980</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -7009,42 +7017,34 @@
         </is>
       </c>
       <c r="E65" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
-      <c r="K65" t="inlineStr"/>
-      <c r="L65" t="inlineStr"/>
-      <c r="M65" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N65" t="inlineStr"/>
       <c r="P65" t="inlineStr">
         <is>
           <t>Bergmyran, Vb</t>
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>718061</v>
+        <v>718535</v>
       </c>
       <c r="R65" t="n">
-        <v>7234332</v>
+        <v>7234587</v>
       </c>
       <c r="S65" t="n">
         <v>10</v>
@@ -7071,17 +7071,17 @@
       </c>
       <c r="Y65" t="inlineStr">
         <is>
-          <t>2025-07-01</t>
+          <t>2025-07-02</t>
         </is>
       </c>
       <c r="AA65" t="inlineStr">
         <is>
-          <t>2025-07-01</t>
+          <t>2025-07-02</t>
         </is>
       </c>
       <c r="AC65" t="inlineStr">
         <is>
-          <t>Äldre ringhack</t>
+          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD65" t="b">
@@ -7111,7 +7111,7 @@
         <v>126379442</v>
       </c>
       <c r="B66" t="n">
-        <v>57816</v>
+        <v>57817</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>

--- a/artfynd/A 24579-2025 artfynd.xlsx
+++ b/artfynd/A 24579-2025 artfynd.xlsx
@@ -1301,10 +1301,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>126379471</v>
+        <v>126379488</v>
       </c>
       <c r="B8" t="n">
-        <v>78980</v>
+        <v>78647</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1312,21 +1312,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6425</v>
+        <v>353</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1336,10 +1336,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>718115</v>
+        <v>718044</v>
       </c>
       <c r="R8" t="n">
-        <v>7234496</v>
+        <v>7234385</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1372,11 +1372,6 @@
       <c r="AA8" t="inlineStr">
         <is>
           <t>2025-07-02</t>
-        </is>
-      </c>
-      <c r="AC8" t="inlineStr">
-        <is>
-          <t>Långa bålar</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1403,32 +1398,32 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>126379425</v>
+        <v>126379471</v>
       </c>
       <c r="B9" t="n">
-        <v>91210</v>
+        <v>78980</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>5447</v>
+        <v>6425</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1438,10 +1433,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>717969</v>
+        <v>718115</v>
       </c>
       <c r="R9" t="n">
-        <v>7234409</v>
+        <v>7234496</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1474,6 +1469,11 @@
       <c r="AA9" t="inlineStr">
         <is>
           <t>2025-07-02</t>
+        </is>
+      </c>
+      <c r="AC9" t="inlineStr">
+        <is>
+          <t>Långa bålar</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1500,32 +1500,32 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>126379484</v>
+        <v>126379425</v>
       </c>
       <c r="B10" t="n">
-        <v>78980</v>
+        <v>91210</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6425</v>
+        <v>5447</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1535,10 +1535,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>718212</v>
+        <v>717969</v>
       </c>
       <c r="R10" t="n">
-        <v>7234353</v>
+        <v>7234409</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1571,11 +1571,6 @@
       <c r="AA10" t="inlineStr">
         <is>
           <t>2025-07-02</t>
-        </is>
-      </c>
-      <c r="AC10" t="inlineStr">
-        <is>
-          <t>Med apothecier</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1602,10 +1597,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>126379488</v>
+        <v>126379484</v>
       </c>
       <c r="B11" t="n">
-        <v>78647</v>
+        <v>78980</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1613,21 +1608,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>353</v>
+        <v>6425</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1637,10 +1632,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>718044</v>
+        <v>718212</v>
       </c>
       <c r="R11" t="n">
-        <v>7234385</v>
+        <v>7234353</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1673,6 +1668,11 @@
       <c r="AA11" t="inlineStr">
         <is>
           <t>2025-07-02</t>
+        </is>
+      </c>
+      <c r="AC11" t="inlineStr">
+        <is>
+          <t>Med apothecier</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -5211,10 +5211,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>126379423</v>
+        <v>126379465</v>
       </c>
       <c r="B47" t="n">
-        <v>79012</v>
+        <v>78980</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5222,21 +5222,21 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>185</v>
+        <v>6425</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
@@ -5246,10 +5246,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>718221</v>
+        <v>718515</v>
       </c>
       <c r="R47" t="n">
-        <v>7234403</v>
+        <v>7234673</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5282,6 +5282,11 @@
       <c r="AA47" t="inlineStr">
         <is>
           <t>2025-07-02</t>
+        </is>
+      </c>
+      <c r="AC47" t="inlineStr">
+        <is>
+          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -5308,10 +5313,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>126379465</v>
+        <v>126379423</v>
       </c>
       <c r="B48" t="n">
-        <v>78980</v>
+        <v>79012</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5319,21 +5324,21 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>6425</v>
+        <v>185</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
@@ -5343,10 +5348,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>718515</v>
+        <v>718221</v>
       </c>
       <c r="R48" t="n">
-        <v>7234673</v>
+        <v>7234403</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5379,11 +5384,6 @@
       <c r="AA48" t="inlineStr">
         <is>
           <t>2025-07-02</t>
-        </is>
-      </c>
-      <c r="AC48" t="inlineStr">
-        <is>
-          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD48" t="b">

--- a/artfynd/A 24579-2025 artfynd.xlsx
+++ b/artfynd/A 24579-2025 artfynd.xlsx
@@ -772,10 +772,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>126379452</v>
+        <v>126379432</v>
       </c>
       <c r="B3" t="n">
-        <v>91263</v>
+        <v>57657</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -783,34 +783,42 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
+      <c r="K3" t="inlineStr"/>
+      <c r="L3" t="inlineStr"/>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
           <t>Bergmyran, Vb</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>718194</v>
+        <v>718387</v>
       </c>
       <c r="R3" t="n">
-        <v>7234461</v>
+        <v>7234490</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -843,6 +851,11 @@
       <c r="AA3" t="inlineStr">
         <is>
           <t>2025-07-02</t>
+        </is>
+      </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -869,7 +882,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>126379432</v>
+        <v>126379431</v>
       </c>
       <c r="B4" t="n">
         <v>57657</v>
@@ -898,24 +911,16 @@
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
-      <c r="K4" t="inlineStr"/>
-      <c r="L4" t="inlineStr"/>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
           <t>Bergmyran, Vb</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>718387</v>
+        <v>718398</v>
       </c>
       <c r="R4" t="n">
-        <v>7234490</v>
+        <v>7234399</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -979,7 +984,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>126379431</v>
+        <v>126379440</v>
       </c>
       <c r="B5" t="n">
         <v>57657</v>
@@ -1008,16 +1013,24 @@
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
+      <c r="K5" t="inlineStr"/>
+      <c r="L5" t="inlineStr"/>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
           <t>Bergmyran, Vb</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>718398</v>
+        <v>718336</v>
       </c>
       <c r="R5" t="n">
-        <v>7234399</v>
+        <v>7234249</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1044,17 +1057,17 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2025-07-02</t>
+          <t>2025-07-01</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2025-07-02</t>
+          <t>2025-07-01</t>
         </is>
       </c>
       <c r="AC5" t="inlineStr">
         <is>
-          <t>Äldre ringhack</t>
+          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1081,10 +1094,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>126379440</v>
+        <v>126379452</v>
       </c>
       <c r="B6" t="n">
-        <v>57657</v>
+        <v>91263</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1092,42 +1105,34 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
-      <c r="K6" t="inlineStr"/>
-      <c r="L6" t="inlineStr"/>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
           <t>Bergmyran, Vb</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>718336</v>
+        <v>718194</v>
       </c>
       <c r="R6" t="n">
-        <v>7234249</v>
+        <v>7234461</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1154,17 +1159,12 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2025-07-01</t>
+          <t>2025-07-02</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2025-07-01</t>
-        </is>
-      </c>
-      <c r="AC6" t="inlineStr">
-        <is>
-          <t>Färska ringhack</t>
+          <t>2025-07-02</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1500,32 +1500,32 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>126379425</v>
+        <v>126379484</v>
       </c>
       <c r="B10" t="n">
-        <v>91210</v>
+        <v>78980</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>5447</v>
+        <v>6425</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1535,10 +1535,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>717969</v>
+        <v>718212</v>
       </c>
       <c r="R10" t="n">
-        <v>7234409</v>
+        <v>7234353</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1571,6 +1571,11 @@
       <c r="AA10" t="inlineStr">
         <is>
           <t>2025-07-02</t>
+        </is>
+      </c>
+      <c r="AC10" t="inlineStr">
+        <is>
+          <t>Med apothecier</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1597,32 +1602,32 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>126379484</v>
+        <v>126379425</v>
       </c>
       <c r="B11" t="n">
-        <v>78980</v>
+        <v>91210</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6425</v>
+        <v>5447</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1632,10 +1637,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>718212</v>
+        <v>717969</v>
       </c>
       <c r="R11" t="n">
-        <v>7234353</v>
+        <v>7234409</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1668,11 +1673,6 @@
       <c r="AA11" t="inlineStr">
         <is>
           <t>2025-07-02</t>
-        </is>
-      </c>
-      <c r="AC11" t="inlineStr">
-        <is>
-          <t>Med apothecier</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1699,10 +1699,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>126379430</v>
+        <v>126379463</v>
       </c>
       <c r="B12" t="n">
-        <v>57657</v>
+        <v>78980</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1710,42 +1710,34 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
-      <c r="K12" t="inlineStr"/>
-      <c r="L12" t="inlineStr"/>
-      <c r="M12" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
           <t>Bergmyran, Vb</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>718154</v>
+        <v>718526</v>
       </c>
       <c r="R12" t="n">
-        <v>7234509</v>
+        <v>7234595</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1778,11 +1770,6 @@
       <c r="AA12" t="inlineStr">
         <is>
           <t>2025-07-02</t>
-        </is>
-      </c>
-      <c r="AC12" t="inlineStr">
-        <is>
-          <t>Färskt ringhack</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1809,10 +1796,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>126379443</v>
+        <v>126379430</v>
       </c>
       <c r="B13" t="n">
-        <v>57817</v>
+        <v>57657</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1820,21 +1807,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>103021</v>
+        <v>100109</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1842,7 +1829,7 @@
       <c r="L13" t="inlineStr"/>
       <c r="M13" t="inlineStr">
         <is>
-          <t>upprörd, varnande</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N13" t="inlineStr"/>
@@ -1852,10 +1839,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>718294</v>
+        <v>718154</v>
       </c>
       <c r="R13" t="n">
-        <v>7234414</v>
+        <v>7234509</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1888,6 +1875,11 @@
       <c r="AA13" t="inlineStr">
         <is>
           <t>2025-07-02</t>
+        </is>
+      </c>
+      <c r="AC13" t="inlineStr">
+        <is>
+          <t>Färskt ringhack</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1914,10 +1906,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>126379463</v>
+        <v>126379434</v>
       </c>
       <c r="B14" t="n">
-        <v>78980</v>
+        <v>57657</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1925,34 +1917,42 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
+      <c r="K14" t="inlineStr"/>
+      <c r="L14" t="inlineStr"/>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
           <t>Bergmyran, Vb</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>718526</v>
+        <v>718150</v>
       </c>
       <c r="R14" t="n">
-        <v>7234595</v>
+        <v>7234307</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -1985,6 +1985,11 @@
       <c r="AA14" t="inlineStr">
         <is>
           <t>2025-07-02</t>
+        </is>
+      </c>
+      <c r="AC14" t="inlineStr">
+        <is>
+          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2011,10 +2016,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>126379434</v>
+        <v>126379443</v>
       </c>
       <c r="B15" t="n">
-        <v>57657</v>
+        <v>57817</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2022,21 +2027,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>100109</v>
+        <v>103021</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2044,7 +2049,7 @@
       <c r="L15" t="inlineStr"/>
       <c r="M15" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>upprörd, varnande</t>
         </is>
       </c>
       <c r="N15" t="inlineStr"/>
@@ -2054,10 +2059,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>718150</v>
+        <v>718294</v>
       </c>
       <c r="R15" t="n">
-        <v>7234307</v>
+        <v>7234414</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2090,11 +2095,6 @@
       <c r="AA15" t="inlineStr">
         <is>
           <t>2025-07-02</t>
-        </is>
-      </c>
-      <c r="AC15" t="inlineStr">
-        <is>
-          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2824,32 +2824,32 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>126379468</v>
+        <v>126379424</v>
       </c>
       <c r="B23" t="n">
-        <v>78980</v>
+        <v>91210</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>6425</v>
+        <v>5447</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -2859,10 +2859,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>718577</v>
+        <v>718450</v>
       </c>
       <c r="R23" t="n">
-        <v>7234539</v>
+        <v>7234710</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2921,32 +2921,32 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>126379481</v>
+        <v>126379446</v>
       </c>
       <c r="B24" t="n">
-        <v>78980</v>
+        <v>80111</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>6425</v>
+        <v>6461</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Norrlandslav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma arcticum</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Torss.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -2956,10 +2956,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>718217</v>
+        <v>718189</v>
       </c>
       <c r="R24" t="n">
-        <v>7234406</v>
+        <v>7234350</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3018,32 +3018,32 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>126379424</v>
+        <v>126379468</v>
       </c>
       <c r="B25" t="n">
-        <v>91210</v>
+        <v>78980</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>5447</v>
+        <v>6425</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3053,10 +3053,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>718450</v>
+        <v>718577</v>
       </c>
       <c r="R25" t="n">
-        <v>7234710</v>
+        <v>7234539</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3115,7 +3115,7 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>126379478</v>
+        <v>126379481</v>
       </c>
       <c r="B26" t="n">
         <v>78980</v>
@@ -3150,10 +3150,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>718319</v>
+        <v>718217</v>
       </c>
       <c r="R26" t="n">
-        <v>7234335</v>
+        <v>7234406</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3186,11 +3186,6 @@
       <c r="AA26" t="inlineStr">
         <is>
           <t>2025-07-02</t>
-        </is>
-      </c>
-      <c r="AC26" t="inlineStr">
-        <is>
-          <t>Långa bålar</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3217,7 +3212,7 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>126379457</v>
+        <v>126379478</v>
       </c>
       <c r="B27" t="n">
         <v>78980</v>
@@ -3252,10 +3247,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>718450</v>
+        <v>718319</v>
       </c>
       <c r="R27" t="n">
-        <v>7234706</v>
+        <v>7234335</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3288,6 +3283,11 @@
       <c r="AA27" t="inlineStr">
         <is>
           <t>2025-07-02</t>
+        </is>
+      </c>
+      <c r="AC27" t="inlineStr">
+        <is>
+          <t>Långa bålar</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3314,32 +3314,32 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>126379446</v>
+        <v>126379457</v>
       </c>
       <c r="B28" t="n">
-        <v>80111</v>
+        <v>78980</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>6461</v>
+        <v>6425</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Norrlandslav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Nephroma arcticum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(L.) Torss.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3349,10 +3349,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>718189</v>
+        <v>718450</v>
       </c>
       <c r="R28" t="n">
-        <v>7234350</v>
+        <v>7234706</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3508,10 +3508,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>126379470</v>
+        <v>126379437</v>
       </c>
       <c r="B30" t="n">
-        <v>78980</v>
+        <v>57657</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3519,34 +3519,42 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
+      <c r="K30" t="inlineStr"/>
+      <c r="L30" t="inlineStr"/>
+      <c r="M30" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
           <t>Bergmyran, Vb</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>718088</v>
+        <v>718001</v>
       </c>
       <c r="R30" t="n">
-        <v>7234482</v>
+        <v>7234400</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3579,6 +3587,11 @@
       <c r="AA30" t="inlineStr">
         <is>
           <t>2025-07-02</t>
+        </is>
+      </c>
+      <c r="AC30" t="inlineStr">
+        <is>
+          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3605,32 +3618,32 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>126379448</v>
+        <v>126379470</v>
       </c>
       <c r="B31" t="n">
-        <v>80119</v>
+        <v>78980</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>6464</v>
+        <v>6425</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -3640,10 +3653,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>718195</v>
+        <v>718088</v>
       </c>
       <c r="R31" t="n">
-        <v>7234369</v>
+        <v>7234482</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3799,53 +3812,45 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>126379437</v>
+        <v>126379448</v>
       </c>
       <c r="B33" t="n">
-        <v>57657</v>
+        <v>80119</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>100109</v>
+        <v>6464</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
-      <c r="K33" t="inlineStr"/>
-      <c r="L33" t="inlineStr"/>
-      <c r="M33" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N33" t="inlineStr"/>
       <c r="P33" t="inlineStr">
         <is>
           <t>Bergmyran, Vb</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>718001</v>
+        <v>718195</v>
       </c>
       <c r="R33" t="n">
-        <v>7234400</v>
+        <v>7234369</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -3878,11 +3883,6 @@
       <c r="AA33" t="inlineStr">
         <is>
           <t>2025-07-02</t>
-        </is>
-      </c>
-      <c r="AC33" t="inlineStr">
-        <is>
-          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4399,32 +4399,32 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>126379475</v>
+        <v>126379490</v>
       </c>
       <c r="B39" t="n">
-        <v>78980</v>
+        <v>92535</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>6425</v>
+        <v>4364</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
@@ -4434,10 +4434,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>718346</v>
+        <v>718545</v>
       </c>
       <c r="R39" t="n">
-        <v>7234422</v>
+        <v>7234655</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4496,10 +4496,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>126379453</v>
+        <v>126379475</v>
       </c>
       <c r="B40" t="n">
-        <v>91263</v>
+        <v>78980</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4507,21 +4507,21 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
@@ -4531,10 +4531,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>718212</v>
+        <v>718346</v>
       </c>
       <c r="R40" t="n">
-        <v>7234351</v>
+        <v>7234422</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4593,32 +4593,32 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>126379490</v>
+        <v>126379453</v>
       </c>
       <c r="B41" t="n">
-        <v>92535</v>
+        <v>91263</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>4364</v>
+        <v>5432</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
@@ -4628,10 +4628,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>718545</v>
+        <v>718212</v>
       </c>
       <c r="R41" t="n">
-        <v>7234655</v>
+        <v>7234351</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -4991,32 +4991,32 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>126379441</v>
+        <v>126379436</v>
       </c>
       <c r="B45" t="n">
-        <v>56849</v>
+        <v>57657</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>100138</v>
+        <v>100109</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
@@ -5024,7 +5024,7 @@
       <c r="L45" t="inlineStr"/>
       <c r="M45" t="inlineStr">
         <is>
-          <t>äldre spillning</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="N45" t="inlineStr"/>
@@ -5034,10 +5034,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>718148</v>
+        <v>718009</v>
       </c>
       <c r="R45" t="n">
-        <v>7234311</v>
+        <v>7234441</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5074,7 +5074,7 @@
       </c>
       <c r="AC45" t="inlineStr">
         <is>
-          <t>Spillning</t>
+          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5101,32 +5101,32 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>126379436</v>
+        <v>126379441</v>
       </c>
       <c r="B46" t="n">
-        <v>57657</v>
+        <v>56849</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>100109</v>
+        <v>100138</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
@@ -5134,7 +5134,7 @@
       <c r="L46" t="inlineStr"/>
       <c r="M46" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>äldre spillning</t>
         </is>
       </c>
       <c r="N46" t="inlineStr"/>
@@ -5144,10 +5144,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>718009</v>
+        <v>718148</v>
       </c>
       <c r="R46" t="n">
-        <v>7234441</v>
+        <v>7234311</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5184,7 +5184,7 @@
       </c>
       <c r="AC46" t="inlineStr">
         <is>
-          <t>Äldre ringhack</t>
+          <t>Spillning</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -5211,10 +5211,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>126379465</v>
+        <v>126379423</v>
       </c>
       <c r="B47" t="n">
-        <v>78980</v>
+        <v>79012</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5222,21 +5222,21 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>6425</v>
+        <v>185</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
@@ -5246,10 +5246,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>718515</v>
+        <v>718221</v>
       </c>
       <c r="R47" t="n">
-        <v>7234673</v>
+        <v>7234403</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5282,11 +5282,6 @@
       <c r="AA47" t="inlineStr">
         <is>
           <t>2025-07-02</t>
-        </is>
-      </c>
-      <c r="AC47" t="inlineStr">
-        <is>
-          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -5313,10 +5308,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>126379423</v>
+        <v>126379465</v>
       </c>
       <c r="B48" t="n">
-        <v>79012</v>
+        <v>78980</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5324,21 +5319,21 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>185</v>
+        <v>6425</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
@@ -5348,10 +5343,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>718221</v>
+        <v>718515</v>
       </c>
       <c r="R48" t="n">
-        <v>7234403</v>
+        <v>7234673</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5384,6 +5379,11 @@
       <c r="AA48" t="inlineStr">
         <is>
           <t>2025-07-02</t>
+        </is>
+      </c>
+      <c r="AC48" t="inlineStr">
+        <is>
+          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -5816,10 +5816,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>126379474</v>
+        <v>126379435</v>
       </c>
       <c r="B53" t="n">
-        <v>78980</v>
+        <v>57657</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -5827,34 +5827,42 @@
         </is>
       </c>
       <c r="E53" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
+      <c r="K53" t="inlineStr"/>
+      <c r="L53" t="inlineStr"/>
+      <c r="M53" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N53" t="inlineStr"/>
       <c r="P53" t="inlineStr">
         <is>
           <t>Bergmyran, Vb</t>
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>718328</v>
+        <v>718107</v>
       </c>
       <c r="R53" t="n">
-        <v>7234423</v>
+        <v>7234326</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -5887,6 +5895,11 @@
       <c r="AA53" t="inlineStr">
         <is>
           <t>2025-07-02</t>
+        </is>
+      </c>
+      <c r="AC53" t="inlineStr">
+        <is>
+          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD53" t="b">
@@ -5913,7 +5926,7 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>126379455</v>
+        <v>126379474</v>
       </c>
       <c r="B54" t="n">
         <v>78980</v>
@@ -5948,10 +5961,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>718524</v>
+        <v>718328</v>
       </c>
       <c r="R54" t="n">
-        <v>7234543</v>
+        <v>7234423</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -6010,7 +6023,7 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>126379456</v>
+        <v>126379455</v>
       </c>
       <c r="B55" t="n">
         <v>78980</v>
@@ -6045,10 +6058,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>718493</v>
+        <v>718524</v>
       </c>
       <c r="R55" t="n">
-        <v>7234644</v>
+        <v>7234543</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -6107,10 +6120,10 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>126379435</v>
+        <v>126379456</v>
       </c>
       <c r="B56" t="n">
-        <v>57657</v>
+        <v>78980</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6118,42 +6131,34 @@
         </is>
       </c>
       <c r="E56" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
-      <c r="K56" t="inlineStr"/>
-      <c r="L56" t="inlineStr"/>
-      <c r="M56" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N56" t="inlineStr"/>
       <c r="P56" t="inlineStr">
         <is>
           <t>Bergmyran, Vb</t>
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>718107</v>
+        <v>718493</v>
       </c>
       <c r="R56" t="n">
-        <v>7234326</v>
+        <v>7234644</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -6186,11 +6191,6 @@
       <c r="AA56" t="inlineStr">
         <is>
           <t>2025-07-02</t>
-        </is>
-      </c>
-      <c r="AC56" t="inlineStr">
-        <is>
-          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD56" t="b">
@@ -6702,10 +6702,10 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>126379438</v>
+        <v>126379459</v>
       </c>
       <c r="B62" t="n">
-        <v>57657</v>
+        <v>78980</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -6713,42 +6713,34 @@
         </is>
       </c>
       <c r="E62" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
-      <c r="K62" t="inlineStr"/>
-      <c r="L62" t="inlineStr"/>
-      <c r="M62" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N62" t="inlineStr"/>
       <c r="P62" t="inlineStr">
         <is>
           <t>Bergmyran, Vb</t>
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>718061</v>
+        <v>718274</v>
       </c>
       <c r="R62" t="n">
-        <v>7234332</v>
+        <v>7234439</v>
       </c>
       <c r="S62" t="n">
         <v>10</v>
@@ -6775,17 +6767,12 @@
       </c>
       <c r="Y62" t="inlineStr">
         <is>
-          <t>2025-07-01</t>
+          <t>2025-07-02</t>
         </is>
       </c>
       <c r="AA62" t="inlineStr">
         <is>
-          <t>2025-07-01</t>
-        </is>
-      </c>
-      <c r="AC62" t="inlineStr">
-        <is>
-          <t>Äldre ringhack</t>
+          <t>2025-07-02</t>
         </is>
       </c>
       <c r="AD62" t="b">
@@ -6812,7 +6799,7 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>126379459</v>
+        <v>126379464</v>
       </c>
       <c r="B63" t="n">
         <v>78980</v>
@@ -6847,10 +6834,10 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>718274</v>
+        <v>718427</v>
       </c>
       <c r="R63" t="n">
-        <v>7234439</v>
+        <v>7234679</v>
       </c>
       <c r="S63" t="n">
         <v>10</v>
@@ -6909,7 +6896,7 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>126379464</v>
+        <v>126379462</v>
       </c>
       <c r="B64" t="n">
         <v>78980</v>
@@ -6944,10 +6931,10 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>718427</v>
+        <v>718535</v>
       </c>
       <c r="R64" t="n">
-        <v>7234679</v>
+        <v>7234587</v>
       </c>
       <c r="S64" t="n">
         <v>10</v>
@@ -6980,6 +6967,11 @@
       <c r="AA64" t="inlineStr">
         <is>
           <t>2025-07-02</t>
+        </is>
+      </c>
+      <c r="AC64" t="inlineStr">
+        <is>
+          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD64" t="b">
@@ -7006,10 +6998,10 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>126379462</v>
+        <v>126379438</v>
       </c>
       <c r="B65" t="n">
-        <v>78980</v>
+        <v>57657</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -7017,34 +7009,42 @@
         </is>
       </c>
       <c r="E65" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
+      <c r="K65" t="inlineStr"/>
+      <c r="L65" t="inlineStr"/>
+      <c r="M65" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N65" t="inlineStr"/>
       <c r="P65" t="inlineStr">
         <is>
           <t>Bergmyran, Vb</t>
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>718535</v>
+        <v>718061</v>
       </c>
       <c r="R65" t="n">
-        <v>7234587</v>
+        <v>7234332</v>
       </c>
       <c r="S65" t="n">
         <v>10</v>
@@ -7071,17 +7071,17 @@
       </c>
       <c r="Y65" t="inlineStr">
         <is>
-          <t>2025-07-02</t>
+          <t>2025-07-01</t>
         </is>
       </c>
       <c r="AA65" t="inlineStr">
         <is>
-          <t>2025-07-02</t>
+          <t>2025-07-01</t>
         </is>
       </c>
       <c r="AC65" t="inlineStr">
         <is>
-          <t>Rikligt</t>
+          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD65" t="b">

--- a/artfynd/A 24579-2025 artfynd.xlsx
+++ b/artfynd/A 24579-2025 artfynd.xlsx
@@ -1699,45 +1699,48 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>126379463</v>
+        <v>126379451</v>
       </c>
       <c r="B12" t="n">
-        <v>78980</v>
+        <v>79168</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6425</v>
+        <v>230552</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Gropig skägglav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Usnea barbata</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Weber ex F.H.Wigg.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
+      <c r="J12" t="inlineStr"/>
+      <c r="K12" t="inlineStr"/>
+      <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
           <t>Bergmyran, Vb</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>718526</v>
+        <v>717977</v>
       </c>
       <c r="R12" t="n">
-        <v>7234595</v>
+        <v>7234425</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1772,12 +1775,18 @@
           <t>2025-07-02</t>
         </is>
       </c>
+      <c r="AC12" t="inlineStr">
+        <is>
+          <t>Måste efterforska</t>
+        </is>
+      </c>
       <c r="AD12" t="b">
         <v>0</v>
       </c>
       <c r="AE12" t="b">
         <v>0</v>
       </c>
+      <c r="AF12" t="inlineStr"/>
       <c r="AG12" t="b">
         <v>0</v>
       </c>
@@ -1796,10 +1805,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>126379430</v>
+        <v>126379463</v>
       </c>
       <c r="B13" t="n">
-        <v>57657</v>
+        <v>78980</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1807,42 +1816,34 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
-      <c r="K13" t="inlineStr"/>
-      <c r="L13" t="inlineStr"/>
-      <c r="M13" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
           <t>Bergmyran, Vb</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>718154</v>
+        <v>718526</v>
       </c>
       <c r="R13" t="n">
-        <v>7234509</v>
+        <v>7234595</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1875,11 +1876,6 @@
       <c r="AA13" t="inlineStr">
         <is>
           <t>2025-07-02</t>
-        </is>
-      </c>
-      <c r="AC13" t="inlineStr">
-        <is>
-          <t>Färskt ringhack</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1906,7 +1902,7 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>126379434</v>
+        <v>126379430</v>
       </c>
       <c r="B14" t="n">
         <v>57657</v>
@@ -1949,10 +1945,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>718150</v>
+        <v>718154</v>
       </c>
       <c r="R14" t="n">
-        <v>7234307</v>
+        <v>7234509</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -1989,7 +1985,7 @@
       </c>
       <c r="AC14" t="inlineStr">
         <is>
-          <t>Färska ringhack</t>
+          <t>Färskt ringhack</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2016,10 +2012,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>126379443</v>
+        <v>126379434</v>
       </c>
       <c r="B15" t="n">
-        <v>57817</v>
+        <v>57657</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2027,21 +2023,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>103021</v>
+        <v>100109</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2049,7 +2045,7 @@
       <c r="L15" t="inlineStr"/>
       <c r="M15" t="inlineStr">
         <is>
-          <t>upprörd, varnande</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N15" t="inlineStr"/>
@@ -2059,10 +2055,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>718294</v>
+        <v>718150</v>
       </c>
       <c r="R15" t="n">
-        <v>7234414</v>
+        <v>7234307</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2095,6 +2091,11 @@
       <c r="AA15" t="inlineStr">
         <is>
           <t>2025-07-02</t>
+        </is>
+      </c>
+      <c r="AC15" t="inlineStr">
+        <is>
+          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2121,37 +2122,42 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>126379451</v>
+        <v>126379443</v>
       </c>
       <c r="B16" t="n">
-        <v>79168</v>
+        <v>57817</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>230552</v>
+        <v>103021</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Gropig skägglav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Usnea barbata</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(L.) Weber ex F.H.Wigg.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
-      <c r="J16" t="inlineStr"/>
       <c r="K16" t="inlineStr"/>
+      <c r="L16" t="inlineStr"/>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>upprörd, varnande</t>
+        </is>
+      </c>
       <c r="N16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
@@ -2159,10 +2165,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>717977</v>
+        <v>718294</v>
       </c>
       <c r="R16" t="n">
-        <v>7234425</v>
+        <v>7234414</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2197,18 +2203,12 @@
           <t>2025-07-02</t>
         </is>
       </c>
-      <c r="AC16" t="inlineStr">
-        <is>
-          <t>Måste efterforska</t>
-        </is>
-      </c>
       <c r="AD16" t="b">
         <v>0</v>
       </c>
       <c r="AE16" t="b">
         <v>0</v>
       </c>
-      <c r="AF16" t="inlineStr"/>
       <c r="AG16" t="b">
         <v>0</v>
       </c>
@@ -5609,53 +5609,45 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>126379439</v>
+        <v>126379444</v>
       </c>
       <c r="B51" t="n">
-        <v>57657</v>
+        <v>98382</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>100109</v>
+        <v>221952</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
-      <c r="K51" t="inlineStr"/>
-      <c r="L51" t="inlineStr"/>
-      <c r="M51" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N51" t="inlineStr"/>
       <c r="P51" t="inlineStr">
         <is>
           <t>Bergmyran, Vb</t>
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>718038</v>
+        <v>717964</v>
       </c>
       <c r="R51" t="n">
-        <v>7234341</v>
+        <v>7234394</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -5682,17 +5674,12 @@
       </c>
       <c r="Y51" t="inlineStr">
         <is>
-          <t>2025-07-01</t>
+          <t>2025-07-02</t>
         </is>
       </c>
       <c r="AA51" t="inlineStr">
         <is>
-          <t>2025-07-01</t>
-        </is>
-      </c>
-      <c r="AC51" t="inlineStr">
-        <is>
-          <t>Äldre ringhack</t>
+          <t>2025-07-02</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -5719,45 +5706,53 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>126379444</v>
+        <v>126379439</v>
       </c>
       <c r="B52" t="n">
-        <v>98382</v>
+        <v>57657</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E52" t="n">
-        <v>221952</v>
+        <v>100109</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
+      <c r="K52" t="inlineStr"/>
+      <c r="L52" t="inlineStr"/>
+      <c r="M52" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N52" t="inlineStr"/>
       <c r="P52" t="inlineStr">
         <is>
           <t>Bergmyran, Vb</t>
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>717964</v>
+        <v>718038</v>
       </c>
       <c r="R52" t="n">
-        <v>7234394</v>
+        <v>7234341</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -5784,12 +5779,17 @@
       </c>
       <c r="Y52" t="inlineStr">
         <is>
-          <t>2025-07-02</t>
+          <t>2025-07-01</t>
         </is>
       </c>
       <c r="AA52" t="inlineStr">
         <is>
-          <t>2025-07-02</t>
+          <t>2025-07-01</t>
+        </is>
+      </c>
+      <c r="AC52" t="inlineStr">
+        <is>
+          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD52" t="b">
@@ -6314,32 +6314,32 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>126379426</v>
+        <v>126379492</v>
       </c>
       <c r="B58" t="n">
-        <v>79598</v>
+        <v>92535</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E58" t="n">
-        <v>6453</v>
+        <v>4364</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
@@ -6349,10 +6349,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>718364</v>
+        <v>718282</v>
       </c>
       <c r="R58" t="n">
-        <v>7234409</v>
+        <v>7234434</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -6411,32 +6411,32 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>126379492</v>
+        <v>126379426</v>
       </c>
       <c r="B59" t="n">
-        <v>92535</v>
+        <v>79598</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E59" t="n">
-        <v>4364</v>
+        <v>6453</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
@@ -6446,10 +6446,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>718282</v>
+        <v>718364</v>
       </c>
       <c r="R59" t="n">
-        <v>7234434</v>
+        <v>7234409</v>
       </c>
       <c r="S59" t="n">
         <v>10</v>
@@ -6508,7 +6508,7 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>126379472</v>
+        <v>126379466</v>
       </c>
       <c r="B60" t="n">
         <v>78980</v>
@@ -6543,10 +6543,10 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>718308</v>
+        <v>718570</v>
       </c>
       <c r="R60" t="n">
-        <v>7234404</v>
+        <v>7234643</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>
@@ -6605,7 +6605,7 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>126379466</v>
+        <v>126379472</v>
       </c>
       <c r="B61" t="n">
         <v>78980</v>
@@ -6640,10 +6640,10 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>718570</v>
+        <v>718308</v>
       </c>
       <c r="R61" t="n">
-        <v>7234643</v>
+        <v>7234404</v>
       </c>
       <c r="S61" t="n">
         <v>10</v>

--- a/artfynd/A 24579-2025 artfynd.xlsx
+++ b/artfynd/A 24579-2025 artfynd.xlsx
@@ -2824,32 +2824,32 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>126379424</v>
+        <v>126379468</v>
       </c>
       <c r="B23" t="n">
-        <v>91210</v>
+        <v>78980</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>5447</v>
+        <v>6425</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -2859,10 +2859,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>718450</v>
+        <v>718577</v>
       </c>
       <c r="R23" t="n">
-        <v>7234710</v>
+        <v>7234539</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2921,32 +2921,32 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>126379446</v>
+        <v>126379481</v>
       </c>
       <c r="B24" t="n">
-        <v>80111</v>
+        <v>78980</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>6461</v>
+        <v>6425</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Norrlandslav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Nephroma arcticum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(L.) Torss.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -2956,10 +2956,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>718189</v>
+        <v>718217</v>
       </c>
       <c r="R24" t="n">
-        <v>7234350</v>
+        <v>7234406</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3018,7 +3018,7 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>126379468</v>
+        <v>126379478</v>
       </c>
       <c r="B25" t="n">
         <v>78980</v>
@@ -3053,10 +3053,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>718577</v>
+        <v>718319</v>
       </c>
       <c r="R25" t="n">
-        <v>7234539</v>
+        <v>7234335</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3089,6 +3089,11 @@
       <c r="AA25" t="inlineStr">
         <is>
           <t>2025-07-02</t>
+        </is>
+      </c>
+      <c r="AC25" t="inlineStr">
+        <is>
+          <t>Långa bålar</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3115,7 +3120,7 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>126379481</v>
+        <v>126379457</v>
       </c>
       <c r="B26" t="n">
         <v>78980</v>
@@ -3150,10 +3155,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>718217</v>
+        <v>718450</v>
       </c>
       <c r="R26" t="n">
-        <v>7234406</v>
+        <v>7234706</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3212,32 +3217,32 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>126379478</v>
+        <v>126379446</v>
       </c>
       <c r="B27" t="n">
-        <v>78980</v>
+        <v>80111</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>6425</v>
+        <v>6461</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Norrlandslav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma arcticum</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Torss.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3247,10 +3252,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>718319</v>
+        <v>718189</v>
       </c>
       <c r="R27" t="n">
-        <v>7234335</v>
+        <v>7234350</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3283,11 +3288,6 @@
       <c r="AA27" t="inlineStr">
         <is>
           <t>2025-07-02</t>
-        </is>
-      </c>
-      <c r="AC27" t="inlineStr">
-        <is>
-          <t>Långa bålar</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3314,10 +3314,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>126379457</v>
+        <v>126379447</v>
       </c>
       <c r="B28" t="n">
-        <v>78980</v>
+        <v>80083</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3325,21 +3325,21 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3349,10 +3349,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>718450</v>
+        <v>718536</v>
       </c>
       <c r="R28" t="n">
-        <v>7234706</v>
+        <v>7234545</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3411,32 +3411,32 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>126379447</v>
+        <v>126379424</v>
       </c>
       <c r="B29" t="n">
-        <v>80083</v>
+        <v>91210</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>6458</v>
+        <v>5447</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3446,10 +3446,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>718536</v>
+        <v>718450</v>
       </c>
       <c r="R29" t="n">
-        <v>7234545</v>
+        <v>7234710</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -4399,32 +4399,32 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>126379490</v>
+        <v>126379453</v>
       </c>
       <c r="B39" t="n">
-        <v>92535</v>
+        <v>91263</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>4364</v>
+        <v>5432</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
@@ -4434,10 +4434,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>718545</v>
+        <v>718212</v>
       </c>
       <c r="R39" t="n">
-        <v>7234655</v>
+        <v>7234351</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4496,32 +4496,32 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>126379475</v>
+        <v>126379490</v>
       </c>
       <c r="B40" t="n">
-        <v>78980</v>
+        <v>92535</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>6425</v>
+        <v>4364</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
@@ -4531,10 +4531,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>718346</v>
+        <v>718545</v>
       </c>
       <c r="R40" t="n">
-        <v>7234422</v>
+        <v>7234655</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4593,10 +4593,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>126379453</v>
+        <v>126379475</v>
       </c>
       <c r="B41" t="n">
-        <v>91263</v>
+        <v>78980</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4604,21 +4604,21 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
@@ -4628,10 +4628,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>718212</v>
+        <v>718346</v>
       </c>
       <c r="R41" t="n">
-        <v>7234351</v>
+        <v>7234422</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -4889,45 +4889,53 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>126379485</v>
+        <v>126379441</v>
       </c>
       <c r="B44" t="n">
-        <v>78980</v>
+        <v>56849</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>6425</v>
+        <v>100138</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
+      <c r="K44" t="inlineStr"/>
+      <c r="L44" t="inlineStr"/>
+      <c r="M44" t="inlineStr">
+        <is>
+          <t>äldre spillning</t>
+        </is>
+      </c>
+      <c r="N44" t="inlineStr"/>
       <c r="P44" t="inlineStr">
         <is>
           <t>Bergmyran, Vb</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>718173</v>
+        <v>718148</v>
       </c>
       <c r="R44" t="n">
-        <v>7234351</v>
+        <v>7234311</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -4964,7 +4972,7 @@
       </c>
       <c r="AC44" t="inlineStr">
         <is>
-          <t>Fertil</t>
+          <t>Spillning</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -4991,10 +4999,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>126379436</v>
+        <v>126379485</v>
       </c>
       <c r="B45" t="n">
-        <v>57657</v>
+        <v>78980</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5002,42 +5010,34 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
-      <c r="K45" t="inlineStr"/>
-      <c r="L45" t="inlineStr"/>
-      <c r="M45" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N45" t="inlineStr"/>
       <c r="P45" t="inlineStr">
         <is>
           <t>Bergmyran, Vb</t>
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>718009</v>
+        <v>718173</v>
       </c>
       <c r="R45" t="n">
-        <v>7234441</v>
+        <v>7234351</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5074,7 +5074,7 @@
       </c>
       <c r="AC45" t="inlineStr">
         <is>
-          <t>Äldre ringhack</t>
+          <t>Fertil</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5101,32 +5101,32 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>126379441</v>
+        <v>126379436</v>
       </c>
       <c r="B46" t="n">
-        <v>56849</v>
+        <v>57657</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>100138</v>
+        <v>100109</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
@@ -5134,7 +5134,7 @@
       <c r="L46" t="inlineStr"/>
       <c r="M46" t="inlineStr">
         <is>
-          <t>äldre spillning</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="N46" t="inlineStr"/>
@@ -5144,10 +5144,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>718148</v>
+        <v>718009</v>
       </c>
       <c r="R46" t="n">
-        <v>7234311</v>
+        <v>7234441</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5184,7 +5184,7 @@
       </c>
       <c r="AC46" t="inlineStr">
         <is>
-          <t>Spillning</t>
+          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -6314,32 +6314,32 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>126379492</v>
+        <v>126379426</v>
       </c>
       <c r="B58" t="n">
-        <v>92535</v>
+        <v>79598</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E58" t="n">
-        <v>4364</v>
+        <v>6453</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
@@ -6349,10 +6349,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>718282</v>
+        <v>718364</v>
       </c>
       <c r="R58" t="n">
-        <v>7234434</v>
+        <v>7234409</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -6411,32 +6411,32 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>126379426</v>
+        <v>126379492</v>
       </c>
       <c r="B59" t="n">
-        <v>79598</v>
+        <v>92535</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E59" t="n">
-        <v>6453</v>
+        <v>4364</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
@@ -6446,10 +6446,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>718364</v>
+        <v>718282</v>
       </c>
       <c r="R59" t="n">
-        <v>7234409</v>
+        <v>7234434</v>
       </c>
       <c r="S59" t="n">
         <v>10</v>
@@ -6702,10 +6702,10 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>126379459</v>
+        <v>126379442</v>
       </c>
       <c r="B62" t="n">
-        <v>78980</v>
+        <v>57817</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -6713,34 +6713,42 @@
         </is>
       </c>
       <c r="E62" t="n">
-        <v>6425</v>
+        <v>103021</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
+      <c r="K62" t="inlineStr"/>
+      <c r="L62" t="inlineStr"/>
+      <c r="M62" t="inlineStr">
+        <is>
+          <t>upprörd, varnande</t>
+        </is>
+      </c>
+      <c r="N62" t="inlineStr"/>
       <c r="P62" t="inlineStr">
         <is>
           <t>Bergmyran, Vb</t>
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>718274</v>
+        <v>718338</v>
       </c>
       <c r="R62" t="n">
-        <v>7234439</v>
+        <v>7234424</v>
       </c>
       <c r="S62" t="n">
         <v>10</v>
@@ -6799,7 +6807,7 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>126379464</v>
+        <v>126379459</v>
       </c>
       <c r="B63" t="n">
         <v>78980</v>
@@ -6834,10 +6842,10 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>718427</v>
+        <v>718274</v>
       </c>
       <c r="R63" t="n">
-        <v>7234679</v>
+        <v>7234439</v>
       </c>
       <c r="S63" t="n">
         <v>10</v>
@@ -6896,7 +6904,7 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>126379462</v>
+        <v>126379464</v>
       </c>
       <c r="B64" t="n">
         <v>78980</v>
@@ -6931,10 +6939,10 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>718535</v>
+        <v>718427</v>
       </c>
       <c r="R64" t="n">
-        <v>7234587</v>
+        <v>7234679</v>
       </c>
       <c r="S64" t="n">
         <v>10</v>
@@ -6967,11 +6975,6 @@
       <c r="AA64" t="inlineStr">
         <is>
           <t>2025-07-02</t>
-        </is>
-      </c>
-      <c r="AC64" t="inlineStr">
-        <is>
-          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD64" t="b">
@@ -6998,10 +7001,10 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>126379438</v>
+        <v>126379462</v>
       </c>
       <c r="B65" t="n">
-        <v>57657</v>
+        <v>78980</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -7009,42 +7012,34 @@
         </is>
       </c>
       <c r="E65" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
-      <c r="K65" t="inlineStr"/>
-      <c r="L65" t="inlineStr"/>
-      <c r="M65" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N65" t="inlineStr"/>
       <c r="P65" t="inlineStr">
         <is>
           <t>Bergmyran, Vb</t>
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>718061</v>
+        <v>718535</v>
       </c>
       <c r="R65" t="n">
-        <v>7234332</v>
+        <v>7234587</v>
       </c>
       <c r="S65" t="n">
         <v>10</v>
@@ -7071,17 +7066,17 @@
       </c>
       <c r="Y65" t="inlineStr">
         <is>
-          <t>2025-07-01</t>
+          <t>2025-07-02</t>
         </is>
       </c>
       <c r="AA65" t="inlineStr">
         <is>
-          <t>2025-07-01</t>
+          <t>2025-07-02</t>
         </is>
       </c>
       <c r="AC65" t="inlineStr">
         <is>
-          <t>Äldre ringhack</t>
+          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD65" t="b">
@@ -7108,10 +7103,10 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>126379442</v>
+        <v>126379438</v>
       </c>
       <c r="B66" t="n">
-        <v>57817</v>
+        <v>57657</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -7119,21 +7114,21 @@
         </is>
       </c>
       <c r="E66" t="n">
-        <v>103021</v>
+        <v>100109</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I66" t="inlineStr"/>
@@ -7141,7 +7136,7 @@
       <c r="L66" t="inlineStr"/>
       <c r="M66" t="inlineStr">
         <is>
-          <t>upprörd, varnande</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="N66" t="inlineStr"/>
@@ -7151,10 +7146,10 @@
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>718338</v>
+        <v>718061</v>
       </c>
       <c r="R66" t="n">
-        <v>7234424</v>
+        <v>7234332</v>
       </c>
       <c r="S66" t="n">
         <v>10</v>
@@ -7181,12 +7176,17 @@
       </c>
       <c r="Y66" t="inlineStr">
         <is>
-          <t>2025-07-02</t>
+          <t>2025-07-01</t>
         </is>
       </c>
       <c r="AA66" t="inlineStr">
         <is>
-          <t>2025-07-02</t>
+          <t>2025-07-01</t>
+        </is>
+      </c>
+      <c r="AC66" t="inlineStr">
+        <is>
+          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD66" t="b">

--- a/artfynd/A 24579-2025 artfynd.xlsx
+++ b/artfynd/A 24579-2025 artfynd.xlsx
@@ -1699,48 +1699,45 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>126379451</v>
+        <v>126379463</v>
       </c>
       <c r="B12" t="n">
-        <v>79168</v>
+        <v>78980</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>230552</v>
+        <v>6425</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Gropig skägglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Usnea barbata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(L.) Weber ex F.H.Wigg.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
-      <c r="J12" t="inlineStr"/>
-      <c r="K12" t="inlineStr"/>
-      <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
           <t>Bergmyran, Vb</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>717977</v>
+        <v>718526</v>
       </c>
       <c r="R12" t="n">
-        <v>7234425</v>
+        <v>7234595</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1775,18 +1772,12 @@
           <t>2025-07-02</t>
         </is>
       </c>
-      <c r="AC12" t="inlineStr">
-        <is>
-          <t>Måste efterforska</t>
-        </is>
-      </c>
       <c r="AD12" t="b">
         <v>0</v>
       </c>
       <c r="AE12" t="b">
         <v>0</v>
       </c>
-      <c r="AF12" t="inlineStr"/>
       <c r="AG12" t="b">
         <v>0</v>
       </c>
@@ -1805,10 +1796,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>126379463</v>
+        <v>126379430</v>
       </c>
       <c r="B13" t="n">
-        <v>78980</v>
+        <v>57657</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1816,34 +1807,42 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
+      <c r="K13" t="inlineStr"/>
+      <c r="L13" t="inlineStr"/>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
           <t>Bergmyran, Vb</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>718526</v>
+        <v>718154</v>
       </c>
       <c r="R13" t="n">
-        <v>7234595</v>
+        <v>7234509</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1876,6 +1875,11 @@
       <c r="AA13" t="inlineStr">
         <is>
           <t>2025-07-02</t>
+        </is>
+      </c>
+      <c r="AC13" t="inlineStr">
+        <is>
+          <t>Färskt ringhack</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1902,7 +1906,7 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>126379430</v>
+        <v>126379434</v>
       </c>
       <c r="B14" t="n">
         <v>57657</v>
@@ -1945,10 +1949,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>718154</v>
+        <v>718150</v>
       </c>
       <c r="R14" t="n">
-        <v>7234509</v>
+        <v>7234307</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -1985,7 +1989,7 @@
       </c>
       <c r="AC14" t="inlineStr">
         <is>
-          <t>Färskt ringhack</t>
+          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2012,10 +2016,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>126379434</v>
+        <v>126379443</v>
       </c>
       <c r="B15" t="n">
-        <v>57657</v>
+        <v>57817</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2023,21 +2027,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>100109</v>
+        <v>103021</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2045,7 +2049,7 @@
       <c r="L15" t="inlineStr"/>
       <c r="M15" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>upprörd, varnande</t>
         </is>
       </c>
       <c r="N15" t="inlineStr"/>
@@ -2055,10 +2059,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>718150</v>
+        <v>718294</v>
       </c>
       <c r="R15" t="n">
-        <v>7234307</v>
+        <v>7234414</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2091,11 +2095,6 @@
       <c r="AA15" t="inlineStr">
         <is>
           <t>2025-07-02</t>
-        </is>
-      </c>
-      <c r="AC15" t="inlineStr">
-        <is>
-          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2122,42 +2121,37 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>126379443</v>
+        <v>126379451</v>
       </c>
       <c r="B16" t="n">
-        <v>57817</v>
+        <v>79168</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>103021</v>
+        <v>230552</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Gropig skägglav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Usnea barbata</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(L.) Weber ex F.H.Wigg.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
+      <c r="J16" t="inlineStr"/>
       <c r="K16" t="inlineStr"/>
-      <c r="L16" t="inlineStr"/>
-      <c r="M16" t="inlineStr">
-        <is>
-          <t>upprörd, varnande</t>
-        </is>
-      </c>
       <c r="N16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
@@ -2165,10 +2159,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>718294</v>
+        <v>717977</v>
       </c>
       <c r="R16" t="n">
-        <v>7234414</v>
+        <v>7234425</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2203,12 +2197,18 @@
           <t>2025-07-02</t>
         </is>
       </c>
+      <c r="AC16" t="inlineStr">
+        <is>
+          <t>Måste efterforska</t>
+        </is>
+      </c>
       <c r="AD16" t="b">
         <v>0</v>
       </c>
       <c r="AE16" t="b">
         <v>0</v>
       </c>
+      <c r="AF16" t="inlineStr"/>
       <c r="AG16" t="b">
         <v>0</v>
       </c>
@@ -4889,53 +4889,45 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>126379441</v>
+        <v>126379485</v>
       </c>
       <c r="B44" t="n">
-        <v>56849</v>
+        <v>78980</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>100138</v>
+        <v>6425</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
-      <c r="K44" t="inlineStr"/>
-      <c r="L44" t="inlineStr"/>
-      <c r="M44" t="inlineStr">
-        <is>
-          <t>äldre spillning</t>
-        </is>
-      </c>
-      <c r="N44" t="inlineStr"/>
       <c r="P44" t="inlineStr">
         <is>
           <t>Bergmyran, Vb</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>718148</v>
+        <v>718173</v>
       </c>
       <c r="R44" t="n">
-        <v>7234311</v>
+        <v>7234351</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -4972,7 +4964,7 @@
       </c>
       <c r="AC44" t="inlineStr">
         <is>
-          <t>Spillning</t>
+          <t>Fertil</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -4999,10 +4991,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>126379485</v>
+        <v>126379436</v>
       </c>
       <c r="B45" t="n">
-        <v>78980</v>
+        <v>57657</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5010,34 +5002,42 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
+      <c r="K45" t="inlineStr"/>
+      <c r="L45" t="inlineStr"/>
+      <c r="M45" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N45" t="inlineStr"/>
       <c r="P45" t="inlineStr">
         <is>
           <t>Bergmyran, Vb</t>
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>718173</v>
+        <v>718009</v>
       </c>
       <c r="R45" t="n">
-        <v>7234351</v>
+        <v>7234441</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5074,7 +5074,7 @@
       </c>
       <c r="AC45" t="inlineStr">
         <is>
-          <t>Fertil</t>
+          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5101,32 +5101,32 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>126379436</v>
+        <v>126379441</v>
       </c>
       <c r="B46" t="n">
-        <v>57657</v>
+        <v>56849</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>100109</v>
+        <v>100138</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
@@ -5134,7 +5134,7 @@
       <c r="L46" t="inlineStr"/>
       <c r="M46" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>äldre spillning</t>
         </is>
       </c>
       <c r="N46" t="inlineStr"/>
@@ -5144,10 +5144,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>718009</v>
+        <v>718148</v>
       </c>
       <c r="R46" t="n">
-        <v>7234441</v>
+        <v>7234311</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5184,7 +5184,7 @@
       </c>
       <c r="AC46" t="inlineStr">
         <is>
-          <t>Äldre ringhack</t>
+          <t>Spillning</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -6702,10 +6702,10 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>126379442</v>
+        <v>126379459</v>
       </c>
       <c r="B62" t="n">
-        <v>57817</v>
+        <v>78980</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -6713,42 +6713,34 @@
         </is>
       </c>
       <c r="E62" t="n">
-        <v>103021</v>
+        <v>6425</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
-      <c r="K62" t="inlineStr"/>
-      <c r="L62" t="inlineStr"/>
-      <c r="M62" t="inlineStr">
-        <is>
-          <t>upprörd, varnande</t>
-        </is>
-      </c>
-      <c r="N62" t="inlineStr"/>
       <c r="P62" t="inlineStr">
         <is>
           <t>Bergmyran, Vb</t>
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>718338</v>
+        <v>718274</v>
       </c>
       <c r="R62" t="n">
-        <v>7234424</v>
+        <v>7234439</v>
       </c>
       <c r="S62" t="n">
         <v>10</v>
@@ -6807,7 +6799,7 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>126379459</v>
+        <v>126379464</v>
       </c>
       <c r="B63" t="n">
         <v>78980</v>
@@ -6842,10 +6834,10 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>718274</v>
+        <v>718427</v>
       </c>
       <c r="R63" t="n">
-        <v>7234439</v>
+        <v>7234679</v>
       </c>
       <c r="S63" t="n">
         <v>10</v>
@@ -6904,7 +6896,7 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>126379464</v>
+        <v>126379462</v>
       </c>
       <c r="B64" t="n">
         <v>78980</v>
@@ -6939,10 +6931,10 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>718427</v>
+        <v>718535</v>
       </c>
       <c r="R64" t="n">
-        <v>7234679</v>
+        <v>7234587</v>
       </c>
       <c r="S64" t="n">
         <v>10</v>
@@ -6975,6 +6967,11 @@
       <c r="AA64" t="inlineStr">
         <is>
           <t>2025-07-02</t>
+        </is>
+      </c>
+      <c r="AC64" t="inlineStr">
+        <is>
+          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD64" t="b">
@@ -7001,10 +6998,10 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>126379462</v>
+        <v>126379438</v>
       </c>
       <c r="B65" t="n">
-        <v>78980</v>
+        <v>57657</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -7012,34 +7009,42 @@
         </is>
       </c>
       <c r="E65" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
+      <c r="K65" t="inlineStr"/>
+      <c r="L65" t="inlineStr"/>
+      <c r="M65" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N65" t="inlineStr"/>
       <c r="P65" t="inlineStr">
         <is>
           <t>Bergmyran, Vb</t>
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>718535</v>
+        <v>718061</v>
       </c>
       <c r="R65" t="n">
-        <v>7234587</v>
+        <v>7234332</v>
       </c>
       <c r="S65" t="n">
         <v>10</v>
@@ -7066,17 +7071,17 @@
       </c>
       <c r="Y65" t="inlineStr">
         <is>
-          <t>2025-07-02</t>
+          <t>2025-07-01</t>
         </is>
       </c>
       <c r="AA65" t="inlineStr">
         <is>
-          <t>2025-07-02</t>
+          <t>2025-07-01</t>
         </is>
       </c>
       <c r="AC65" t="inlineStr">
         <is>
-          <t>Rikligt</t>
+          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD65" t="b">
@@ -7103,10 +7108,10 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>126379438</v>
+        <v>126379442</v>
       </c>
       <c r="B66" t="n">
-        <v>57657</v>
+        <v>57817</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -7114,21 +7119,21 @@
         </is>
       </c>
       <c r="E66" t="n">
-        <v>100109</v>
+        <v>103021</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I66" t="inlineStr"/>
@@ -7136,7 +7141,7 @@
       <c r="L66" t="inlineStr"/>
       <c r="M66" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>upprörd, varnande</t>
         </is>
       </c>
       <c r="N66" t="inlineStr"/>
@@ -7146,10 +7151,10 @@
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>718061</v>
+        <v>718338</v>
       </c>
       <c r="R66" t="n">
-        <v>7234332</v>
+        <v>7234424</v>
       </c>
       <c r="S66" t="n">
         <v>10</v>
@@ -7176,17 +7181,12 @@
       </c>
       <c r="Y66" t="inlineStr">
         <is>
-          <t>2025-07-01</t>
+          <t>2025-07-02</t>
         </is>
       </c>
       <c r="AA66" t="inlineStr">
         <is>
-          <t>2025-07-01</t>
-        </is>
-      </c>
-      <c r="AC66" t="inlineStr">
-        <is>
-          <t>Äldre ringhack</t>
+          <t>2025-07-02</t>
         </is>
       </c>
       <c r="AD66" t="b">

--- a/artfynd/A 24579-2025 artfynd.xlsx
+++ b/artfynd/A 24579-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>126379461</v>
       </c>
       <c r="B2" t="n">
-        <v>78980</v>
+        <v>79120</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -768,14 +768,18 @@
           <t>Anton Lundberg</t>
         </is>
       </c>
-      <c r="AY2" t="inlineStr"/>
+      <c r="AY2" t="inlineStr">
+        <is>
+          <t>Naturskyddsföreningen i Västerbottens naturvärdesinventeringar 2025</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
         <v>126379432</v>
       </c>
       <c r="B3" t="n">
-        <v>57657</v>
+        <v>57716</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -878,14 +882,18 @@
           <t>Anton Lundberg</t>
         </is>
       </c>
-      <c r="AY3" t="inlineStr"/>
+      <c r="AY3" t="inlineStr">
+        <is>
+          <t>Naturskyddsföreningen i Västerbottens naturvärdesinventeringar 2025</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
         <v>126379431</v>
       </c>
       <c r="B4" t="n">
-        <v>57657</v>
+        <v>57716</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -980,14 +988,18 @@
           <t>Anton Lundberg</t>
         </is>
       </c>
-      <c r="AY4" t="inlineStr"/>
+      <c r="AY4" t="inlineStr">
+        <is>
+          <t>Naturskyddsföreningen i Västerbottens naturvärdesinventeringar 2025</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
         <v>126379440</v>
       </c>
       <c r="B5" t="n">
-        <v>57657</v>
+        <v>57716</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1090,14 +1102,18 @@
           <t>Anton Lundberg</t>
         </is>
       </c>
-      <c r="AY5" t="inlineStr"/>
+      <c r="AY5" t="inlineStr">
+        <is>
+          <t>Naturskyddsföreningen i Västerbottens naturvärdesinventeringar 2025</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
         <v>126379452</v>
       </c>
       <c r="B6" t="n">
-        <v>91263</v>
+        <v>91522</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1187,14 +1203,18 @@
           <t>Anton Lundberg</t>
         </is>
       </c>
-      <c r="AY6" t="inlineStr"/>
+      <c r="AY6" t="inlineStr">
+        <is>
+          <t>Naturskyddsföreningen i Västerbottens naturvärdesinventeringar 2025</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
         <v>126379433</v>
       </c>
       <c r="B7" t="n">
-        <v>57657</v>
+        <v>57716</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1297,14 +1317,18 @@
           <t>Anton Lundberg</t>
         </is>
       </c>
-      <c r="AY7" t="inlineStr"/>
+      <c r="AY7" t="inlineStr">
+        <is>
+          <t>Naturskyddsföreningen i Västerbottens naturvärdesinventeringar 2025</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
         <v>126379488</v>
       </c>
       <c r="B8" t="n">
-        <v>78647</v>
+        <v>78786</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1394,14 +1418,18 @@
           <t>Anton Lundberg</t>
         </is>
       </c>
-      <c r="AY8" t="inlineStr"/>
+      <c r="AY8" t="inlineStr">
+        <is>
+          <t>Naturskyddsföreningen i Västerbottens naturvärdesinventeringar 2025</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
         <v>126379471</v>
       </c>
       <c r="B9" t="n">
-        <v>78980</v>
+        <v>79120</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1496,14 +1524,18 @@
           <t>Anton Lundberg</t>
         </is>
       </c>
-      <c r="AY9" t="inlineStr"/>
+      <c r="AY9" t="inlineStr">
+        <is>
+          <t>Naturskyddsföreningen i Västerbottens naturvärdesinventeringar 2025</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
         <v>126379484</v>
       </c>
       <c r="B10" t="n">
-        <v>78980</v>
+        <v>79120</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1598,14 +1630,18 @@
           <t>Anton Lundberg</t>
         </is>
       </c>
-      <c r="AY10" t="inlineStr"/>
+      <c r="AY10" t="inlineStr">
+        <is>
+          <t>Naturskyddsföreningen i Västerbottens naturvärdesinventeringar 2025</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
         <v>126379425</v>
       </c>
       <c r="B11" t="n">
-        <v>91210</v>
+        <v>91469</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1695,14 +1731,18 @@
           <t>Anton Lundberg</t>
         </is>
       </c>
-      <c r="AY11" t="inlineStr"/>
+      <c r="AY11" t="inlineStr">
+        <is>
+          <t>Naturskyddsföreningen i Västerbottens naturvärdesinventeringar 2025</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
         <v>126379451</v>
       </c>
       <c r="B12" t="n">
-        <v>79168</v>
+        <v>79308</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1801,14 +1841,18 @@
           <t>Anton Lundberg</t>
         </is>
       </c>
-      <c r="AY12" t="inlineStr"/>
+      <c r="AY12" t="inlineStr">
+        <is>
+          <t>Naturskyddsföreningen i Västerbottens naturvärdesinventeringar 2025</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
         <v>126379463</v>
       </c>
       <c r="B13" t="n">
-        <v>78980</v>
+        <v>79120</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1898,14 +1942,18 @@
           <t>Anton Lundberg</t>
         </is>
       </c>
-      <c r="AY13" t="inlineStr"/>
+      <c r="AY13" t="inlineStr">
+        <is>
+          <t>Naturskyddsföreningen i Västerbottens naturvärdesinventeringar 2025</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
         <v>126379430</v>
       </c>
       <c r="B14" t="n">
-        <v>57657</v>
+        <v>57716</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2008,14 +2056,18 @@
           <t>Anton Lundberg</t>
         </is>
       </c>
-      <c r="AY14" t="inlineStr"/>
+      <c r="AY14" t="inlineStr">
+        <is>
+          <t>Naturskyddsföreningen i Västerbottens naturvärdesinventeringar 2025</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
         <v>126379434</v>
       </c>
       <c r="B15" t="n">
-        <v>57657</v>
+        <v>57716</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2118,14 +2170,18 @@
           <t>Anton Lundberg</t>
         </is>
       </c>
-      <c r="AY15" t="inlineStr"/>
+      <c r="AY15" t="inlineStr">
+        <is>
+          <t>Naturskyddsföreningen i Västerbottens naturvärdesinventeringar 2025</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
         <v>126379443</v>
       </c>
       <c r="B16" t="n">
-        <v>57817</v>
+        <v>57876</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2223,14 +2279,18 @@
           <t>Anton Lundberg</t>
         </is>
       </c>
-      <c r="AY16" t="inlineStr"/>
+      <c r="AY16" t="inlineStr">
+        <is>
+          <t>Naturskyddsföreningen i Västerbottens naturvärdesinventeringar 2025</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
         <v>126379487</v>
       </c>
       <c r="B17" t="n">
-        <v>78980</v>
+        <v>79120</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2325,14 +2385,18 @@
           <t>Anton Lundberg</t>
         </is>
       </c>
-      <c r="AY17" t="inlineStr"/>
+      <c r="AY17" t="inlineStr">
+        <is>
+          <t>Naturskyddsföreningen i Västerbottens naturvärdesinventeringar 2025</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
         <v>126379469</v>
       </c>
       <c r="B18" t="n">
-        <v>78980</v>
+        <v>79120</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2422,14 +2486,18 @@
           <t>Anton Lundberg</t>
         </is>
       </c>
-      <c r="AY18" t="inlineStr"/>
+      <c r="AY18" t="inlineStr">
+        <is>
+          <t>Naturskyddsföreningen i Västerbottens naturvärdesinventeringar 2025</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
         <v>126379458</v>
       </c>
       <c r="B19" t="n">
-        <v>78980</v>
+        <v>79120</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2524,14 +2592,18 @@
           <t>Anton Lundberg</t>
         </is>
       </c>
-      <c r="AY19" t="inlineStr"/>
+      <c r="AY19" t="inlineStr">
+        <is>
+          <t>Naturskyddsföreningen i Västerbottens naturvärdesinventeringar 2025</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
         <v>126379428</v>
       </c>
       <c r="B20" t="n">
-        <v>79598</v>
+        <v>79739</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2621,14 +2693,18 @@
           <t>Anton Lundberg</t>
         </is>
       </c>
-      <c r="AY20" t="inlineStr"/>
+      <c r="AY20" t="inlineStr">
+        <is>
+          <t>Naturskyddsföreningen i Västerbottens naturvärdesinventeringar 2025</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
         <v>126379454</v>
       </c>
       <c r="B21" t="n">
-        <v>78980</v>
+        <v>79120</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2723,14 +2799,18 @@
           <t>Anton Lundberg</t>
         </is>
       </c>
-      <c r="AY21" t="inlineStr"/>
+      <c r="AY21" t="inlineStr">
+        <is>
+          <t>Naturskyddsföreningen i Västerbottens naturvärdesinventeringar 2025</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
         <v>126379427</v>
       </c>
       <c r="B22" t="n">
-        <v>79598</v>
+        <v>79739</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2820,14 +2900,18 @@
           <t>Anton Lundberg</t>
         </is>
       </c>
-      <c r="AY22" t="inlineStr"/>
+      <c r="AY22" t="inlineStr">
+        <is>
+          <t>Naturskyddsföreningen i Västerbottens naturvärdesinventeringar 2025</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
         <v>126379424</v>
       </c>
       <c r="B23" t="n">
-        <v>91210</v>
+        <v>91469</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2917,14 +3001,18 @@
           <t>Anton Lundberg</t>
         </is>
       </c>
-      <c r="AY23" t="inlineStr"/>
+      <c r="AY23" t="inlineStr">
+        <is>
+          <t>Naturskyddsföreningen i Västerbottens naturvärdesinventeringar 2025</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
         <v>126379446</v>
       </c>
       <c r="B24" t="n">
-        <v>80111</v>
+        <v>80253</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3014,14 +3102,18 @@
           <t>Anton Lundberg</t>
         </is>
       </c>
-      <c r="AY24" t="inlineStr"/>
+      <c r="AY24" t="inlineStr">
+        <is>
+          <t>Naturskyddsföreningen i Västerbottens naturvärdesinventeringar 2025</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
         <v>126379468</v>
       </c>
       <c r="B25" t="n">
-        <v>78980</v>
+        <v>79120</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3111,14 +3203,18 @@
           <t>Anton Lundberg</t>
         </is>
       </c>
-      <c r="AY25" t="inlineStr"/>
+      <c r="AY25" t="inlineStr">
+        <is>
+          <t>Naturskyddsföreningen i Västerbottens naturvärdesinventeringar 2025</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
         <v>126379481</v>
       </c>
       <c r="B26" t="n">
-        <v>78980</v>
+        <v>79120</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3208,14 +3304,18 @@
           <t>Anton Lundberg</t>
         </is>
       </c>
-      <c r="AY26" t="inlineStr"/>
+      <c r="AY26" t="inlineStr">
+        <is>
+          <t>Naturskyddsföreningen i Västerbottens naturvärdesinventeringar 2025</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
         <v>126379478</v>
       </c>
       <c r="B27" t="n">
-        <v>78980</v>
+        <v>79120</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3310,14 +3410,18 @@
           <t>Anton Lundberg</t>
         </is>
       </c>
-      <c r="AY27" t="inlineStr"/>
+      <c r="AY27" t="inlineStr">
+        <is>
+          <t>Naturskyddsföreningen i Västerbottens naturvärdesinventeringar 2025</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
         <v>126379457</v>
       </c>
       <c r="B28" t="n">
-        <v>78980</v>
+        <v>79120</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3407,14 +3511,18 @@
           <t>Anton Lundberg</t>
         </is>
       </c>
-      <c r="AY28" t="inlineStr"/>
+      <c r="AY28" t="inlineStr">
+        <is>
+          <t>Naturskyddsföreningen i Västerbottens naturvärdesinventeringar 2025</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
         <v>126379447</v>
       </c>
       <c r="B29" t="n">
-        <v>80083</v>
+        <v>80225</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3504,14 +3612,18 @@
           <t>Anton Lundberg</t>
         </is>
       </c>
-      <c r="AY29" t="inlineStr"/>
+      <c r="AY29" t="inlineStr">
+        <is>
+          <t>Naturskyddsföreningen i Västerbottens naturvärdesinventeringar 2025</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
         <v>126379437</v>
       </c>
       <c r="B30" t="n">
-        <v>57657</v>
+        <v>57716</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3614,14 +3726,18 @@
           <t>Anton Lundberg</t>
         </is>
       </c>
-      <c r="AY30" t="inlineStr"/>
+      <c r="AY30" t="inlineStr">
+        <is>
+          <t>Naturskyddsföreningen i Västerbottens naturvärdesinventeringar 2025</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
         <v>126379470</v>
       </c>
       <c r="B31" t="n">
-        <v>78980</v>
+        <v>79120</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3711,14 +3827,18 @@
           <t>Anton Lundberg</t>
         </is>
       </c>
-      <c r="AY31" t="inlineStr"/>
+      <c r="AY31" t="inlineStr">
+        <is>
+          <t>Naturskyddsföreningen i Västerbottens naturvärdesinventeringar 2025</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
         <v>126379491</v>
       </c>
       <c r="B32" t="n">
-        <v>92535</v>
+        <v>92794</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3808,14 +3928,18 @@
           <t>Anton Lundberg</t>
         </is>
       </c>
-      <c r="AY32" t="inlineStr"/>
+      <c r="AY32" t="inlineStr">
+        <is>
+          <t>Naturskyddsföreningen i Västerbottens naturvärdesinventeringar 2025</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
         <v>126379448</v>
       </c>
       <c r="B33" t="n">
-        <v>80119</v>
+        <v>80261</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3905,14 +4029,18 @@
           <t>Anton Lundberg</t>
         </is>
       </c>
-      <c r="AY33" t="inlineStr"/>
+      <c r="AY33" t="inlineStr">
+        <is>
+          <t>Naturskyddsföreningen i Västerbottens naturvärdesinventeringar 2025</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
         <v>126379486</v>
       </c>
       <c r="B34" t="n">
-        <v>78980</v>
+        <v>79120</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4002,14 +4130,18 @@
           <t>Anton Lundberg</t>
         </is>
       </c>
-      <c r="AY34" t="inlineStr"/>
+      <c r="AY34" t="inlineStr">
+        <is>
+          <t>Naturskyddsföreningen i Västerbottens naturvärdesinventeringar 2025</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
         <v>126379467</v>
       </c>
       <c r="B35" t="n">
-        <v>78980</v>
+        <v>79120</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4099,14 +4231,18 @@
           <t>Anton Lundberg</t>
         </is>
       </c>
-      <c r="AY35" t="inlineStr"/>
+      <c r="AY35" t="inlineStr">
+        <is>
+          <t>Naturskyddsföreningen i Västerbottens naturvärdesinventeringar 2025</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
         <v>126379489</v>
       </c>
       <c r="B36" t="n">
-        <v>92535</v>
+        <v>92794</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4196,14 +4332,18 @@
           <t>Anton Lundberg</t>
         </is>
       </c>
-      <c r="AY36" t="inlineStr"/>
+      <c r="AY36" t="inlineStr">
+        <is>
+          <t>Naturskyddsföreningen i Västerbottens naturvärdesinventeringar 2025</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="n">
         <v>126379482</v>
       </c>
       <c r="B37" t="n">
-        <v>78980</v>
+        <v>79120</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4298,14 +4438,18 @@
           <t>Anton Lundberg</t>
         </is>
       </c>
-      <c r="AY37" t="inlineStr"/>
+      <c r="AY37" t="inlineStr">
+        <is>
+          <t>Naturskyddsföreningen i Västerbottens naturvärdesinventeringar 2025</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" t="n">
         <v>126379480</v>
       </c>
       <c r="B38" t="n">
-        <v>78980</v>
+        <v>79120</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4395,14 +4539,18 @@
           <t>Anton Lundberg</t>
         </is>
       </c>
-      <c r="AY38" t="inlineStr"/>
+      <c r="AY38" t="inlineStr">
+        <is>
+          <t>Naturskyddsföreningen i Västerbottens naturvärdesinventeringar 2025</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" t="n">
         <v>126379490</v>
       </c>
       <c r="B39" t="n">
-        <v>92535</v>
+        <v>92794</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4492,14 +4640,18 @@
           <t>Anton Lundberg</t>
         </is>
       </c>
-      <c r="AY39" t="inlineStr"/>
+      <c r="AY39" t="inlineStr">
+        <is>
+          <t>Naturskyddsföreningen i Västerbottens naturvärdesinventeringar 2025</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" t="n">
         <v>126379475</v>
       </c>
       <c r="B40" t="n">
-        <v>78980</v>
+        <v>79120</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4589,14 +4741,18 @@
           <t>Anton Lundberg</t>
         </is>
       </c>
-      <c r="AY40" t="inlineStr"/>
+      <c r="AY40" t="inlineStr">
+        <is>
+          <t>Naturskyddsföreningen i Västerbottens naturvärdesinventeringar 2025</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" t="n">
         <v>126379453</v>
       </c>
       <c r="B41" t="n">
-        <v>91263</v>
+        <v>91522</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4686,14 +4842,18 @@
           <t>Anton Lundberg</t>
         </is>
       </c>
-      <c r="AY41" t="inlineStr"/>
+      <c r="AY41" t="inlineStr">
+        <is>
+          <t>Naturskyddsföreningen i Västerbottens naturvärdesinventeringar 2025</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" t="n">
         <v>126379476</v>
       </c>
       <c r="B42" t="n">
-        <v>78980</v>
+        <v>79120</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -4788,14 +4948,18 @@
           <t>Anton Lundberg</t>
         </is>
       </c>
-      <c r="AY42" t="inlineStr"/>
+      <c r="AY42" t="inlineStr">
+        <is>
+          <t>Naturskyddsföreningen i Västerbottens naturvärdesinventeringar 2025</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" t="n">
         <v>126379460</v>
       </c>
       <c r="B43" t="n">
-        <v>78980</v>
+        <v>79120</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -4885,14 +5049,18 @@
           <t>Anton Lundberg</t>
         </is>
       </c>
-      <c r="AY43" t="inlineStr"/>
+      <c r="AY43" t="inlineStr">
+        <is>
+          <t>Naturskyddsföreningen i Västerbottens naturvärdesinventeringar 2025</t>
+        </is>
+      </c>
     </row>
     <row r="44">
       <c r="A44" t="n">
         <v>126379441</v>
       </c>
       <c r="B44" t="n">
-        <v>56849</v>
+        <v>56907</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -4995,14 +5163,18 @@
           <t>Anton Lundberg</t>
         </is>
       </c>
-      <c r="AY44" t="inlineStr"/>
+      <c r="AY44" t="inlineStr">
+        <is>
+          <t>Naturskyddsföreningen i Västerbottens naturvärdesinventeringar 2025</t>
+        </is>
+      </c>
     </row>
     <row r="45">
       <c r="A45" t="n">
         <v>126379485</v>
       </c>
       <c r="B45" t="n">
-        <v>78980</v>
+        <v>79120</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5097,14 +5269,18 @@
           <t>Anton Lundberg</t>
         </is>
       </c>
-      <c r="AY45" t="inlineStr"/>
+      <c r="AY45" t="inlineStr">
+        <is>
+          <t>Naturskyddsföreningen i Västerbottens naturvärdesinventeringar 2025</t>
+        </is>
+      </c>
     </row>
     <row r="46">
       <c r="A46" t="n">
         <v>126379436</v>
       </c>
       <c r="B46" t="n">
-        <v>57657</v>
+        <v>57716</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5207,14 +5383,18 @@
           <t>Anton Lundberg</t>
         </is>
       </c>
-      <c r="AY46" t="inlineStr"/>
+      <c r="AY46" t="inlineStr">
+        <is>
+          <t>Naturskyddsföreningen i Västerbottens naturvärdesinventeringar 2025</t>
+        </is>
+      </c>
     </row>
     <row r="47">
       <c r="A47" t="n">
         <v>126379423</v>
       </c>
       <c r="B47" t="n">
-        <v>79012</v>
+        <v>79152</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5304,14 +5484,18 @@
           <t>Anton Lundberg</t>
         </is>
       </c>
-      <c r="AY47" t="inlineStr"/>
+      <c r="AY47" t="inlineStr">
+        <is>
+          <t>Naturskyddsföreningen i Västerbottens naturvärdesinventeringar 2025</t>
+        </is>
+      </c>
     </row>
     <row r="48">
       <c r="A48" t="n">
         <v>126379465</v>
       </c>
       <c r="B48" t="n">
-        <v>78980</v>
+        <v>79120</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5406,14 +5590,18 @@
           <t>Anton Lundberg</t>
         </is>
       </c>
-      <c r="AY48" t="inlineStr"/>
+      <c r="AY48" t="inlineStr">
+        <is>
+          <t>Naturskyddsföreningen i Västerbottens naturvärdesinventeringar 2025</t>
+        </is>
+      </c>
     </row>
     <row r="49">
       <c r="A49" t="n">
         <v>126379483</v>
       </c>
       <c r="B49" t="n">
-        <v>78980</v>
+        <v>79120</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5508,14 +5696,18 @@
           <t>Anton Lundberg</t>
         </is>
       </c>
-      <c r="AY49" t="inlineStr"/>
+      <c r="AY49" t="inlineStr">
+        <is>
+          <t>Naturskyddsföreningen i Västerbottens naturvärdesinventeringar 2025</t>
+        </is>
+      </c>
     </row>
     <row r="50">
       <c r="A50" t="n">
         <v>126379479</v>
       </c>
       <c r="B50" t="n">
-        <v>78980</v>
+        <v>79120</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5605,14 +5797,18 @@
           <t>Anton Lundberg</t>
         </is>
       </c>
-      <c r="AY50" t="inlineStr"/>
+      <c r="AY50" t="inlineStr">
+        <is>
+          <t>Naturskyddsföreningen i Västerbottens naturvärdesinventeringar 2025</t>
+        </is>
+      </c>
     </row>
     <row r="51">
       <c r="A51" t="n">
         <v>126379444</v>
       </c>
       <c r="B51" t="n">
-        <v>98382</v>
+        <v>98653</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -5702,14 +5898,18 @@
           <t>Anton Lundberg</t>
         </is>
       </c>
-      <c r="AY51" t="inlineStr"/>
+      <c r="AY51" t="inlineStr">
+        <is>
+          <t>Naturskyddsföreningen i Västerbottens naturvärdesinventeringar 2025</t>
+        </is>
+      </c>
     </row>
     <row r="52">
       <c r="A52" t="n">
         <v>126379439</v>
       </c>
       <c r="B52" t="n">
-        <v>57657</v>
+        <v>57716</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -5812,14 +6012,18 @@
           <t>Anton Lundberg</t>
         </is>
       </c>
-      <c r="AY52" t="inlineStr"/>
+      <c r="AY52" t="inlineStr">
+        <is>
+          <t>Naturskyddsföreningen i Västerbottens naturvärdesinventeringar 2025</t>
+        </is>
+      </c>
     </row>
     <row r="53">
       <c r="A53" t="n">
         <v>126379435</v>
       </c>
       <c r="B53" t="n">
-        <v>57657</v>
+        <v>57716</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -5922,14 +6126,18 @@
           <t>Anton Lundberg</t>
         </is>
       </c>
-      <c r="AY53" t="inlineStr"/>
+      <c r="AY53" t="inlineStr">
+        <is>
+          <t>Naturskyddsföreningen i Västerbottens naturvärdesinventeringar 2025</t>
+        </is>
+      </c>
     </row>
     <row r="54">
       <c r="A54" t="n">
         <v>126379474</v>
       </c>
       <c r="B54" t="n">
-        <v>78980</v>
+        <v>79120</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6019,14 +6227,18 @@
           <t>Anton Lundberg</t>
         </is>
       </c>
-      <c r="AY54" t="inlineStr"/>
+      <c r="AY54" t="inlineStr">
+        <is>
+          <t>Naturskyddsföreningen i Västerbottens naturvärdesinventeringar 2025</t>
+        </is>
+      </c>
     </row>
     <row r="55">
       <c r="A55" t="n">
         <v>126379455</v>
       </c>
       <c r="B55" t="n">
-        <v>78980</v>
+        <v>79120</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6116,14 +6328,18 @@
           <t>Anton Lundberg</t>
         </is>
       </c>
-      <c r="AY55" t="inlineStr"/>
+      <c r="AY55" t="inlineStr">
+        <is>
+          <t>Naturskyddsföreningen i Västerbottens naturvärdesinventeringar 2025</t>
+        </is>
+      </c>
     </row>
     <row r="56">
       <c r="A56" t="n">
         <v>126379456</v>
       </c>
       <c r="B56" t="n">
-        <v>78980</v>
+        <v>79120</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6213,14 +6429,18 @@
           <t>Anton Lundberg</t>
         </is>
       </c>
-      <c r="AY56" t="inlineStr"/>
+      <c r="AY56" t="inlineStr">
+        <is>
+          <t>Naturskyddsföreningen i Västerbottens naturvärdesinventeringar 2025</t>
+        </is>
+      </c>
     </row>
     <row r="57">
       <c r="A57" t="n">
         <v>126379473</v>
       </c>
       <c r="B57" t="n">
-        <v>78980</v>
+        <v>79120</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6310,14 +6530,18 @@
           <t>Anton Lundberg</t>
         </is>
       </c>
-      <c r="AY57" t="inlineStr"/>
+      <c r="AY57" t="inlineStr">
+        <is>
+          <t>Naturskyddsföreningen i Västerbottens naturvärdesinventeringar 2025</t>
+        </is>
+      </c>
     </row>
     <row r="58">
       <c r="A58" t="n">
         <v>126379492</v>
       </c>
       <c r="B58" t="n">
-        <v>92535</v>
+        <v>92794</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -6407,14 +6631,18 @@
           <t>Anton Lundberg</t>
         </is>
       </c>
-      <c r="AY58" t="inlineStr"/>
+      <c r="AY58" t="inlineStr">
+        <is>
+          <t>Naturskyddsföreningen i Västerbottens naturvärdesinventeringar 2025</t>
+        </is>
+      </c>
     </row>
     <row r="59">
       <c r="A59" t="n">
         <v>126379426</v>
       </c>
       <c r="B59" t="n">
-        <v>79598</v>
+        <v>79739</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -6504,14 +6732,18 @@
           <t>Anton Lundberg</t>
         </is>
       </c>
-      <c r="AY59" t="inlineStr"/>
+      <c r="AY59" t="inlineStr">
+        <is>
+          <t>Naturskyddsföreningen i Västerbottens naturvärdesinventeringar 2025</t>
+        </is>
+      </c>
     </row>
     <row r="60">
       <c r="A60" t="n">
         <v>126379466</v>
       </c>
       <c r="B60" t="n">
-        <v>78980</v>
+        <v>79120</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -6601,14 +6833,18 @@
           <t>Anton Lundberg</t>
         </is>
       </c>
-      <c r="AY60" t="inlineStr"/>
+      <c r="AY60" t="inlineStr">
+        <is>
+          <t>Naturskyddsföreningen i Västerbottens naturvärdesinventeringar 2025</t>
+        </is>
+      </c>
     </row>
     <row r="61">
       <c r="A61" t="n">
         <v>126379472</v>
       </c>
       <c r="B61" t="n">
-        <v>78980</v>
+        <v>79120</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -6698,14 +6934,18 @@
           <t>Anton Lundberg</t>
         </is>
       </c>
-      <c r="AY61" t="inlineStr"/>
+      <c r="AY61" t="inlineStr">
+        <is>
+          <t>Naturskyddsföreningen i Västerbottens naturvärdesinventeringar 2025</t>
+        </is>
+      </c>
     </row>
     <row r="62">
       <c r="A62" t="n">
         <v>126379442</v>
       </c>
       <c r="B62" t="n">
-        <v>57817</v>
+        <v>57876</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -6803,14 +7043,18 @@
           <t>Anton Lundberg</t>
         </is>
       </c>
-      <c r="AY62" t="inlineStr"/>
+      <c r="AY62" t="inlineStr">
+        <is>
+          <t>Naturskyddsföreningen i Västerbottens naturvärdesinventeringar 2025</t>
+        </is>
+      </c>
     </row>
     <row r="63">
       <c r="A63" t="n">
         <v>126379459</v>
       </c>
       <c r="B63" t="n">
-        <v>78980</v>
+        <v>79120</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -6900,14 +7144,18 @@
           <t>Anton Lundberg</t>
         </is>
       </c>
-      <c r="AY63" t="inlineStr"/>
+      <c r="AY63" t="inlineStr">
+        <is>
+          <t>Naturskyddsföreningen i Västerbottens naturvärdesinventeringar 2025</t>
+        </is>
+      </c>
     </row>
     <row r="64">
       <c r="A64" t="n">
         <v>126379464</v>
       </c>
       <c r="B64" t="n">
-        <v>78980</v>
+        <v>79120</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -6997,14 +7245,18 @@
           <t>Anton Lundberg</t>
         </is>
       </c>
-      <c r="AY64" t="inlineStr"/>
+      <c r="AY64" t="inlineStr">
+        <is>
+          <t>Naturskyddsföreningen i Västerbottens naturvärdesinventeringar 2025</t>
+        </is>
+      </c>
     </row>
     <row r="65">
       <c r="A65" t="n">
         <v>126379462</v>
       </c>
       <c r="B65" t="n">
-        <v>78980</v>
+        <v>79120</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -7099,14 +7351,18 @@
           <t>Anton Lundberg</t>
         </is>
       </c>
-      <c r="AY65" t="inlineStr"/>
+      <c r="AY65" t="inlineStr">
+        <is>
+          <t>Naturskyddsföreningen i Västerbottens naturvärdesinventeringar 2025</t>
+        </is>
+      </c>
     </row>
     <row r="66">
       <c r="A66" t="n">
         <v>126379438</v>
       </c>
       <c r="B66" t="n">
-        <v>57657</v>
+        <v>57716</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -7209,7 +7465,11 @@
           <t>Anton Lundberg</t>
         </is>
       </c>
-      <c r="AY66" t="inlineStr"/>
+      <c r="AY66" t="inlineStr">
+        <is>
+          <t>Naturskyddsföreningen i Västerbottens naturvärdesinventeringar 2025</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 24579-2025 artfynd.xlsx
+++ b/artfynd/A 24579-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>126379461</v>
       </c>
       <c r="B2" t="n">
-        <v>79120</v>
+        <v>79124</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -779,7 +779,7 @@
         <v>126379432</v>
       </c>
       <c r="B3" t="n">
-        <v>57716</v>
+        <v>57720</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -893,7 +893,7 @@
         <v>126379431</v>
       </c>
       <c r="B4" t="n">
-        <v>57716</v>
+        <v>57720</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -999,7 +999,7 @@
         <v>126379440</v>
       </c>
       <c r="B5" t="n">
-        <v>57716</v>
+        <v>57720</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1113,7 +1113,7 @@
         <v>126379452</v>
       </c>
       <c r="B6" t="n">
-        <v>91522</v>
+        <v>91526</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1214,7 +1214,7 @@
         <v>126379433</v>
       </c>
       <c r="B7" t="n">
-        <v>57716</v>
+        <v>57720</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1328,7 +1328,7 @@
         <v>126379488</v>
       </c>
       <c r="B8" t="n">
-        <v>78786</v>
+        <v>78790</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1429,7 +1429,7 @@
         <v>126379471</v>
       </c>
       <c r="B9" t="n">
-        <v>79120</v>
+        <v>79124</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1535,7 +1535,7 @@
         <v>126379484</v>
       </c>
       <c r="B10" t="n">
-        <v>79120</v>
+        <v>79124</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1641,7 +1641,7 @@
         <v>126379425</v>
       </c>
       <c r="B11" t="n">
-        <v>91469</v>
+        <v>91473</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1742,7 +1742,7 @@
         <v>126379451</v>
       </c>
       <c r="B12" t="n">
-        <v>79308</v>
+        <v>79312</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1852,7 +1852,7 @@
         <v>126379463</v>
       </c>
       <c r="B13" t="n">
-        <v>79120</v>
+        <v>79124</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1953,7 +1953,7 @@
         <v>126379430</v>
       </c>
       <c r="B14" t="n">
-        <v>57716</v>
+        <v>57720</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2067,7 +2067,7 @@
         <v>126379434</v>
       </c>
       <c r="B15" t="n">
-        <v>57716</v>
+        <v>57720</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2181,7 +2181,7 @@
         <v>126379443</v>
       </c>
       <c r="B16" t="n">
-        <v>57876</v>
+        <v>57880</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2290,7 +2290,7 @@
         <v>126379487</v>
       </c>
       <c r="B17" t="n">
-        <v>79120</v>
+        <v>79124</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2396,7 +2396,7 @@
         <v>126379469</v>
       </c>
       <c r="B18" t="n">
-        <v>79120</v>
+        <v>79124</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2497,7 +2497,7 @@
         <v>126379458</v>
       </c>
       <c r="B19" t="n">
-        <v>79120</v>
+        <v>79124</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2603,7 +2603,7 @@
         <v>126379428</v>
       </c>
       <c r="B20" t="n">
-        <v>79739</v>
+        <v>79743</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2704,7 +2704,7 @@
         <v>126379454</v>
       </c>
       <c r="B21" t="n">
-        <v>79120</v>
+        <v>79124</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2810,7 +2810,7 @@
         <v>126379427</v>
       </c>
       <c r="B22" t="n">
-        <v>79739</v>
+        <v>79743</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2911,7 +2911,7 @@
         <v>126379424</v>
       </c>
       <c r="B23" t="n">
-        <v>91469</v>
+        <v>91473</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3012,7 +3012,7 @@
         <v>126379446</v>
       </c>
       <c r="B24" t="n">
-        <v>80253</v>
+        <v>80257</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3113,7 +3113,7 @@
         <v>126379468</v>
       </c>
       <c r="B25" t="n">
-        <v>79120</v>
+        <v>79124</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3214,7 +3214,7 @@
         <v>126379481</v>
       </c>
       <c r="B26" t="n">
-        <v>79120</v>
+        <v>79124</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3315,7 +3315,7 @@
         <v>126379478</v>
       </c>
       <c r="B27" t="n">
-        <v>79120</v>
+        <v>79124</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3421,7 +3421,7 @@
         <v>126379457</v>
       </c>
       <c r="B28" t="n">
-        <v>79120</v>
+        <v>79124</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3522,7 +3522,7 @@
         <v>126379447</v>
       </c>
       <c r="B29" t="n">
-        <v>80225</v>
+        <v>80229</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3623,7 +3623,7 @@
         <v>126379437</v>
       </c>
       <c r="B30" t="n">
-        <v>57716</v>
+        <v>57720</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3737,7 +3737,7 @@
         <v>126379470</v>
       </c>
       <c r="B31" t="n">
-        <v>79120</v>
+        <v>79124</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3838,7 +3838,7 @@
         <v>126379491</v>
       </c>
       <c r="B32" t="n">
-        <v>92794</v>
+        <v>92798</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3939,7 +3939,7 @@
         <v>126379448</v>
       </c>
       <c r="B33" t="n">
-        <v>80261</v>
+        <v>80265</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4040,7 +4040,7 @@
         <v>126379486</v>
       </c>
       <c r="B34" t="n">
-        <v>79120</v>
+        <v>79124</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4141,7 +4141,7 @@
         <v>126379467</v>
       </c>
       <c r="B35" t="n">
-        <v>79120</v>
+        <v>79124</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4242,7 +4242,7 @@
         <v>126379489</v>
       </c>
       <c r="B36" t="n">
-        <v>92794</v>
+        <v>92798</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4343,7 +4343,7 @@
         <v>126379482</v>
       </c>
       <c r="B37" t="n">
-        <v>79120</v>
+        <v>79124</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4449,7 +4449,7 @@
         <v>126379480</v>
       </c>
       <c r="B38" t="n">
-        <v>79120</v>
+        <v>79124</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4550,7 +4550,7 @@
         <v>126379490</v>
       </c>
       <c r="B39" t="n">
-        <v>92794</v>
+        <v>92798</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4651,7 +4651,7 @@
         <v>126379475</v>
       </c>
       <c r="B40" t="n">
-        <v>79120</v>
+        <v>79124</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4752,7 +4752,7 @@
         <v>126379453</v>
       </c>
       <c r="B41" t="n">
-        <v>91522</v>
+        <v>91526</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4853,7 +4853,7 @@
         <v>126379476</v>
       </c>
       <c r="B42" t="n">
-        <v>79120</v>
+        <v>79124</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -4959,7 +4959,7 @@
         <v>126379460</v>
       </c>
       <c r="B43" t="n">
-        <v>79120</v>
+        <v>79124</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5060,7 +5060,7 @@
         <v>126379441</v>
       </c>
       <c r="B44" t="n">
-        <v>56907</v>
+        <v>56910</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5174,7 +5174,7 @@
         <v>126379485</v>
       </c>
       <c r="B45" t="n">
-        <v>79120</v>
+        <v>79124</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5280,7 +5280,7 @@
         <v>126379436</v>
       </c>
       <c r="B46" t="n">
-        <v>57716</v>
+        <v>57720</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5394,7 +5394,7 @@
         <v>126379423</v>
       </c>
       <c r="B47" t="n">
-        <v>79152</v>
+        <v>79156</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5495,7 +5495,7 @@
         <v>126379465</v>
       </c>
       <c r="B48" t="n">
-        <v>79120</v>
+        <v>79124</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5601,7 +5601,7 @@
         <v>126379483</v>
       </c>
       <c r="B49" t="n">
-        <v>79120</v>
+        <v>79124</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5707,7 +5707,7 @@
         <v>126379479</v>
       </c>
       <c r="B50" t="n">
-        <v>79120</v>
+        <v>79124</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5808,7 +5808,7 @@
         <v>126379444</v>
       </c>
       <c r="B51" t="n">
-        <v>98653</v>
+        <v>98657</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -5909,7 +5909,7 @@
         <v>126379439</v>
       </c>
       <c r="B52" t="n">
-        <v>57716</v>
+        <v>57720</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -6023,7 +6023,7 @@
         <v>126379435</v>
       </c>
       <c r="B53" t="n">
-        <v>57716</v>
+        <v>57720</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6137,7 +6137,7 @@
         <v>126379474</v>
       </c>
       <c r="B54" t="n">
-        <v>79120</v>
+        <v>79124</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6238,7 +6238,7 @@
         <v>126379455</v>
       </c>
       <c r="B55" t="n">
-        <v>79120</v>
+        <v>79124</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6339,7 +6339,7 @@
         <v>126379456</v>
       </c>
       <c r="B56" t="n">
-        <v>79120</v>
+        <v>79124</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6440,7 +6440,7 @@
         <v>126379473</v>
       </c>
       <c r="B57" t="n">
-        <v>79120</v>
+        <v>79124</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6541,7 +6541,7 @@
         <v>126379492</v>
       </c>
       <c r="B58" t="n">
-        <v>92794</v>
+        <v>92798</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -6642,7 +6642,7 @@
         <v>126379426</v>
       </c>
       <c r="B59" t="n">
-        <v>79739</v>
+        <v>79743</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -6743,7 +6743,7 @@
         <v>126379466</v>
       </c>
       <c r="B60" t="n">
-        <v>79120</v>
+        <v>79124</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -6844,7 +6844,7 @@
         <v>126379472</v>
       </c>
       <c r="B61" t="n">
-        <v>79120</v>
+        <v>79124</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -6945,7 +6945,7 @@
         <v>126379442</v>
       </c>
       <c r="B62" t="n">
-        <v>57876</v>
+        <v>57880</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -7054,7 +7054,7 @@
         <v>126379459</v>
       </c>
       <c r="B63" t="n">
-        <v>79120</v>
+        <v>79124</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -7155,7 +7155,7 @@
         <v>126379464</v>
       </c>
       <c r="B64" t="n">
-        <v>79120</v>
+        <v>79124</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -7256,7 +7256,7 @@
         <v>126379462</v>
       </c>
       <c r="B65" t="n">
-        <v>79120</v>
+        <v>79124</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -7362,7 +7362,7 @@
         <v>126379438</v>
       </c>
       <c r="B66" t="n">
-        <v>57716</v>
+        <v>57720</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>

--- a/artfynd/A 24579-2025 artfynd.xlsx
+++ b/artfynd/A 24579-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>126379461</v>
       </c>
       <c r="B2" t="n">
-        <v>79124</v>
+        <v>79029</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -779,7 +779,7 @@
         <v>126379432</v>
       </c>
       <c r="B3" t="n">
-        <v>57720</v>
+        <v>57723</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -893,7 +893,7 @@
         <v>126379431</v>
       </c>
       <c r="B4" t="n">
-        <v>57720</v>
+        <v>57723</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -999,7 +999,7 @@
         <v>126379440</v>
       </c>
       <c r="B5" t="n">
-        <v>57720</v>
+        <v>57723</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1113,7 +1113,7 @@
         <v>126379452</v>
       </c>
       <c r="B6" t="n">
-        <v>91526</v>
+        <v>91531</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1214,7 +1214,7 @@
         <v>126379433</v>
       </c>
       <c r="B7" t="n">
-        <v>57720</v>
+        <v>57723</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1328,7 +1328,7 @@
         <v>126379488</v>
       </c>
       <c r="B8" t="n">
-        <v>78790</v>
+        <v>78695</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1429,7 +1429,7 @@
         <v>126379471</v>
       </c>
       <c r="B9" t="n">
-        <v>79124</v>
+        <v>79029</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1535,7 +1535,7 @@
         <v>126379484</v>
       </c>
       <c r="B10" t="n">
-        <v>79124</v>
+        <v>79029</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1641,7 +1641,7 @@
         <v>126379425</v>
       </c>
       <c r="B11" t="n">
-        <v>91473</v>
+        <v>91478</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1742,7 +1742,7 @@
         <v>126379451</v>
       </c>
       <c r="B12" t="n">
-        <v>79312</v>
+        <v>79217</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1852,7 +1852,7 @@
         <v>126379463</v>
       </c>
       <c r="B13" t="n">
-        <v>79124</v>
+        <v>79029</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1953,7 +1953,7 @@
         <v>126379430</v>
       </c>
       <c r="B14" t="n">
-        <v>57720</v>
+        <v>57723</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2067,7 +2067,7 @@
         <v>126379434</v>
       </c>
       <c r="B15" t="n">
-        <v>57720</v>
+        <v>57723</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2181,7 +2181,7 @@
         <v>126379443</v>
       </c>
       <c r="B16" t="n">
-        <v>57880</v>
+        <v>57883</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2290,7 +2290,7 @@
         <v>126379487</v>
       </c>
       <c r="B17" t="n">
-        <v>79124</v>
+        <v>79029</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2396,7 +2396,7 @@
         <v>126379469</v>
       </c>
       <c r="B18" t="n">
-        <v>79124</v>
+        <v>79029</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2497,7 +2497,7 @@
         <v>126379458</v>
       </c>
       <c r="B19" t="n">
-        <v>79124</v>
+        <v>79029</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2603,7 +2603,7 @@
         <v>126379428</v>
       </c>
       <c r="B20" t="n">
-        <v>79743</v>
+        <v>79648</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2704,7 +2704,7 @@
         <v>126379454</v>
       </c>
       <c r="B21" t="n">
-        <v>79124</v>
+        <v>79029</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2810,7 +2810,7 @@
         <v>126379427</v>
       </c>
       <c r="B22" t="n">
-        <v>79743</v>
+        <v>79648</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2911,7 +2911,7 @@
         <v>126379424</v>
       </c>
       <c r="B23" t="n">
-        <v>91473</v>
+        <v>91478</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3012,7 +3012,7 @@
         <v>126379446</v>
       </c>
       <c r="B24" t="n">
-        <v>80257</v>
+        <v>80162</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3113,7 +3113,7 @@
         <v>126379468</v>
       </c>
       <c r="B25" t="n">
-        <v>79124</v>
+        <v>79029</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3214,7 +3214,7 @@
         <v>126379481</v>
       </c>
       <c r="B26" t="n">
-        <v>79124</v>
+        <v>79029</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3315,7 +3315,7 @@
         <v>126379478</v>
       </c>
       <c r="B27" t="n">
-        <v>79124</v>
+        <v>79029</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3421,7 +3421,7 @@
         <v>126379457</v>
       </c>
       <c r="B28" t="n">
-        <v>79124</v>
+        <v>79029</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3522,7 +3522,7 @@
         <v>126379447</v>
       </c>
       <c r="B29" t="n">
-        <v>80229</v>
+        <v>80134</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3623,7 +3623,7 @@
         <v>126379437</v>
       </c>
       <c r="B30" t="n">
-        <v>57720</v>
+        <v>57723</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3737,7 +3737,7 @@
         <v>126379470</v>
       </c>
       <c r="B31" t="n">
-        <v>79124</v>
+        <v>79029</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3838,7 +3838,7 @@
         <v>126379491</v>
       </c>
       <c r="B32" t="n">
-        <v>92798</v>
+        <v>92803</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3939,7 +3939,7 @@
         <v>126379448</v>
       </c>
       <c r="B33" t="n">
-        <v>80265</v>
+        <v>80170</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4040,7 +4040,7 @@
         <v>126379486</v>
       </c>
       <c r="B34" t="n">
-        <v>79124</v>
+        <v>79029</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4141,7 +4141,7 @@
         <v>126379467</v>
       </c>
       <c r="B35" t="n">
-        <v>79124</v>
+        <v>79029</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4242,7 +4242,7 @@
         <v>126379489</v>
       </c>
       <c r="B36" t="n">
-        <v>92798</v>
+        <v>92803</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4343,7 +4343,7 @@
         <v>126379482</v>
       </c>
       <c r="B37" t="n">
-        <v>79124</v>
+        <v>79029</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4449,7 +4449,7 @@
         <v>126379480</v>
       </c>
       <c r="B38" t="n">
-        <v>79124</v>
+        <v>79029</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4550,7 +4550,7 @@
         <v>126379490</v>
       </c>
       <c r="B39" t="n">
-        <v>92798</v>
+        <v>92803</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4651,7 +4651,7 @@
         <v>126379475</v>
       </c>
       <c r="B40" t="n">
-        <v>79124</v>
+        <v>79029</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4752,7 +4752,7 @@
         <v>126379453</v>
       </c>
       <c r="B41" t="n">
-        <v>91526</v>
+        <v>91531</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4853,7 +4853,7 @@
         <v>126379476</v>
       </c>
       <c r="B42" t="n">
-        <v>79124</v>
+        <v>79029</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -4959,7 +4959,7 @@
         <v>126379460</v>
       </c>
       <c r="B43" t="n">
-        <v>79124</v>
+        <v>79029</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5060,7 +5060,7 @@
         <v>126379441</v>
       </c>
       <c r="B44" t="n">
-        <v>56910</v>
+        <v>56913</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5174,7 +5174,7 @@
         <v>126379485</v>
       </c>
       <c r="B45" t="n">
-        <v>79124</v>
+        <v>79029</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5280,7 +5280,7 @@
         <v>126379436</v>
       </c>
       <c r="B46" t="n">
-        <v>57720</v>
+        <v>57723</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5394,7 +5394,7 @@
         <v>126379423</v>
       </c>
       <c r="B47" t="n">
-        <v>79156</v>
+        <v>79061</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5495,7 +5495,7 @@
         <v>126379465</v>
       </c>
       <c r="B48" t="n">
-        <v>79124</v>
+        <v>79029</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5601,7 +5601,7 @@
         <v>126379483</v>
       </c>
       <c r="B49" t="n">
-        <v>79124</v>
+        <v>79029</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5707,7 +5707,7 @@
         <v>126379479</v>
       </c>
       <c r="B50" t="n">
-        <v>79124</v>
+        <v>79029</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5808,7 +5808,7 @@
         <v>126379444</v>
       </c>
       <c r="B51" t="n">
-        <v>98657</v>
+        <v>98664</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -5909,7 +5909,7 @@
         <v>126379439</v>
       </c>
       <c r="B52" t="n">
-        <v>57720</v>
+        <v>57723</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -6023,7 +6023,7 @@
         <v>126379435</v>
       </c>
       <c r="B53" t="n">
-        <v>57720</v>
+        <v>57723</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6137,7 +6137,7 @@
         <v>126379474</v>
       </c>
       <c r="B54" t="n">
-        <v>79124</v>
+        <v>79029</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6238,7 +6238,7 @@
         <v>126379455</v>
       </c>
       <c r="B55" t="n">
-        <v>79124</v>
+        <v>79029</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6339,7 +6339,7 @@
         <v>126379456</v>
       </c>
       <c r="B56" t="n">
-        <v>79124</v>
+        <v>79029</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6440,7 +6440,7 @@
         <v>126379473</v>
       </c>
       <c r="B57" t="n">
-        <v>79124</v>
+        <v>79029</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6541,7 +6541,7 @@
         <v>126379492</v>
       </c>
       <c r="B58" t="n">
-        <v>92798</v>
+        <v>92803</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -6642,7 +6642,7 @@
         <v>126379426</v>
       </c>
       <c r="B59" t="n">
-        <v>79743</v>
+        <v>79648</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -6743,7 +6743,7 @@
         <v>126379466</v>
       </c>
       <c r="B60" t="n">
-        <v>79124</v>
+        <v>79029</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -6844,7 +6844,7 @@
         <v>126379472</v>
       </c>
       <c r="B61" t="n">
-        <v>79124</v>
+        <v>79029</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -6945,7 +6945,7 @@
         <v>126379442</v>
       </c>
       <c r="B62" t="n">
-        <v>57880</v>
+        <v>57883</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -7054,7 +7054,7 @@
         <v>126379459</v>
       </c>
       <c r="B63" t="n">
-        <v>79124</v>
+        <v>79029</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -7155,7 +7155,7 @@
         <v>126379464</v>
       </c>
       <c r="B64" t="n">
-        <v>79124</v>
+        <v>79029</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -7256,7 +7256,7 @@
         <v>126379462</v>
       </c>
       <c r="B65" t="n">
-        <v>79124</v>
+        <v>79029</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -7362,7 +7362,7 @@
         <v>126379438</v>
       </c>
       <c r="B66" t="n">
-        <v>57720</v>
+        <v>57723</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>

--- a/artfynd/A 24579-2025 artfynd.xlsx
+++ b/artfynd/A 24579-2025 artfynd.xlsx
@@ -1113,7 +1113,7 @@
         <v>126379452</v>
       </c>
       <c r="B6" t="n">
-        <v>91538</v>
+        <v>91541</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1641,7 +1641,7 @@
         <v>126379425</v>
       </c>
       <c r="B11" t="n">
-        <v>91485</v>
+        <v>91488</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -2911,7 +2911,7 @@
         <v>126379424</v>
       </c>
       <c r="B23" t="n">
-        <v>91485</v>
+        <v>91488</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3838,7 +3838,7 @@
         <v>126379491</v>
       </c>
       <c r="B32" t="n">
-        <v>92811</v>
+        <v>92816</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4242,7 +4242,7 @@
         <v>126379489</v>
       </c>
       <c r="B36" t="n">
-        <v>92811</v>
+        <v>92816</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4550,7 +4550,7 @@
         <v>126379490</v>
       </c>
       <c r="B39" t="n">
-        <v>92811</v>
+        <v>92816</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4752,7 +4752,7 @@
         <v>126379453</v>
       </c>
       <c r="B41" t="n">
-        <v>91538</v>
+        <v>91541</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -5808,7 +5808,7 @@
         <v>126379444</v>
       </c>
       <c r="B51" t="n">
-        <v>98672</v>
+        <v>98677</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -6541,7 +6541,7 @@
         <v>126379492</v>
       </c>
       <c r="B58" t="n">
-        <v>92811</v>
+        <v>92816</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>

--- a/artfynd/A 24579-2025 artfynd.xlsx
+++ b/artfynd/A 24579-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>126379461</v>
       </c>
       <c r="B2" t="n">
-        <v>79034</v>
+        <v>79035</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -1113,7 +1113,7 @@
         <v>126379452</v>
       </c>
       <c r="B6" t="n">
-        <v>91541</v>
+        <v>91544</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1328,7 +1328,7 @@
         <v>126379488</v>
       </c>
       <c r="B8" t="n">
-        <v>78700</v>
+        <v>78701</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1429,7 +1429,7 @@
         <v>126379471</v>
       </c>
       <c r="B9" t="n">
-        <v>79034</v>
+        <v>79035</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1535,7 +1535,7 @@
         <v>126379484</v>
       </c>
       <c r="B10" t="n">
-        <v>79034</v>
+        <v>79035</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1641,7 +1641,7 @@
         <v>126379425</v>
       </c>
       <c r="B11" t="n">
-        <v>91488</v>
+        <v>91491</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1742,7 +1742,7 @@
         <v>126379451</v>
       </c>
       <c r="B12" t="n">
-        <v>79222</v>
+        <v>79223</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1852,7 +1852,7 @@
         <v>126379463</v>
       </c>
       <c r="B13" t="n">
-        <v>79034</v>
+        <v>79035</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2290,7 +2290,7 @@
         <v>126379487</v>
       </c>
       <c r="B17" t="n">
-        <v>79034</v>
+        <v>79035</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2396,7 +2396,7 @@
         <v>126379469</v>
       </c>
       <c r="B18" t="n">
-        <v>79034</v>
+        <v>79035</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2497,7 +2497,7 @@
         <v>126379458</v>
       </c>
       <c r="B19" t="n">
-        <v>79034</v>
+        <v>79035</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2603,7 +2603,7 @@
         <v>126379428</v>
       </c>
       <c r="B20" t="n">
-        <v>79653</v>
+        <v>79654</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2704,7 +2704,7 @@
         <v>126379454</v>
       </c>
       <c r="B21" t="n">
-        <v>79034</v>
+        <v>79035</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2810,7 +2810,7 @@
         <v>126379427</v>
       </c>
       <c r="B22" t="n">
-        <v>79653</v>
+        <v>79654</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2911,7 +2911,7 @@
         <v>126379424</v>
       </c>
       <c r="B23" t="n">
-        <v>91488</v>
+        <v>91491</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3012,7 +3012,7 @@
         <v>126379446</v>
       </c>
       <c r="B24" t="n">
-        <v>80167</v>
+        <v>80168</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3113,7 +3113,7 @@
         <v>126379468</v>
       </c>
       <c r="B25" t="n">
-        <v>79034</v>
+        <v>79035</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3214,7 +3214,7 @@
         <v>126379481</v>
       </c>
       <c r="B26" t="n">
-        <v>79034</v>
+        <v>79035</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3315,7 +3315,7 @@
         <v>126379478</v>
       </c>
       <c r="B27" t="n">
-        <v>79034</v>
+        <v>79035</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3421,7 +3421,7 @@
         <v>126379457</v>
       </c>
       <c r="B28" t="n">
-        <v>79034</v>
+        <v>79035</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3522,7 +3522,7 @@
         <v>126379447</v>
       </c>
       <c r="B29" t="n">
-        <v>80139</v>
+        <v>80140</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3737,7 +3737,7 @@
         <v>126379470</v>
       </c>
       <c r="B31" t="n">
-        <v>79034</v>
+        <v>79035</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3838,7 +3838,7 @@
         <v>126379491</v>
       </c>
       <c r="B32" t="n">
-        <v>92816</v>
+        <v>92819</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3939,7 +3939,7 @@
         <v>126379448</v>
       </c>
       <c r="B33" t="n">
-        <v>80175</v>
+        <v>80176</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4040,7 +4040,7 @@
         <v>126379486</v>
       </c>
       <c r="B34" t="n">
-        <v>79034</v>
+        <v>79035</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4141,7 +4141,7 @@
         <v>126379467</v>
       </c>
       <c r="B35" t="n">
-        <v>79034</v>
+        <v>79035</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4242,7 +4242,7 @@
         <v>126379489</v>
       </c>
       <c r="B36" t="n">
-        <v>92816</v>
+        <v>92819</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4343,7 +4343,7 @@
         <v>126379482</v>
       </c>
       <c r="B37" t="n">
-        <v>79034</v>
+        <v>79035</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4449,7 +4449,7 @@
         <v>126379480</v>
       </c>
       <c r="B38" t="n">
-        <v>79034</v>
+        <v>79035</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4550,7 +4550,7 @@
         <v>126379490</v>
       </c>
       <c r="B39" t="n">
-        <v>92816</v>
+        <v>92819</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4651,7 +4651,7 @@
         <v>126379475</v>
       </c>
       <c r="B40" t="n">
-        <v>79034</v>
+        <v>79035</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4752,7 +4752,7 @@
         <v>126379453</v>
       </c>
       <c r="B41" t="n">
-        <v>91541</v>
+        <v>91544</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4853,7 +4853,7 @@
         <v>126379476</v>
       </c>
       <c r="B42" t="n">
-        <v>79034</v>
+        <v>79035</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -4959,7 +4959,7 @@
         <v>126379460</v>
       </c>
       <c r="B43" t="n">
-        <v>79034</v>
+        <v>79035</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5174,7 +5174,7 @@
         <v>126379485</v>
       </c>
       <c r="B45" t="n">
-        <v>79034</v>
+        <v>79035</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5394,7 +5394,7 @@
         <v>126379423</v>
       </c>
       <c r="B47" t="n">
-        <v>79066</v>
+        <v>79067</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5495,7 +5495,7 @@
         <v>126379465</v>
       </c>
       <c r="B48" t="n">
-        <v>79034</v>
+        <v>79035</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5601,7 +5601,7 @@
         <v>126379483</v>
       </c>
       <c r="B49" t="n">
-        <v>79034</v>
+        <v>79035</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5707,7 +5707,7 @@
         <v>126379479</v>
       </c>
       <c r="B50" t="n">
-        <v>79034</v>
+        <v>79035</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5808,7 +5808,7 @@
         <v>126379444</v>
       </c>
       <c r="B51" t="n">
-        <v>98677</v>
+        <v>98680</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -6137,7 +6137,7 @@
         <v>126379474</v>
       </c>
       <c r="B54" t="n">
-        <v>79034</v>
+        <v>79035</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6238,7 +6238,7 @@
         <v>126379455</v>
       </c>
       <c r="B55" t="n">
-        <v>79034</v>
+        <v>79035</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6339,7 +6339,7 @@
         <v>126379456</v>
       </c>
       <c r="B56" t="n">
-        <v>79034</v>
+        <v>79035</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6440,7 +6440,7 @@
         <v>126379473</v>
       </c>
       <c r="B57" t="n">
-        <v>79034</v>
+        <v>79035</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6541,7 +6541,7 @@
         <v>126379492</v>
       </c>
       <c r="B58" t="n">
-        <v>92816</v>
+        <v>92819</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -6642,7 +6642,7 @@
         <v>126379426</v>
       </c>
       <c r="B59" t="n">
-        <v>79653</v>
+        <v>79654</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -6743,7 +6743,7 @@
         <v>126379466</v>
       </c>
       <c r="B60" t="n">
-        <v>79034</v>
+        <v>79035</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -6844,7 +6844,7 @@
         <v>126379472</v>
       </c>
       <c r="B61" t="n">
-        <v>79034</v>
+        <v>79035</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -7054,7 +7054,7 @@
         <v>126379459</v>
       </c>
       <c r="B63" t="n">
-        <v>79034</v>
+        <v>79035</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -7155,7 +7155,7 @@
         <v>126379464</v>
       </c>
       <c r="B64" t="n">
-        <v>79034</v>
+        <v>79035</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -7256,7 +7256,7 @@
         <v>126379462</v>
       </c>
       <c r="B65" t="n">
-        <v>79034</v>
+        <v>79035</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>

--- a/artfynd/A 24579-2025 artfynd.xlsx
+++ b/artfynd/A 24579-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>126379461</v>
       </c>
       <c r="B2" t="n">
-        <v>79035</v>
+        <v>79039</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -779,7 +779,7 @@
         <v>126379432</v>
       </c>
       <c r="B3" t="n">
-        <v>57723</v>
+        <v>57725</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -893,7 +893,7 @@
         <v>126379431</v>
       </c>
       <c r="B4" t="n">
-        <v>57723</v>
+        <v>57725</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -999,7 +999,7 @@
         <v>126379440</v>
       </c>
       <c r="B5" t="n">
-        <v>57723</v>
+        <v>57725</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1113,7 +1113,7 @@
         <v>126379452</v>
       </c>
       <c r="B6" t="n">
-        <v>91544</v>
+        <v>91551</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1214,7 +1214,7 @@
         <v>126379433</v>
       </c>
       <c r="B7" t="n">
-        <v>57723</v>
+        <v>57725</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1328,7 +1328,7 @@
         <v>126379488</v>
       </c>
       <c r="B8" t="n">
-        <v>78701</v>
+        <v>78705</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1429,7 +1429,7 @@
         <v>126379471</v>
       </c>
       <c r="B9" t="n">
-        <v>79035</v>
+        <v>79039</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1535,7 +1535,7 @@
         <v>126379484</v>
       </c>
       <c r="B10" t="n">
-        <v>79035</v>
+        <v>79039</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1641,7 +1641,7 @@
         <v>126379425</v>
       </c>
       <c r="B11" t="n">
-        <v>91491</v>
+        <v>91497</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1742,7 +1742,7 @@
         <v>126379451</v>
       </c>
       <c r="B12" t="n">
-        <v>79223</v>
+        <v>79227</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1852,7 +1852,7 @@
         <v>126379463</v>
       </c>
       <c r="B13" t="n">
-        <v>79035</v>
+        <v>79039</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1953,7 +1953,7 @@
         <v>126379430</v>
       </c>
       <c r="B14" t="n">
-        <v>57723</v>
+        <v>57725</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2067,7 +2067,7 @@
         <v>126379434</v>
       </c>
       <c r="B15" t="n">
-        <v>57723</v>
+        <v>57725</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2181,7 +2181,7 @@
         <v>126379443</v>
       </c>
       <c r="B16" t="n">
-        <v>57883</v>
+        <v>57885</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2290,7 +2290,7 @@
         <v>126379487</v>
       </c>
       <c r="B17" t="n">
-        <v>79035</v>
+        <v>79039</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2396,7 +2396,7 @@
         <v>126379469</v>
       </c>
       <c r="B18" t="n">
-        <v>79035</v>
+        <v>79039</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2497,7 +2497,7 @@
         <v>126379458</v>
       </c>
       <c r="B19" t="n">
-        <v>79035</v>
+        <v>79039</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2603,7 +2603,7 @@
         <v>126379428</v>
       </c>
       <c r="B20" t="n">
-        <v>79654</v>
+        <v>79658</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2704,7 +2704,7 @@
         <v>126379454</v>
       </c>
       <c r="B21" t="n">
-        <v>79035</v>
+        <v>79039</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2810,7 +2810,7 @@
         <v>126379427</v>
       </c>
       <c r="B22" t="n">
-        <v>79654</v>
+        <v>79658</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2911,7 +2911,7 @@
         <v>126379424</v>
       </c>
       <c r="B23" t="n">
-        <v>91491</v>
+        <v>91497</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3012,7 +3012,7 @@
         <v>126379446</v>
       </c>
       <c r="B24" t="n">
-        <v>80168</v>
+        <v>80172</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3113,7 +3113,7 @@
         <v>126379468</v>
       </c>
       <c r="B25" t="n">
-        <v>79035</v>
+        <v>79039</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3214,7 +3214,7 @@
         <v>126379481</v>
       </c>
       <c r="B26" t="n">
-        <v>79035</v>
+        <v>79039</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3315,7 +3315,7 @@
         <v>126379478</v>
       </c>
       <c r="B27" t="n">
-        <v>79035</v>
+        <v>79039</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3421,7 +3421,7 @@
         <v>126379457</v>
       </c>
       <c r="B28" t="n">
-        <v>79035</v>
+        <v>79039</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3522,7 +3522,7 @@
         <v>126379447</v>
       </c>
       <c r="B29" t="n">
-        <v>80140</v>
+        <v>80144</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3623,7 +3623,7 @@
         <v>126379437</v>
       </c>
       <c r="B30" t="n">
-        <v>57723</v>
+        <v>57725</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3737,7 +3737,7 @@
         <v>126379470</v>
       </c>
       <c r="B31" t="n">
-        <v>79035</v>
+        <v>79039</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3838,7 +3838,7 @@
         <v>126379491</v>
       </c>
       <c r="B32" t="n">
-        <v>92819</v>
+        <v>92826</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3939,7 +3939,7 @@
         <v>126379448</v>
       </c>
       <c r="B33" t="n">
-        <v>80176</v>
+        <v>80180</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4040,7 +4040,7 @@
         <v>126379486</v>
       </c>
       <c r="B34" t="n">
-        <v>79035</v>
+        <v>79039</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4141,7 +4141,7 @@
         <v>126379467</v>
       </c>
       <c r="B35" t="n">
-        <v>79035</v>
+        <v>79039</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4242,7 +4242,7 @@
         <v>126379489</v>
       </c>
       <c r="B36" t="n">
-        <v>92819</v>
+        <v>92826</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4343,7 +4343,7 @@
         <v>126379482</v>
       </c>
       <c r="B37" t="n">
-        <v>79035</v>
+        <v>79039</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4449,7 +4449,7 @@
         <v>126379480</v>
       </c>
       <c r="B38" t="n">
-        <v>79035</v>
+        <v>79039</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4550,7 +4550,7 @@
         <v>126379490</v>
       </c>
       <c r="B39" t="n">
-        <v>92819</v>
+        <v>92826</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4651,7 +4651,7 @@
         <v>126379475</v>
       </c>
       <c r="B40" t="n">
-        <v>79035</v>
+        <v>79039</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4752,7 +4752,7 @@
         <v>126379453</v>
       </c>
       <c r="B41" t="n">
-        <v>91544</v>
+        <v>91551</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4853,7 +4853,7 @@
         <v>126379476</v>
       </c>
       <c r="B42" t="n">
-        <v>79035</v>
+        <v>79039</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -4959,7 +4959,7 @@
         <v>126379460</v>
       </c>
       <c r="B43" t="n">
-        <v>79035</v>
+        <v>79039</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5060,7 +5060,7 @@
         <v>126379441</v>
       </c>
       <c r="B44" t="n">
-        <v>56913</v>
+        <v>56915</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5174,7 +5174,7 @@
         <v>126379485</v>
       </c>
       <c r="B45" t="n">
-        <v>79035</v>
+        <v>79039</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5280,7 +5280,7 @@
         <v>126379436</v>
       </c>
       <c r="B46" t="n">
-        <v>57723</v>
+        <v>57725</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5394,7 +5394,7 @@
         <v>126379423</v>
       </c>
       <c r="B47" t="n">
-        <v>79067</v>
+        <v>79071</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5495,7 +5495,7 @@
         <v>126379465</v>
       </c>
       <c r="B48" t="n">
-        <v>79035</v>
+        <v>79039</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5601,7 +5601,7 @@
         <v>126379483</v>
       </c>
       <c r="B49" t="n">
-        <v>79035</v>
+        <v>79039</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5707,7 +5707,7 @@
         <v>126379479</v>
       </c>
       <c r="B50" t="n">
-        <v>79035</v>
+        <v>79039</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5808,7 +5808,7 @@
         <v>126379444</v>
       </c>
       <c r="B51" t="n">
-        <v>98680</v>
+        <v>98690</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -5909,7 +5909,7 @@
         <v>126379439</v>
       </c>
       <c r="B52" t="n">
-        <v>57723</v>
+        <v>57725</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -6023,7 +6023,7 @@
         <v>126379435</v>
       </c>
       <c r="B53" t="n">
-        <v>57723</v>
+        <v>57725</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6137,7 +6137,7 @@
         <v>126379474</v>
       </c>
       <c r="B54" t="n">
-        <v>79035</v>
+        <v>79039</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6238,7 +6238,7 @@
         <v>126379455</v>
       </c>
       <c r="B55" t="n">
-        <v>79035</v>
+        <v>79039</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6339,7 +6339,7 @@
         <v>126379456</v>
       </c>
       <c r="B56" t="n">
-        <v>79035</v>
+        <v>79039</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6440,7 +6440,7 @@
         <v>126379473</v>
       </c>
       <c r="B57" t="n">
-        <v>79035</v>
+        <v>79039</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6541,7 +6541,7 @@
         <v>126379492</v>
       </c>
       <c r="B58" t="n">
-        <v>92819</v>
+        <v>92826</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -6642,7 +6642,7 @@
         <v>126379426</v>
       </c>
       <c r="B59" t="n">
-        <v>79654</v>
+        <v>79658</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -6743,7 +6743,7 @@
         <v>126379466</v>
       </c>
       <c r="B60" t="n">
-        <v>79035</v>
+        <v>79039</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -6844,7 +6844,7 @@
         <v>126379472</v>
       </c>
       <c r="B61" t="n">
-        <v>79035</v>
+        <v>79039</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -6945,7 +6945,7 @@
         <v>126379442</v>
       </c>
       <c r="B62" t="n">
-        <v>57883</v>
+        <v>57885</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -7054,7 +7054,7 @@
         <v>126379459</v>
       </c>
       <c r="B63" t="n">
-        <v>79035</v>
+        <v>79039</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -7155,7 +7155,7 @@
         <v>126379464</v>
       </c>
       <c r="B64" t="n">
-        <v>79035</v>
+        <v>79039</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -7256,7 +7256,7 @@
         <v>126379462</v>
       </c>
       <c r="B65" t="n">
-        <v>79035</v>
+        <v>79039</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -7362,7 +7362,7 @@
         <v>126379438</v>
       </c>
       <c r="B66" t="n">
-        <v>57723</v>
+        <v>57725</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>

--- a/artfynd/A 24579-2025 artfynd.xlsx
+++ b/artfynd/A 24579-2025 artfynd.xlsx
@@ -1113,7 +1113,7 @@
         <v>126379452</v>
       </c>
       <c r="B6" t="n">
-        <v>91551</v>
+        <v>91558</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1641,7 +1641,7 @@
         <v>126379425</v>
       </c>
       <c r="B11" t="n">
-        <v>91497</v>
+        <v>91504</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -2911,7 +2911,7 @@
         <v>126379424</v>
       </c>
       <c r="B23" t="n">
-        <v>91497</v>
+        <v>91504</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3838,7 +3838,7 @@
         <v>126379491</v>
       </c>
       <c r="B32" t="n">
-        <v>92826</v>
+        <v>92833</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4242,7 +4242,7 @@
         <v>126379489</v>
       </c>
       <c r="B36" t="n">
-        <v>92826</v>
+        <v>92833</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4550,7 +4550,7 @@
         <v>126379490</v>
       </c>
       <c r="B39" t="n">
-        <v>92826</v>
+        <v>92833</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4752,7 +4752,7 @@
         <v>126379453</v>
       </c>
       <c r="B41" t="n">
-        <v>91551</v>
+        <v>91558</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -5808,7 +5808,7 @@
         <v>126379444</v>
       </c>
       <c r="B51" t="n">
-        <v>98690</v>
+        <v>98697</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -6541,7 +6541,7 @@
         <v>126379492</v>
       </c>
       <c r="B58" t="n">
-        <v>92826</v>
+        <v>92833</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>

--- a/artfynd/A 24579-2025 artfynd.xlsx
+++ b/artfynd/A 24579-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>126379461</v>
       </c>
       <c r="B2" t="n">
-        <v>79039</v>
+        <v>79041</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -779,7 +779,7 @@
         <v>126379432</v>
       </c>
       <c r="B3" t="n">
-        <v>57725</v>
+        <v>57727</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -893,7 +893,7 @@
         <v>126379431</v>
       </c>
       <c r="B4" t="n">
-        <v>57725</v>
+        <v>57727</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -999,7 +999,7 @@
         <v>126379440</v>
       </c>
       <c r="B5" t="n">
-        <v>57725</v>
+        <v>57727</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1113,7 +1113,7 @@
         <v>126379452</v>
       </c>
       <c r="B6" t="n">
-        <v>91558</v>
+        <v>91560</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1214,7 +1214,7 @@
         <v>126379433</v>
       </c>
       <c r="B7" t="n">
-        <v>57725</v>
+        <v>57727</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1328,7 +1328,7 @@
         <v>126379488</v>
       </c>
       <c r="B8" t="n">
-        <v>78705</v>
+        <v>78707</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1429,7 +1429,7 @@
         <v>126379471</v>
       </c>
       <c r="B9" t="n">
-        <v>79039</v>
+        <v>79041</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1535,7 +1535,7 @@
         <v>126379484</v>
       </c>
       <c r="B10" t="n">
-        <v>79039</v>
+        <v>79041</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1641,7 +1641,7 @@
         <v>126379425</v>
       </c>
       <c r="B11" t="n">
-        <v>91504</v>
+        <v>91506</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1742,7 +1742,7 @@
         <v>126379451</v>
       </c>
       <c r="B12" t="n">
-        <v>79227</v>
+        <v>79229</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1852,7 +1852,7 @@
         <v>126379463</v>
       </c>
       <c r="B13" t="n">
-        <v>79039</v>
+        <v>79041</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1953,7 +1953,7 @@
         <v>126379430</v>
       </c>
       <c r="B14" t="n">
-        <v>57725</v>
+        <v>57727</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2067,7 +2067,7 @@
         <v>126379434</v>
       </c>
       <c r="B15" t="n">
-        <v>57725</v>
+        <v>57727</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2181,7 +2181,7 @@
         <v>126379443</v>
       </c>
       <c r="B16" t="n">
-        <v>57885</v>
+        <v>57887</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2290,7 +2290,7 @@
         <v>126379487</v>
       </c>
       <c r="B17" t="n">
-        <v>79039</v>
+        <v>79041</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2396,7 +2396,7 @@
         <v>126379469</v>
       </c>
       <c r="B18" t="n">
-        <v>79039</v>
+        <v>79041</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2497,7 +2497,7 @@
         <v>126379458</v>
       </c>
       <c r="B19" t="n">
-        <v>79039</v>
+        <v>79041</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2603,7 +2603,7 @@
         <v>126379428</v>
       </c>
       <c r="B20" t="n">
-        <v>79658</v>
+        <v>79660</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2704,7 +2704,7 @@
         <v>126379454</v>
       </c>
       <c r="B21" t="n">
-        <v>79039</v>
+        <v>79041</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2810,7 +2810,7 @@
         <v>126379427</v>
       </c>
       <c r="B22" t="n">
-        <v>79658</v>
+        <v>79660</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2911,7 +2911,7 @@
         <v>126379424</v>
       </c>
       <c r="B23" t="n">
-        <v>91504</v>
+        <v>91506</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3012,7 +3012,7 @@
         <v>126379446</v>
       </c>
       <c r="B24" t="n">
-        <v>80172</v>
+        <v>80174</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3113,7 +3113,7 @@
         <v>126379468</v>
       </c>
       <c r="B25" t="n">
-        <v>79039</v>
+        <v>79041</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3214,7 +3214,7 @@
         <v>126379481</v>
       </c>
       <c r="B26" t="n">
-        <v>79039</v>
+        <v>79041</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3315,7 +3315,7 @@
         <v>126379478</v>
       </c>
       <c r="B27" t="n">
-        <v>79039</v>
+        <v>79041</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3421,7 +3421,7 @@
         <v>126379457</v>
       </c>
       <c r="B28" t="n">
-        <v>79039</v>
+        <v>79041</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3522,7 +3522,7 @@
         <v>126379447</v>
       </c>
       <c r="B29" t="n">
-        <v>80144</v>
+        <v>80146</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3623,7 +3623,7 @@
         <v>126379437</v>
       </c>
       <c r="B30" t="n">
-        <v>57725</v>
+        <v>57727</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3737,7 +3737,7 @@
         <v>126379470</v>
       </c>
       <c r="B31" t="n">
-        <v>79039</v>
+        <v>79041</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3838,7 +3838,7 @@
         <v>126379491</v>
       </c>
       <c r="B32" t="n">
-        <v>92833</v>
+        <v>92835</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3939,7 +3939,7 @@
         <v>126379448</v>
       </c>
       <c r="B33" t="n">
-        <v>80180</v>
+        <v>80182</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4040,7 +4040,7 @@
         <v>126379486</v>
       </c>
       <c r="B34" t="n">
-        <v>79039</v>
+        <v>79041</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4141,7 +4141,7 @@
         <v>126379467</v>
       </c>
       <c r="B35" t="n">
-        <v>79039</v>
+        <v>79041</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4242,7 +4242,7 @@
         <v>126379489</v>
       </c>
       <c r="B36" t="n">
-        <v>92833</v>
+        <v>92835</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4343,7 +4343,7 @@
         <v>126379482</v>
       </c>
       <c r="B37" t="n">
-        <v>79039</v>
+        <v>79041</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4449,7 +4449,7 @@
         <v>126379480</v>
       </c>
       <c r="B38" t="n">
-        <v>79039</v>
+        <v>79041</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4550,7 +4550,7 @@
         <v>126379490</v>
       </c>
       <c r="B39" t="n">
-        <v>92833</v>
+        <v>92835</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4651,7 +4651,7 @@
         <v>126379475</v>
       </c>
       <c r="B40" t="n">
-        <v>79039</v>
+        <v>79041</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4752,7 +4752,7 @@
         <v>126379453</v>
       </c>
       <c r="B41" t="n">
-        <v>91558</v>
+        <v>91560</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4853,7 +4853,7 @@
         <v>126379476</v>
       </c>
       <c r="B42" t="n">
-        <v>79039</v>
+        <v>79041</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -4959,7 +4959,7 @@
         <v>126379460</v>
       </c>
       <c r="B43" t="n">
-        <v>79039</v>
+        <v>79041</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5060,7 +5060,7 @@
         <v>126379441</v>
       </c>
       <c r="B44" t="n">
-        <v>56915</v>
+        <v>56917</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5174,7 +5174,7 @@
         <v>126379485</v>
       </c>
       <c r="B45" t="n">
-        <v>79039</v>
+        <v>79041</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5280,7 +5280,7 @@
         <v>126379436</v>
       </c>
       <c r="B46" t="n">
-        <v>57725</v>
+        <v>57727</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5394,7 +5394,7 @@
         <v>126379423</v>
       </c>
       <c r="B47" t="n">
-        <v>79071</v>
+        <v>79073</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5495,7 +5495,7 @@
         <v>126379465</v>
       </c>
       <c r="B48" t="n">
-        <v>79039</v>
+        <v>79041</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5601,7 +5601,7 @@
         <v>126379483</v>
       </c>
       <c r="B49" t="n">
-        <v>79039</v>
+        <v>79041</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5707,7 +5707,7 @@
         <v>126379479</v>
       </c>
       <c r="B50" t="n">
-        <v>79039</v>
+        <v>79041</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5808,7 +5808,7 @@
         <v>126379444</v>
       </c>
       <c r="B51" t="n">
-        <v>98697</v>
+        <v>98699</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -5909,7 +5909,7 @@
         <v>126379439</v>
       </c>
       <c r="B52" t="n">
-        <v>57725</v>
+        <v>57727</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -6023,7 +6023,7 @@
         <v>126379435</v>
       </c>
       <c r="B53" t="n">
-        <v>57725</v>
+        <v>57727</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6137,7 +6137,7 @@
         <v>126379474</v>
       </c>
       <c r="B54" t="n">
-        <v>79039</v>
+        <v>79041</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6238,7 +6238,7 @@
         <v>126379455</v>
       </c>
       <c r="B55" t="n">
-        <v>79039</v>
+        <v>79041</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6339,7 +6339,7 @@
         <v>126379456</v>
       </c>
       <c r="B56" t="n">
-        <v>79039</v>
+        <v>79041</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6440,7 +6440,7 @@
         <v>126379473</v>
       </c>
       <c r="B57" t="n">
-        <v>79039</v>
+        <v>79041</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6541,7 +6541,7 @@
         <v>126379492</v>
       </c>
       <c r="B58" t="n">
-        <v>92833</v>
+        <v>92835</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -6642,7 +6642,7 @@
         <v>126379426</v>
       </c>
       <c r="B59" t="n">
-        <v>79658</v>
+        <v>79660</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -6743,7 +6743,7 @@
         <v>126379466</v>
       </c>
       <c r="B60" t="n">
-        <v>79039</v>
+        <v>79041</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -6844,7 +6844,7 @@
         <v>126379472</v>
       </c>
       <c r="B61" t="n">
-        <v>79039</v>
+        <v>79041</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -6945,7 +6945,7 @@
         <v>126379442</v>
       </c>
       <c r="B62" t="n">
-        <v>57885</v>
+        <v>57887</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -7054,7 +7054,7 @@
         <v>126379459</v>
       </c>
       <c r="B63" t="n">
-        <v>79039</v>
+        <v>79041</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -7155,7 +7155,7 @@
         <v>126379464</v>
       </c>
       <c r="B64" t="n">
-        <v>79039</v>
+        <v>79041</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -7256,7 +7256,7 @@
         <v>126379462</v>
       </c>
       <c r="B65" t="n">
-        <v>79039</v>
+        <v>79041</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -7362,7 +7362,7 @@
         <v>126379438</v>
       </c>
       <c r="B66" t="n">
-        <v>57725</v>
+        <v>57727</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>

--- a/artfynd/A 24579-2025 artfynd.xlsx
+++ b/artfynd/A 24579-2025 artfynd.xlsx
@@ -1113,7 +1113,7 @@
         <v>126379452</v>
       </c>
       <c r="B6" t="n">
-        <v>91560</v>
+        <v>91558</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1641,7 +1641,7 @@
         <v>126379425</v>
       </c>
       <c r="B11" t="n">
-        <v>91506</v>
+        <v>91504</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -2911,7 +2911,7 @@
         <v>126379424</v>
       </c>
       <c r="B23" t="n">
-        <v>91506</v>
+        <v>91504</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3838,7 +3838,7 @@
         <v>126379491</v>
       </c>
       <c r="B32" t="n">
-        <v>92835</v>
+        <v>92821</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4242,7 +4242,7 @@
         <v>126379489</v>
       </c>
       <c r="B36" t="n">
-        <v>92835</v>
+        <v>92821</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4550,7 +4550,7 @@
         <v>126379490</v>
       </c>
       <c r="B39" t="n">
-        <v>92835</v>
+        <v>92821</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4752,7 +4752,7 @@
         <v>126379453</v>
       </c>
       <c r="B41" t="n">
-        <v>91560</v>
+        <v>91558</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -5808,7 +5808,7 @@
         <v>126379444</v>
       </c>
       <c r="B51" t="n">
-        <v>98699</v>
+        <v>98725</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -6541,7 +6541,7 @@
         <v>126379492</v>
       </c>
       <c r="B58" t="n">
-        <v>92835</v>
+        <v>92821</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>

--- a/artfynd/A 24579-2025 artfynd.xlsx
+++ b/artfynd/A 24579-2025 artfynd.xlsx
@@ -1113,7 +1113,7 @@
         <v>126379452</v>
       </c>
       <c r="B6" t="n">
-        <v>91558</v>
+        <v>91560</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1130,14 +1130,10 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
-        </is>
-      </c>
-      <c r="H6" t="inlineStr">
-        <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr"/>
       <c r="I6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
@@ -3838,7 +3834,7 @@
         <v>126379491</v>
       </c>
       <c r="B32" t="n">
-        <v>92821</v>
+        <v>92822</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4242,7 +4238,7 @@
         <v>126379489</v>
       </c>
       <c r="B36" t="n">
-        <v>92821</v>
+        <v>92822</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4550,7 +4546,7 @@
         <v>126379490</v>
       </c>
       <c r="B39" t="n">
-        <v>92821</v>
+        <v>92822</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4752,7 +4748,7 @@
         <v>126379453</v>
       </c>
       <c r="B41" t="n">
-        <v>91558</v>
+        <v>91560</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4769,14 +4765,10 @@
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
-        </is>
-      </c>
-      <c r="H41" t="inlineStr">
-        <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H41" t="inlineStr"/>
       <c r="I41" t="inlineStr"/>
       <c r="P41" t="inlineStr">
         <is>
@@ -5808,7 +5800,7 @@
         <v>126379444</v>
       </c>
       <c r="B51" t="n">
-        <v>98725</v>
+        <v>98726</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -6541,7 +6533,7 @@
         <v>126379492</v>
       </c>
       <c r="B58" t="n">
-        <v>92821</v>
+        <v>92822</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>

--- a/artfynd/A 24579-2025 artfynd.xlsx
+++ b/artfynd/A 24579-2025 artfynd.xlsx
@@ -5800,7 +5800,7 @@
         <v>126379444</v>
       </c>
       <c r="B51" t="n">
-        <v>98726</v>
+        <v>98727</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>

--- a/artfynd/A 24579-2025 artfynd.xlsx
+++ b/artfynd/A 24579-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>126379461</v>
       </c>
       <c r="B2" t="n">
-        <v>79041</v>
+        <v>79043</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -1113,7 +1113,7 @@
         <v>126379452</v>
       </c>
       <c r="B6" t="n">
-        <v>91560</v>
+        <v>91563</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1324,7 +1324,7 @@
         <v>126379488</v>
       </c>
       <c r="B8" t="n">
-        <v>78707</v>
+        <v>78709</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1425,7 +1425,7 @@
         <v>126379471</v>
       </c>
       <c r="B9" t="n">
-        <v>79041</v>
+        <v>79043</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1531,7 +1531,7 @@
         <v>126379484</v>
       </c>
       <c r="B10" t="n">
-        <v>79041</v>
+        <v>79043</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1637,7 +1637,7 @@
         <v>126379425</v>
       </c>
       <c r="B11" t="n">
-        <v>91504</v>
+        <v>91507</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1738,7 +1738,7 @@
         <v>126379451</v>
       </c>
       <c r="B12" t="n">
-        <v>79229</v>
+        <v>79231</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1848,7 +1848,7 @@
         <v>126379463</v>
       </c>
       <c r="B13" t="n">
-        <v>79041</v>
+        <v>79043</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2286,7 +2286,7 @@
         <v>126379487</v>
       </c>
       <c r="B17" t="n">
-        <v>79041</v>
+        <v>79043</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2392,7 +2392,7 @@
         <v>126379469</v>
       </c>
       <c r="B18" t="n">
-        <v>79041</v>
+        <v>79043</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2493,7 +2493,7 @@
         <v>126379458</v>
       </c>
       <c r="B19" t="n">
-        <v>79041</v>
+        <v>79043</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2599,7 +2599,7 @@
         <v>126379428</v>
       </c>
       <c r="B20" t="n">
-        <v>79660</v>
+        <v>79662</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2700,7 +2700,7 @@
         <v>126379454</v>
       </c>
       <c r="B21" t="n">
-        <v>79041</v>
+        <v>79043</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2806,7 +2806,7 @@
         <v>126379427</v>
       </c>
       <c r="B22" t="n">
-        <v>79660</v>
+        <v>79662</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2907,7 +2907,7 @@
         <v>126379424</v>
       </c>
       <c r="B23" t="n">
-        <v>91504</v>
+        <v>91507</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3008,7 +3008,7 @@
         <v>126379446</v>
       </c>
       <c r="B24" t="n">
-        <v>80174</v>
+        <v>80176</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3109,7 +3109,7 @@
         <v>126379468</v>
       </c>
       <c r="B25" t="n">
-        <v>79041</v>
+        <v>79043</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3210,7 +3210,7 @@
         <v>126379481</v>
       </c>
       <c r="B26" t="n">
-        <v>79041</v>
+        <v>79043</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3311,7 +3311,7 @@
         <v>126379478</v>
       </c>
       <c r="B27" t="n">
-        <v>79041</v>
+        <v>79043</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3417,7 +3417,7 @@
         <v>126379457</v>
       </c>
       <c r="B28" t="n">
-        <v>79041</v>
+        <v>79043</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3518,7 +3518,7 @@
         <v>126379447</v>
       </c>
       <c r="B29" t="n">
-        <v>80146</v>
+        <v>80148</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3733,7 +3733,7 @@
         <v>126379470</v>
       </c>
       <c r="B31" t="n">
-        <v>79041</v>
+        <v>79043</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3834,7 +3834,7 @@
         <v>126379491</v>
       </c>
       <c r="B32" t="n">
-        <v>92822</v>
+        <v>92825</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3935,7 +3935,7 @@
         <v>126379448</v>
       </c>
       <c r="B33" t="n">
-        <v>80182</v>
+        <v>80184</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4036,7 +4036,7 @@
         <v>126379486</v>
       </c>
       <c r="B34" t="n">
-        <v>79041</v>
+        <v>79043</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4137,7 +4137,7 @@
         <v>126379467</v>
       </c>
       <c r="B35" t="n">
-        <v>79041</v>
+        <v>79043</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4238,7 +4238,7 @@
         <v>126379489</v>
       </c>
       <c r="B36" t="n">
-        <v>92822</v>
+        <v>92825</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4339,7 +4339,7 @@
         <v>126379482</v>
       </c>
       <c r="B37" t="n">
-        <v>79041</v>
+        <v>79043</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4445,7 +4445,7 @@
         <v>126379480</v>
       </c>
       <c r="B38" t="n">
-        <v>79041</v>
+        <v>79043</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4546,7 +4546,7 @@
         <v>126379490</v>
       </c>
       <c r="B39" t="n">
-        <v>92822</v>
+        <v>92825</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4647,7 +4647,7 @@
         <v>126379475</v>
       </c>
       <c r="B40" t="n">
-        <v>79041</v>
+        <v>79043</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4748,7 +4748,7 @@
         <v>126379453</v>
       </c>
       <c r="B41" t="n">
-        <v>91560</v>
+        <v>91563</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4845,7 +4845,7 @@
         <v>126379476</v>
       </c>
       <c r="B42" t="n">
-        <v>79041</v>
+        <v>79043</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -4951,7 +4951,7 @@
         <v>126379460</v>
       </c>
       <c r="B43" t="n">
-        <v>79041</v>
+        <v>79043</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5166,7 +5166,7 @@
         <v>126379485</v>
       </c>
       <c r="B45" t="n">
-        <v>79041</v>
+        <v>79043</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5386,7 +5386,7 @@
         <v>126379423</v>
       </c>
       <c r="B47" t="n">
-        <v>79073</v>
+        <v>79075</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5487,7 +5487,7 @@
         <v>126379465</v>
       </c>
       <c r="B48" t="n">
-        <v>79041</v>
+        <v>79043</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5593,7 +5593,7 @@
         <v>126379483</v>
       </c>
       <c r="B49" t="n">
-        <v>79041</v>
+        <v>79043</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5699,7 +5699,7 @@
         <v>126379479</v>
       </c>
       <c r="B50" t="n">
-        <v>79041</v>
+        <v>79043</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5800,7 +5800,7 @@
         <v>126379444</v>
       </c>
       <c r="B51" t="n">
-        <v>98727</v>
+        <v>98731</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -6129,7 +6129,7 @@
         <v>126379474</v>
       </c>
       <c r="B54" t="n">
-        <v>79041</v>
+        <v>79043</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6230,7 +6230,7 @@
         <v>126379455</v>
       </c>
       <c r="B55" t="n">
-        <v>79041</v>
+        <v>79043</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6331,7 +6331,7 @@
         <v>126379456</v>
       </c>
       <c r="B56" t="n">
-        <v>79041</v>
+        <v>79043</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6432,7 +6432,7 @@
         <v>126379473</v>
       </c>
       <c r="B57" t="n">
-        <v>79041</v>
+        <v>79043</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6533,7 +6533,7 @@
         <v>126379492</v>
       </c>
       <c r="B58" t="n">
-        <v>92822</v>
+        <v>92825</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -6634,7 +6634,7 @@
         <v>126379426</v>
       </c>
       <c r="B59" t="n">
-        <v>79660</v>
+        <v>79662</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -6735,7 +6735,7 @@
         <v>126379466</v>
       </c>
       <c r="B60" t="n">
-        <v>79041</v>
+        <v>79043</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -6836,7 +6836,7 @@
         <v>126379472</v>
       </c>
       <c r="B61" t="n">
-        <v>79041</v>
+        <v>79043</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -7046,7 +7046,7 @@
         <v>126379459</v>
       </c>
       <c r="B63" t="n">
-        <v>79041</v>
+        <v>79043</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -7147,7 +7147,7 @@
         <v>126379464</v>
       </c>
       <c r="B64" t="n">
-        <v>79041</v>
+        <v>79043</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -7248,7 +7248,7 @@
         <v>126379462</v>
       </c>
       <c r="B65" t="n">
-        <v>79041</v>
+        <v>79043</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>

--- a/artfynd/A 24579-2025 artfynd.xlsx
+++ b/artfynd/A 24579-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>126379461</v>
       </c>
       <c r="B2" t="n">
-        <v>79043</v>
+        <v>79044</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -1113,7 +1113,7 @@
         <v>126379452</v>
       </c>
       <c r="B6" t="n">
-        <v>91563</v>
+        <v>91565</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1324,7 +1324,7 @@
         <v>126379488</v>
       </c>
       <c r="B8" t="n">
-        <v>78709</v>
+        <v>78710</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1425,7 +1425,7 @@
         <v>126379471</v>
       </c>
       <c r="B9" t="n">
-        <v>79043</v>
+        <v>79044</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1531,7 +1531,7 @@
         <v>126379484</v>
       </c>
       <c r="B10" t="n">
-        <v>79043</v>
+        <v>79044</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1637,7 +1637,7 @@
         <v>126379425</v>
       </c>
       <c r="B11" t="n">
-        <v>91507</v>
+        <v>91509</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1738,7 +1738,7 @@
         <v>126379451</v>
       </c>
       <c r="B12" t="n">
-        <v>79231</v>
+        <v>79232</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1848,7 +1848,7 @@
         <v>126379463</v>
       </c>
       <c r="B13" t="n">
-        <v>79043</v>
+        <v>79044</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2286,7 +2286,7 @@
         <v>126379487</v>
       </c>
       <c r="B17" t="n">
-        <v>79043</v>
+        <v>79044</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2392,7 +2392,7 @@
         <v>126379469</v>
       </c>
       <c r="B18" t="n">
-        <v>79043</v>
+        <v>79044</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2493,7 +2493,7 @@
         <v>126379458</v>
       </c>
       <c r="B19" t="n">
-        <v>79043</v>
+        <v>79044</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2599,7 +2599,7 @@
         <v>126379428</v>
       </c>
       <c r="B20" t="n">
-        <v>79662</v>
+        <v>79663</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2700,7 +2700,7 @@
         <v>126379454</v>
       </c>
       <c r="B21" t="n">
-        <v>79043</v>
+        <v>79044</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2806,7 +2806,7 @@
         <v>126379427</v>
       </c>
       <c r="B22" t="n">
-        <v>79662</v>
+        <v>79663</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2907,7 +2907,7 @@
         <v>126379424</v>
       </c>
       <c r="B23" t="n">
-        <v>91507</v>
+        <v>91509</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3008,7 +3008,7 @@
         <v>126379446</v>
       </c>
       <c r="B24" t="n">
-        <v>80176</v>
+        <v>80177</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3109,7 +3109,7 @@
         <v>126379468</v>
       </c>
       <c r="B25" t="n">
-        <v>79043</v>
+        <v>79044</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3210,7 +3210,7 @@
         <v>126379481</v>
       </c>
       <c r="B26" t="n">
-        <v>79043</v>
+        <v>79044</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3311,7 +3311,7 @@
         <v>126379478</v>
       </c>
       <c r="B27" t="n">
-        <v>79043</v>
+        <v>79044</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3417,7 +3417,7 @@
         <v>126379457</v>
       </c>
       <c r="B28" t="n">
-        <v>79043</v>
+        <v>79044</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3518,7 +3518,7 @@
         <v>126379447</v>
       </c>
       <c r="B29" t="n">
-        <v>80148</v>
+        <v>80149</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3733,7 +3733,7 @@
         <v>126379470</v>
       </c>
       <c r="B31" t="n">
-        <v>79043</v>
+        <v>79044</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3834,7 +3834,7 @@
         <v>126379491</v>
       </c>
       <c r="B32" t="n">
-        <v>92825</v>
+        <v>92827</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3935,7 +3935,7 @@
         <v>126379448</v>
       </c>
       <c r="B33" t="n">
-        <v>80184</v>
+        <v>80185</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4036,7 +4036,7 @@
         <v>126379486</v>
       </c>
       <c r="B34" t="n">
-        <v>79043</v>
+        <v>79044</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4137,7 +4137,7 @@
         <v>126379467</v>
       </c>
       <c r="B35" t="n">
-        <v>79043</v>
+        <v>79044</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4238,7 +4238,7 @@
         <v>126379489</v>
       </c>
       <c r="B36" t="n">
-        <v>92825</v>
+        <v>92827</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4339,7 +4339,7 @@
         <v>126379482</v>
       </c>
       <c r="B37" t="n">
-        <v>79043</v>
+        <v>79044</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4445,7 +4445,7 @@
         <v>126379480</v>
       </c>
       <c r="B38" t="n">
-        <v>79043</v>
+        <v>79044</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4546,7 +4546,7 @@
         <v>126379490</v>
       </c>
       <c r="B39" t="n">
-        <v>92825</v>
+        <v>92827</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4647,7 +4647,7 @@
         <v>126379475</v>
       </c>
       <c r="B40" t="n">
-        <v>79043</v>
+        <v>79044</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4748,7 +4748,7 @@
         <v>126379453</v>
       </c>
       <c r="B41" t="n">
-        <v>91563</v>
+        <v>91565</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4845,7 +4845,7 @@
         <v>126379476</v>
       </c>
       <c r="B42" t="n">
-        <v>79043</v>
+        <v>79044</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -4951,7 +4951,7 @@
         <v>126379460</v>
       </c>
       <c r="B43" t="n">
-        <v>79043</v>
+        <v>79044</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5166,7 +5166,7 @@
         <v>126379485</v>
       </c>
       <c r="B45" t="n">
-        <v>79043</v>
+        <v>79044</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5386,7 +5386,7 @@
         <v>126379423</v>
       </c>
       <c r="B47" t="n">
-        <v>79075</v>
+        <v>79076</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5487,7 +5487,7 @@
         <v>126379465</v>
       </c>
       <c r="B48" t="n">
-        <v>79043</v>
+        <v>79044</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5593,7 +5593,7 @@
         <v>126379483</v>
       </c>
       <c r="B49" t="n">
-        <v>79043</v>
+        <v>79044</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5699,7 +5699,7 @@
         <v>126379479</v>
       </c>
       <c r="B50" t="n">
-        <v>79043</v>
+        <v>79044</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5800,7 +5800,7 @@
         <v>126379444</v>
       </c>
       <c r="B51" t="n">
-        <v>98731</v>
+        <v>98733</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -6129,7 +6129,7 @@
         <v>126379474</v>
       </c>
       <c r="B54" t="n">
-        <v>79043</v>
+        <v>79044</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6230,7 +6230,7 @@
         <v>126379455</v>
       </c>
       <c r="B55" t="n">
-        <v>79043</v>
+        <v>79044</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6331,7 +6331,7 @@
         <v>126379456</v>
       </c>
       <c r="B56" t="n">
-        <v>79043</v>
+        <v>79044</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6432,7 +6432,7 @@
         <v>126379473</v>
       </c>
       <c r="B57" t="n">
-        <v>79043</v>
+        <v>79044</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6533,7 +6533,7 @@
         <v>126379492</v>
       </c>
       <c r="B58" t="n">
-        <v>92825</v>
+        <v>92827</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -6634,7 +6634,7 @@
         <v>126379426</v>
       </c>
       <c r="B59" t="n">
-        <v>79662</v>
+        <v>79663</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -6735,7 +6735,7 @@
         <v>126379466</v>
       </c>
       <c r="B60" t="n">
-        <v>79043</v>
+        <v>79044</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -6836,7 +6836,7 @@
         <v>126379472</v>
       </c>
       <c r="B61" t="n">
-        <v>79043</v>
+        <v>79044</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -7046,7 +7046,7 @@
         <v>126379459</v>
       </c>
       <c r="B63" t="n">
-        <v>79043</v>
+        <v>79044</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -7147,7 +7147,7 @@
         <v>126379464</v>
       </c>
       <c r="B64" t="n">
-        <v>79043</v>
+        <v>79044</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -7248,7 +7248,7 @@
         <v>126379462</v>
       </c>
       <c r="B65" t="n">
-        <v>79043</v>
+        <v>79044</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>

--- a/artfynd/A 24579-2025 artfynd.xlsx
+++ b/artfynd/A 24579-2025 artfynd.xlsx
@@ -1113,7 +1113,7 @@
         <v>126379452</v>
       </c>
       <c r="B6" t="n">
-        <v>91565</v>
+        <v>91569</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1637,7 +1637,7 @@
         <v>126379425</v>
       </c>
       <c r="B11" t="n">
-        <v>91509</v>
+        <v>91513</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -2907,7 +2907,7 @@
         <v>126379424</v>
       </c>
       <c r="B23" t="n">
-        <v>91509</v>
+        <v>91513</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3834,7 +3834,7 @@
         <v>126379491</v>
       </c>
       <c r="B32" t="n">
-        <v>92827</v>
+        <v>92831</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4238,7 +4238,7 @@
         <v>126379489</v>
       </c>
       <c r="B36" t="n">
-        <v>92827</v>
+        <v>92831</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4546,7 +4546,7 @@
         <v>126379490</v>
       </c>
       <c r="B39" t="n">
-        <v>92827</v>
+        <v>92831</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4748,7 +4748,7 @@
         <v>126379453</v>
       </c>
       <c r="B41" t="n">
-        <v>91565</v>
+        <v>91569</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -5800,7 +5800,7 @@
         <v>126379444</v>
       </c>
       <c r="B51" t="n">
-        <v>98733</v>
+        <v>98737</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -6533,7 +6533,7 @@
         <v>126379492</v>
       </c>
       <c r="B58" t="n">
-        <v>92827</v>
+        <v>92831</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>

--- a/artfynd/A 24579-2025 artfynd.xlsx
+++ b/artfynd/A 24579-2025 artfynd.xlsx
@@ -1820,7 +1820,7 @@
         <v>0</v>
       </c>
       <c r="AE12" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AF12" t="inlineStr"/>
       <c r="AG12" t="b">

--- a/artfynd/A 24579-2025 artfynd.xlsx
+++ b/artfynd/A 24579-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY66"/>
+  <dimension ref="A1:AY64"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>126379461</v>
+        <v>126379423</v>
       </c>
       <c r="B2" t="n">
-        <v>79044</v>
+        <v>79359</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -686,21 +686,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6425</v>
+        <v>185</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -710,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>718621</v>
+        <v>718221</v>
       </c>
       <c r="R2" t="n">
-        <v>7234528</v>
+        <v>7234403</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -776,10 +776,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>126379432</v>
+        <v>126379488</v>
       </c>
       <c r="B3" t="n">
-        <v>57727</v>
+        <v>78993</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -787,42 +787,34 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100109</v>
+        <v>353</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
-      <c r="K3" t="inlineStr"/>
-      <c r="L3" t="inlineStr"/>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
           <t>Bergmyran, Vb</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>718387</v>
+        <v>718044</v>
       </c>
       <c r="R3" t="n">
-        <v>7234490</v>
+        <v>7234385</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -855,11 +847,6 @@
       <c r="AA3" t="inlineStr">
         <is>
           <t>2025-07-02</t>
-        </is>
-      </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -890,10 +877,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>126379431</v>
+        <v>126379492</v>
       </c>
       <c r="B4" t="n">
-        <v>57727</v>
+        <v>93197</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -901,21 +888,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100109</v>
+        <v>4364</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -925,10 +912,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>718398</v>
+        <v>718282</v>
       </c>
       <c r="R4" t="n">
-        <v>7234399</v>
+        <v>7234434</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -961,11 +948,6 @@
       <c r="AA4" t="inlineStr">
         <is>
           <t>2025-07-02</t>
-        </is>
-      </c>
-      <c r="AC4" t="inlineStr">
-        <is>
-          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -996,53 +978,45 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>126379440</v>
+        <v>126379425</v>
       </c>
       <c r="B5" t="n">
-        <v>57727</v>
+        <v>91872</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>100109</v>
+        <v>5447</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
-      <c r="K5" t="inlineStr"/>
-      <c r="L5" t="inlineStr"/>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
           <t>Bergmyran, Vb</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>718336</v>
+        <v>717969</v>
       </c>
       <c r="R5" t="n">
-        <v>7234249</v>
+        <v>7234409</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1069,17 +1043,12 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2025-07-01</t>
+          <t>2025-07-02</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2025-07-01</t>
-        </is>
-      </c>
-      <c r="AC5" t="inlineStr">
-        <is>
-          <t>Färska ringhack</t>
+          <t>2025-07-02</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1110,30 +1079,34 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>126379452</v>
+        <v>126379458</v>
       </c>
       <c r="B6" t="n">
-        <v>91569</v>
+        <v>79327</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H6" t="inlineStr"/>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
       <c r="I6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
@@ -1141,10 +1114,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>718194</v>
+        <v>718022</v>
       </c>
       <c r="R6" t="n">
-        <v>7234461</v>
+        <v>7234436</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1177,6 +1150,11 @@
       <c r="AA6" t="inlineStr">
         <is>
           <t>2025-07-02</t>
+        </is>
+      </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1207,53 +1185,45 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>126379433</v>
+        <v>126379459</v>
       </c>
       <c r="B7" t="n">
-        <v>57727</v>
+        <v>79327</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
-      <c r="K7" t="inlineStr"/>
-      <c r="L7" t="inlineStr"/>
-      <c r="M7" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
           <t>Bergmyran, Vb</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>718308</v>
+        <v>718274</v>
       </c>
       <c r="R7" t="n">
-        <v>7234486</v>
+        <v>7234439</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1286,11 +1256,6 @@
       <c r="AA7" t="inlineStr">
         <is>
           <t>2025-07-02</t>
-        </is>
-      </c>
-      <c r="AC7" t="inlineStr">
-        <is>
-          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1321,32 +1286,32 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>126379488</v>
+        <v>126379460</v>
       </c>
       <c r="B8" t="n">
-        <v>78710</v>
+        <v>79327</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>353</v>
+        <v>6425</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1356,7 +1321,7 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>718044</v>
+        <v>718039</v>
       </c>
       <c r="R8" t="n">
         <v>7234385</v>
@@ -1422,14 +1387,14 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>126379471</v>
+        <v>126379472</v>
       </c>
       <c r="B9" t="n">
-        <v>79044</v>
+        <v>79327</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E9" t="n">
@@ -1457,10 +1422,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>718115</v>
+        <v>718308</v>
       </c>
       <c r="R9" t="n">
-        <v>7234496</v>
+        <v>7234404</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1493,11 +1458,6 @@
       <c r="AA9" t="inlineStr">
         <is>
           <t>2025-07-02</t>
-        </is>
-      </c>
-      <c r="AC9" t="inlineStr">
-        <is>
-          <t>Långa bålar</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1528,14 +1488,14 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>126379484</v>
+        <v>126379473</v>
       </c>
       <c r="B10" t="n">
-        <v>79044</v>
+        <v>79327</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E10" t="n">
@@ -1563,10 +1523,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>718212</v>
+        <v>718327</v>
       </c>
       <c r="R10" t="n">
-        <v>7234353</v>
+        <v>7234412</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1599,11 +1559,6 @@
       <c r="AA10" t="inlineStr">
         <is>
           <t>2025-07-02</t>
-        </is>
-      </c>
-      <c r="AC10" t="inlineStr">
-        <is>
-          <t>Med apothecier</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1634,32 +1589,32 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>126379425</v>
+        <v>126379474</v>
       </c>
       <c r="B11" t="n">
-        <v>91513</v>
+        <v>79327</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>5447</v>
+        <v>6425</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1669,10 +1624,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>717969</v>
+        <v>718328</v>
       </c>
       <c r="R11" t="n">
-        <v>7234409</v>
+        <v>7234423</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1735,10 +1690,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>126379451</v>
+        <v>126379475</v>
       </c>
       <c r="B12" t="n">
-        <v>79232</v>
+        <v>79327</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1746,37 +1701,34 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>230552</v>
+        <v>6425</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Gropig skägglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Usnea barbata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(L.) Weber ex F.H.Wigg.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
-      <c r="J12" t="inlineStr"/>
-      <c r="K12" t="inlineStr"/>
-      <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
           <t>Bergmyran, Vb</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>717977</v>
+        <v>718346</v>
       </c>
       <c r="R12" t="n">
-        <v>7234425</v>
+        <v>7234422</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1811,18 +1763,12 @@
           <t>2025-07-02</t>
         </is>
       </c>
-      <c r="AC12" t="inlineStr">
-        <is>
-          <t>Måste efterforska</t>
-        </is>
-      </c>
       <c r="AD12" t="b">
         <v>0</v>
       </c>
       <c r="AE12" t="b">
-        <v>1</v>
-      </c>
-      <c r="AF12" t="inlineStr"/>
+        <v>0</v>
+      </c>
       <c r="AG12" t="b">
         <v>0</v>
       </c>
@@ -1845,14 +1791,14 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>126379463</v>
+        <v>126379476</v>
       </c>
       <c r="B13" t="n">
-        <v>79044</v>
+        <v>79327</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E13" t="n">
@@ -1880,10 +1826,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>718526</v>
+        <v>718277</v>
       </c>
       <c r="R13" t="n">
-        <v>7234595</v>
+        <v>7234381</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1916,6 +1862,11 @@
       <c r="AA13" t="inlineStr">
         <is>
           <t>2025-07-02</t>
+        </is>
+      </c>
+      <c r="AC13" t="inlineStr">
+        <is>
+          <t>Rikligt. På flera träd</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1946,53 +1897,45 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>126379430</v>
+        <v>126379478</v>
       </c>
       <c r="B14" t="n">
-        <v>57727</v>
+        <v>79327</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
-      <c r="K14" t="inlineStr"/>
-      <c r="L14" t="inlineStr"/>
-      <c r="M14" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
           <t>Bergmyran, Vb</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>718154</v>
+        <v>718319</v>
       </c>
       <c r="R14" t="n">
-        <v>7234509</v>
+        <v>7234335</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2029,7 +1972,7 @@
       </c>
       <c r="AC14" t="inlineStr">
         <is>
-          <t>Färskt ringhack</t>
+          <t>Långa bålar</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2060,53 +2003,45 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>126379434</v>
+        <v>126379479</v>
       </c>
       <c r="B15" t="n">
-        <v>57727</v>
+        <v>79327</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
-      <c r="K15" t="inlineStr"/>
-      <c r="L15" t="inlineStr"/>
-      <c r="M15" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
           <t>Bergmyran, Vb</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>718150</v>
+        <v>718272</v>
       </c>
       <c r="R15" t="n">
-        <v>7234307</v>
+        <v>7234358</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2139,11 +2074,6 @@
       <c r="AA15" t="inlineStr">
         <is>
           <t>2025-07-02</t>
-        </is>
-      </c>
-      <c r="AC15" t="inlineStr">
-        <is>
-          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2174,53 +2104,45 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>126379443</v>
+        <v>126379480</v>
       </c>
       <c r="B16" t="n">
-        <v>57887</v>
+        <v>79327</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>103021</v>
+        <v>6425</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
-      <c r="K16" t="inlineStr"/>
-      <c r="L16" t="inlineStr"/>
-      <c r="M16" t="inlineStr">
-        <is>
-          <t>upprörd, varnande</t>
-        </is>
-      </c>
-      <c r="N16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
           <t>Bergmyran, Vb</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>718294</v>
+        <v>718236</v>
       </c>
       <c r="R16" t="n">
-        <v>7234414</v>
+        <v>7234393</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2283,14 +2205,14 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>126379487</v>
+        <v>126379481</v>
       </c>
       <c r="B17" t="n">
-        <v>79044</v>
+        <v>79327</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E17" t="n">
@@ -2318,10 +2240,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>718050</v>
+        <v>718217</v>
       </c>
       <c r="R17" t="n">
-        <v>7234355</v>
+        <v>7234406</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2354,11 +2276,6 @@
       <c r="AA17" t="inlineStr">
         <is>
           <t>2025-07-02</t>
-        </is>
-      </c>
-      <c r="AC17" t="inlineStr">
-        <is>
-          <t>Långa bålar</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2389,14 +2306,14 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>126379469</v>
+        <v>126379482</v>
       </c>
       <c r="B18" t="n">
-        <v>79044</v>
+        <v>79327</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E18" t="n">
@@ -2424,10 +2341,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>718625</v>
+        <v>718206</v>
       </c>
       <c r="R18" t="n">
-        <v>7234575</v>
+        <v>7234360</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2460,6 +2377,11 @@
       <c r="AA18" t="inlineStr">
         <is>
           <t>2025-07-02</t>
+        </is>
+      </c>
+      <c r="AC18" t="inlineStr">
+        <is>
+          <t>Långa bålar</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2490,14 +2412,14 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>126379458</v>
+        <v>126379483</v>
       </c>
       <c r="B19" t="n">
-        <v>79044</v>
+        <v>79327</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E19" t="n">
@@ -2525,10 +2447,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>718022</v>
+        <v>718189</v>
       </c>
       <c r="R19" t="n">
-        <v>7234436</v>
+        <v>7234360</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2565,7 +2487,7 @@
       </c>
       <c r="AC19" t="inlineStr">
         <is>
-          <t>Rikligt</t>
+          <t>Långa bålar</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2596,32 +2518,32 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>126379428</v>
+        <v>126379484</v>
       </c>
       <c r="B20" t="n">
-        <v>79663</v>
+        <v>79327</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2631,10 +2553,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>718042</v>
+        <v>718212</v>
       </c>
       <c r="R20" t="n">
-        <v>7234389</v>
+        <v>7234353</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2667,6 +2589,11 @@
       <c r="AA20" t="inlineStr">
         <is>
           <t>2025-07-02</t>
+        </is>
+      </c>
+      <c r="AC20" t="inlineStr">
+        <is>
+          <t>Med apothecier</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2697,14 +2624,14 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>126379454</v>
+        <v>126379485</v>
       </c>
       <c r="B21" t="n">
-        <v>79044</v>
+        <v>79327</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E21" t="n">
@@ -2732,10 +2659,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>718501</v>
+        <v>718173</v>
       </c>
       <c r="R21" t="n">
-        <v>7234552</v>
+        <v>7234351</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2772,7 +2699,7 @@
       </c>
       <c r="AC21" t="inlineStr">
         <is>
-          <t>Rikligt</t>
+          <t>Fertil</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2803,32 +2730,32 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>126379427</v>
+        <v>126379486</v>
       </c>
       <c r="B22" t="n">
-        <v>79663</v>
+        <v>79327</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2838,10 +2765,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>718379</v>
+        <v>718194</v>
       </c>
       <c r="R22" t="n">
-        <v>7234438</v>
+        <v>7234334</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2904,32 +2831,32 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>126379424</v>
+        <v>126379487</v>
       </c>
       <c r="B23" t="n">
-        <v>91513</v>
+        <v>79327</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>5447</v>
+        <v>6425</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -2939,10 +2866,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>718450</v>
+        <v>718050</v>
       </c>
       <c r="R23" t="n">
-        <v>7234710</v>
+        <v>7234355</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2975,6 +2902,11 @@
       <c r="AA23" t="inlineStr">
         <is>
           <t>2025-07-02</t>
+        </is>
+      </c>
+      <c r="AC23" t="inlineStr">
+        <is>
+          <t>Långa bålar</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3005,32 +2937,32 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>126379446</v>
+        <v>126379426</v>
       </c>
       <c r="B24" t="n">
-        <v>80177</v>
+        <v>79946</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>6461</v>
+        <v>6453</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Norrlandslav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Nephroma arcticum</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(L.) Torss.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -3040,10 +2972,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>718189</v>
+        <v>718364</v>
       </c>
       <c r="R24" t="n">
-        <v>7234350</v>
+        <v>7234409</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3106,10 +3038,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>126379468</v>
+        <v>126379427</v>
       </c>
       <c r="B25" t="n">
-        <v>79044</v>
+        <v>79946</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3117,21 +3049,21 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3141,10 +3073,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>718577</v>
+        <v>718379</v>
       </c>
       <c r="R25" t="n">
-        <v>7234539</v>
+        <v>7234438</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3207,10 +3139,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>126379481</v>
+        <v>126379428</v>
       </c>
       <c r="B26" t="n">
-        <v>79044</v>
+        <v>79946</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3218,21 +3150,21 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3242,10 +3174,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>718217</v>
+        <v>718042</v>
       </c>
       <c r="R26" t="n">
-        <v>7234406</v>
+        <v>7234389</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3308,32 +3240,32 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>126379478</v>
+        <v>126379446</v>
       </c>
       <c r="B27" t="n">
-        <v>79044</v>
+        <v>80460</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>6425</v>
+        <v>6461</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Norrlandslav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma arcticum</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Torss.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3343,10 +3275,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>718319</v>
+        <v>718189</v>
       </c>
       <c r="R27" t="n">
-        <v>7234335</v>
+        <v>7234350</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3379,11 +3311,6 @@
       <c r="AA27" t="inlineStr">
         <is>
           <t>2025-07-02</t>
-        </is>
-      </c>
-      <c r="AC27" t="inlineStr">
-        <is>
-          <t>Långa bålar</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3414,32 +3341,32 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>126379457</v>
+        <v>126379448</v>
       </c>
       <c r="B28" t="n">
-        <v>79044</v>
+        <v>80468</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>6425</v>
+        <v>6464</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3449,10 +3376,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>718450</v>
+        <v>718195</v>
       </c>
       <c r="R28" t="n">
-        <v>7234706</v>
+        <v>7234369</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3515,10 +3442,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>126379447</v>
+        <v>126379431</v>
       </c>
       <c r="B29" t="n">
-        <v>80149</v>
+        <v>57953</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3526,21 +3453,21 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3550,10 +3477,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>718536</v>
+        <v>718398</v>
       </c>
       <c r="R29" t="n">
-        <v>7234545</v>
+        <v>7234399</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3586,6 +3513,11 @@
       <c r="AA29" t="inlineStr">
         <is>
           <t>2025-07-02</t>
+        </is>
+      </c>
+      <c r="AC29" t="inlineStr">
+        <is>
+          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3616,10 +3548,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>126379437</v>
+        <v>126379434</v>
       </c>
       <c r="B30" t="n">
-        <v>57727</v>
+        <v>57953</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3649,7 +3581,7 @@
       <c r="L30" t="inlineStr"/>
       <c r="M30" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N30" t="inlineStr"/>
@@ -3659,10 +3591,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>718001</v>
+        <v>718150</v>
       </c>
       <c r="R30" t="n">
-        <v>7234400</v>
+        <v>7234307</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3699,7 +3631,7 @@
       </c>
       <c r="AC30" t="inlineStr">
         <is>
-          <t>Äldre ringhack</t>
+          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3730,10 +3662,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>126379470</v>
+        <v>126379435</v>
       </c>
       <c r="B31" t="n">
-        <v>79044</v>
+        <v>57953</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3741,34 +3673,42 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
+      <c r="K31" t="inlineStr"/>
+      <c r="L31" t="inlineStr"/>
+      <c r="M31" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
           <t>Bergmyran, Vb</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>718088</v>
+        <v>718107</v>
       </c>
       <c r="R31" t="n">
-        <v>7234482</v>
+        <v>7234326</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3801,6 +3741,11 @@
       <c r="AA31" t="inlineStr">
         <is>
           <t>2025-07-02</t>
+        </is>
+      </c>
+      <c r="AC31" t="inlineStr">
+        <is>
+          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -3831,45 +3776,53 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>126379491</v>
+        <v>126379436</v>
       </c>
       <c r="B32" t="n">
-        <v>92831</v>
+        <v>57953</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>4364</v>
+        <v>100109</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
+      <c r="K32" t="inlineStr"/>
+      <c r="L32" t="inlineStr"/>
+      <c r="M32" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N32" t="inlineStr"/>
       <c r="P32" t="inlineStr">
         <is>
           <t>Bergmyran, Vb</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>718094</v>
+        <v>718009</v>
       </c>
       <c r="R32" t="n">
-        <v>7234481</v>
+        <v>7234441</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3902,6 +3855,11 @@
       <c r="AA32" t="inlineStr">
         <is>
           <t>2025-07-02</t>
+        </is>
+      </c>
+      <c r="AC32" t="inlineStr">
+        <is>
+          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -3932,45 +3890,53 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>126379448</v>
+        <v>126379437</v>
       </c>
       <c r="B33" t="n">
-        <v>80185</v>
+        <v>57953</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>6464</v>
+        <v>100109</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
+      <c r="K33" t="inlineStr"/>
+      <c r="L33" t="inlineStr"/>
+      <c r="M33" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N33" t="inlineStr"/>
       <c r="P33" t="inlineStr">
         <is>
           <t>Bergmyran, Vb</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>718195</v>
+        <v>718001</v>
       </c>
       <c r="R33" t="n">
-        <v>7234369</v>
+        <v>7234400</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4003,6 +3969,11 @@
       <c r="AA33" t="inlineStr">
         <is>
           <t>2025-07-02</t>
+        </is>
+      </c>
+      <c r="AC33" t="inlineStr">
+        <is>
+          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4033,10 +4004,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>126379486</v>
+        <v>126379438</v>
       </c>
       <c r="B34" t="n">
-        <v>79044</v>
+        <v>57953</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4044,34 +4015,42 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
+      <c r="K34" t="inlineStr"/>
+      <c r="L34" t="inlineStr"/>
+      <c r="M34" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N34" t="inlineStr"/>
       <c r="P34" t="inlineStr">
         <is>
           <t>Bergmyran, Vb</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>718194</v>
+        <v>718061</v>
       </c>
       <c r="R34" t="n">
-        <v>7234334</v>
+        <v>7234332</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4098,12 +4077,17 @@
       </c>
       <c r="Y34" t="inlineStr">
         <is>
-          <t>2025-07-02</t>
+          <t>2025-07-01</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
         <is>
-          <t>2025-07-02</t>
+          <t>2025-07-01</t>
+        </is>
+      </c>
+      <c r="AC34" t="inlineStr">
+        <is>
+          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4134,10 +4118,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>126379467</v>
+        <v>126379439</v>
       </c>
       <c r="B35" t="n">
-        <v>79044</v>
+        <v>57953</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4145,34 +4129,42 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
+      <c r="K35" t="inlineStr"/>
+      <c r="L35" t="inlineStr"/>
+      <c r="M35" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N35" t="inlineStr"/>
       <c r="P35" t="inlineStr">
         <is>
           <t>Bergmyran, Vb</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>718635</v>
+        <v>718038</v>
       </c>
       <c r="R35" t="n">
-        <v>7234620</v>
+        <v>7234341</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4199,12 +4191,17 @@
       </c>
       <c r="Y35" t="inlineStr">
         <is>
-          <t>2025-07-02</t>
+          <t>2025-07-01</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
         <is>
-          <t>2025-07-02</t>
+          <t>2025-07-01</t>
+        </is>
+      </c>
+      <c r="AC35" t="inlineStr">
+        <is>
+          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4235,45 +4232,53 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>126379489</v>
+        <v>126379440</v>
       </c>
       <c r="B36" t="n">
-        <v>92831</v>
+        <v>57953</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>4364</v>
+        <v>100109</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
+      <c r="K36" t="inlineStr"/>
+      <c r="L36" t="inlineStr"/>
+      <c r="M36" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N36" t="inlineStr"/>
       <c r="P36" t="inlineStr">
         <is>
           <t>Bergmyran, Vb</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>718427</v>
+        <v>718336</v>
       </c>
       <c r="R36" t="n">
-        <v>7234679</v>
+        <v>7234249</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4300,12 +4305,17 @@
       </c>
       <c r="Y36" t="inlineStr">
         <is>
-          <t>2025-07-02</t>
+          <t>2025-07-01</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
         <is>
-          <t>2025-07-02</t>
+          <t>2025-07-01</t>
+        </is>
+      </c>
+      <c r="AC36" t="inlineStr">
+        <is>
+          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4336,45 +4346,53 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>126379482</v>
+        <v>126379441</v>
       </c>
       <c r="B37" t="n">
-        <v>79044</v>
+        <v>57141</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>6425</v>
+        <v>100138</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
+      <c r="K37" t="inlineStr"/>
+      <c r="L37" t="inlineStr"/>
+      <c r="M37" t="inlineStr">
+        <is>
+          <t>äldre spillning</t>
+        </is>
+      </c>
+      <c r="N37" t="inlineStr"/>
       <c r="P37" t="inlineStr">
         <is>
           <t>Bergmyran, Vb</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>718206</v>
+        <v>718148</v>
       </c>
       <c r="R37" t="n">
-        <v>7234360</v>
+        <v>7234311</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4411,7 +4429,7 @@
       </c>
       <c r="AC37" t="inlineStr">
         <is>
-          <t>Långa bålar</t>
+          <t>Spillning</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4442,10 +4460,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>126379480</v>
+        <v>126379442</v>
       </c>
       <c r="B38" t="n">
-        <v>79044</v>
+        <v>58114</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4453,34 +4471,42 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>6425</v>
+        <v>103021</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
+      <c r="K38" t="inlineStr"/>
+      <c r="L38" t="inlineStr"/>
+      <c r="M38" t="inlineStr">
+        <is>
+          <t>upprörd, varnande</t>
+        </is>
+      </c>
+      <c r="N38" t="inlineStr"/>
       <c r="P38" t="inlineStr">
         <is>
           <t>Bergmyran, Vb</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>718236</v>
+        <v>718338</v>
       </c>
       <c r="R38" t="n">
-        <v>7234393</v>
+        <v>7234424</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4543,45 +4569,53 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>126379490</v>
+        <v>126379443</v>
       </c>
       <c r="B39" t="n">
-        <v>92831</v>
+        <v>58114</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>4364</v>
+        <v>103021</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
+      <c r="K39" t="inlineStr"/>
+      <c r="L39" t="inlineStr"/>
+      <c r="M39" t="inlineStr">
+        <is>
+          <t>upprörd, varnande</t>
+        </is>
+      </c>
+      <c r="N39" t="inlineStr"/>
       <c r="P39" t="inlineStr">
         <is>
           <t>Bergmyran, Vb</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>718545</v>
+        <v>718294</v>
       </c>
       <c r="R39" t="n">
-        <v>7234655</v>
+        <v>7234414</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4644,32 +4678,32 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>126379475</v>
+        <v>126379444</v>
       </c>
       <c r="B40" t="n">
-        <v>79044</v>
+        <v>99140</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>6425</v>
+        <v>221952</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
@@ -4679,10 +4713,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>718346</v>
+        <v>717964</v>
       </c>
       <c r="R40" t="n">
-        <v>7234422</v>
+        <v>7234394</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4745,41 +4779,48 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>126379453</v>
+        <v>126379451</v>
       </c>
       <c r="B41" t="n">
-        <v>91569</v>
+        <v>79515</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>5432</v>
+        <v>230552</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Gropig skägglav</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H41" t="inlineStr"/>
+          <t>Usnea barbata</t>
+        </is>
+      </c>
+      <c r="H41" t="inlineStr">
+        <is>
+          <t>(L.) Weber ex F.H.Wigg.</t>
+        </is>
+      </c>
       <c r="I41" t="inlineStr"/>
+      <c r="J41" t="inlineStr"/>
+      <c r="K41" t="inlineStr"/>
+      <c r="N41" t="inlineStr"/>
       <c r="P41" t="inlineStr">
         <is>
           <t>Bergmyran, Vb</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>718212</v>
+        <v>717977</v>
       </c>
       <c r="R41" t="n">
-        <v>7234351</v>
+        <v>7234425</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -4814,12 +4855,18 @@
           <t>2025-07-02</t>
         </is>
       </c>
+      <c r="AC41" t="inlineStr">
+        <is>
+          <t>Måste efterforska</t>
+        </is>
+      </c>
       <c r="AD41" t="b">
         <v>0</v>
       </c>
       <c r="AE41" t="b">
-        <v>0</v>
-      </c>
+        <v>1</v>
+      </c>
+      <c r="AF41" t="inlineStr"/>
       <c r="AG41" t="b">
         <v>0</v>
       </c>
@@ -4842,10 +4889,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>126379476</v>
+        <v>126379489</v>
       </c>
       <c r="B42" t="n">
-        <v>79044</v>
+        <v>93197</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -4853,21 +4900,21 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>6425</v>
+        <v>4364</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
@@ -4877,10 +4924,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>718277</v>
+        <v>718427</v>
       </c>
       <c r="R42" t="n">
-        <v>7234381</v>
+        <v>7234679</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -4913,11 +4960,6 @@
       <c r="AA42" t="inlineStr">
         <is>
           <t>2025-07-02</t>
-        </is>
-      </c>
-      <c r="AC42" t="inlineStr">
-        <is>
-          <t>Rikligt. På flera träd</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -4948,10 +4990,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>126379460</v>
+        <v>126379490</v>
       </c>
       <c r="B43" t="n">
-        <v>79044</v>
+        <v>93197</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -4959,21 +5001,21 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>6425</v>
+        <v>4364</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
@@ -4983,10 +5025,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>718039</v>
+        <v>718545</v>
       </c>
       <c r="R43" t="n">
-        <v>7234385</v>
+        <v>7234655</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -5049,53 +5091,45 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>126379441</v>
+        <v>126379491</v>
       </c>
       <c r="B44" t="n">
-        <v>56917</v>
+        <v>93197</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>100138</v>
+        <v>4364</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
-      <c r="K44" t="inlineStr"/>
-      <c r="L44" t="inlineStr"/>
-      <c r="M44" t="inlineStr">
-        <is>
-          <t>äldre spillning</t>
-        </is>
-      </c>
-      <c r="N44" t="inlineStr"/>
       <c r="P44" t="inlineStr">
         <is>
           <t>Bergmyran, Vb</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>718148</v>
+        <v>718094</v>
       </c>
       <c r="R44" t="n">
-        <v>7234311</v>
+        <v>7234481</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5128,11 +5162,6 @@
       <c r="AA44" t="inlineStr">
         <is>
           <t>2025-07-02</t>
-        </is>
-      </c>
-      <c r="AC44" t="inlineStr">
-        <is>
-          <t>Spillning</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5163,32 +5192,32 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>126379485</v>
+        <v>126379424</v>
       </c>
       <c r="B45" t="n">
-        <v>79044</v>
+        <v>91872</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>6425</v>
+        <v>5447</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
@@ -5198,10 +5227,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>718173</v>
+        <v>718450</v>
       </c>
       <c r="R45" t="n">
-        <v>7234351</v>
+        <v>7234710</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5234,11 +5263,6 @@
       <c r="AA45" t="inlineStr">
         <is>
           <t>2025-07-02</t>
-        </is>
-      </c>
-      <c r="AC45" t="inlineStr">
-        <is>
-          <t>Fertil</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5269,53 +5293,45 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>126379436</v>
+        <v>126379454</v>
       </c>
       <c r="B46" t="n">
-        <v>57727</v>
+        <v>79327</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
-      <c r="K46" t="inlineStr"/>
-      <c r="L46" t="inlineStr"/>
-      <c r="M46" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N46" t="inlineStr"/>
       <c r="P46" t="inlineStr">
         <is>
           <t>Bergmyran, Vb</t>
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>718009</v>
+        <v>718501</v>
       </c>
       <c r="R46" t="n">
-        <v>7234441</v>
+        <v>7234552</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5352,7 +5368,7 @@
       </c>
       <c r="AC46" t="inlineStr">
         <is>
-          <t>Äldre ringhack</t>
+          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -5383,32 +5399,32 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>126379423</v>
+        <v>126379455</v>
       </c>
       <c r="B47" t="n">
-        <v>79076</v>
+        <v>79327</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>185</v>
+        <v>6425</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
@@ -5418,10 +5434,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>718221</v>
+        <v>718524</v>
       </c>
       <c r="R47" t="n">
-        <v>7234403</v>
+        <v>7234543</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5484,14 +5500,14 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>126379465</v>
+        <v>126379456</v>
       </c>
       <c r="B48" t="n">
-        <v>79044</v>
+        <v>79327</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E48" t="n">
@@ -5519,10 +5535,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>718515</v>
+        <v>718493</v>
       </c>
       <c r="R48" t="n">
-        <v>7234673</v>
+        <v>7234644</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5555,11 +5571,6 @@
       <c r="AA48" t="inlineStr">
         <is>
           <t>2025-07-02</t>
-        </is>
-      </c>
-      <c r="AC48" t="inlineStr">
-        <is>
-          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -5590,14 +5601,14 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>126379483</v>
+        <v>126379457</v>
       </c>
       <c r="B49" t="n">
-        <v>79044</v>
+        <v>79327</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E49" t="n">
@@ -5625,10 +5636,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>718189</v>
+        <v>718450</v>
       </c>
       <c r="R49" t="n">
-        <v>7234360</v>
+        <v>7234706</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -5661,11 +5672,6 @@
       <c r="AA49" t="inlineStr">
         <is>
           <t>2025-07-02</t>
-        </is>
-      </c>
-      <c r="AC49" t="inlineStr">
-        <is>
-          <t>Långa bålar</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -5696,14 +5702,14 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>126379479</v>
+        <v>126379461</v>
       </c>
       <c r="B50" t="n">
-        <v>79044</v>
+        <v>79327</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E50" t="n">
@@ -5731,10 +5737,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>718272</v>
+        <v>718621</v>
       </c>
       <c r="R50" t="n">
-        <v>7234358</v>
+        <v>7234528</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -5797,32 +5803,32 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>126379444</v>
+        <v>126379462</v>
       </c>
       <c r="B51" t="n">
-        <v>98737</v>
+        <v>79327</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>221952</v>
+        <v>6425</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
@@ -5832,10 +5838,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>717964</v>
+        <v>718535</v>
       </c>
       <c r="R51" t="n">
-        <v>7234394</v>
+        <v>7234587</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -5868,6 +5874,11 @@
       <c r="AA51" t="inlineStr">
         <is>
           <t>2025-07-02</t>
+        </is>
+      </c>
+      <c r="AC51" t="inlineStr">
+        <is>
+          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -5898,53 +5909,45 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>126379439</v>
+        <v>126379463</v>
       </c>
       <c r="B52" t="n">
-        <v>57727</v>
+        <v>79327</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E52" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
-      <c r="K52" t="inlineStr"/>
-      <c r="L52" t="inlineStr"/>
-      <c r="M52" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N52" t="inlineStr"/>
       <c r="P52" t="inlineStr">
         <is>
           <t>Bergmyran, Vb</t>
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>718038</v>
+        <v>718526</v>
       </c>
       <c r="R52" t="n">
-        <v>7234341</v>
+        <v>7234595</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -5971,17 +5974,12 @@
       </c>
       <c r="Y52" t="inlineStr">
         <is>
-          <t>2025-07-01</t>
+          <t>2025-07-02</t>
         </is>
       </c>
       <c r="AA52" t="inlineStr">
         <is>
-          <t>2025-07-01</t>
-        </is>
-      </c>
-      <c r="AC52" t="inlineStr">
-        <is>
-          <t>Äldre ringhack</t>
+          <t>2025-07-02</t>
         </is>
       </c>
       <c r="AD52" t="b">
@@ -6012,53 +6010,45 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>126379435</v>
+        <v>126379464</v>
       </c>
       <c r="B53" t="n">
-        <v>57727</v>
+        <v>79327</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E53" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
-      <c r="K53" t="inlineStr"/>
-      <c r="L53" t="inlineStr"/>
-      <c r="M53" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N53" t="inlineStr"/>
       <c r="P53" t="inlineStr">
         <is>
           <t>Bergmyran, Vb</t>
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>718107</v>
+        <v>718427</v>
       </c>
       <c r="R53" t="n">
-        <v>7234326</v>
+        <v>7234679</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -6091,11 +6081,6 @@
       <c r="AA53" t="inlineStr">
         <is>
           <t>2025-07-02</t>
-        </is>
-      </c>
-      <c r="AC53" t="inlineStr">
-        <is>
-          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD53" t="b">
@@ -6126,14 +6111,14 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>126379474</v>
+        <v>126379465</v>
       </c>
       <c r="B54" t="n">
-        <v>79044</v>
+        <v>79327</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E54" t="n">
@@ -6161,10 +6146,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>718328</v>
+        <v>718515</v>
       </c>
       <c r="R54" t="n">
-        <v>7234423</v>
+        <v>7234673</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -6197,6 +6182,11 @@
       <c r="AA54" t="inlineStr">
         <is>
           <t>2025-07-02</t>
+        </is>
+      </c>
+      <c r="AC54" t="inlineStr">
+        <is>
+          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD54" t="b">
@@ -6227,14 +6217,14 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>126379455</v>
+        <v>126379466</v>
       </c>
       <c r="B55" t="n">
-        <v>79044</v>
+        <v>79327</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E55" t="n">
@@ -6262,10 +6252,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>718524</v>
+        <v>718570</v>
       </c>
       <c r="R55" t="n">
-        <v>7234543</v>
+        <v>7234643</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -6328,14 +6318,14 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>126379456</v>
+        <v>126379467</v>
       </c>
       <c r="B56" t="n">
-        <v>79044</v>
+        <v>79327</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E56" t="n">
@@ -6363,10 +6353,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>718493</v>
+        <v>718635</v>
       </c>
       <c r="R56" t="n">
-        <v>7234644</v>
+        <v>7234620</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -6429,14 +6419,14 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>126379473</v>
+        <v>126379468</v>
       </c>
       <c r="B57" t="n">
-        <v>79044</v>
+        <v>79327</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E57" t="n">
@@ -6464,10 +6454,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>718327</v>
+        <v>718577</v>
       </c>
       <c r="R57" t="n">
-        <v>7234412</v>
+        <v>7234539</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -6530,32 +6520,32 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>126379492</v>
+        <v>126379469</v>
       </c>
       <c r="B58" t="n">
-        <v>92831</v>
+        <v>79327</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E58" t="n">
-        <v>4364</v>
+        <v>6425</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
@@ -6565,10 +6555,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>718282</v>
+        <v>718625</v>
       </c>
       <c r="R58" t="n">
-        <v>7234434</v>
+        <v>7234575</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -6631,32 +6621,32 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>126379426</v>
+        <v>126379470</v>
       </c>
       <c r="B59" t="n">
-        <v>79663</v>
+        <v>79327</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E59" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
@@ -6666,10 +6656,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>718364</v>
+        <v>718088</v>
       </c>
       <c r="R59" t="n">
-        <v>7234409</v>
+        <v>7234482</v>
       </c>
       <c r="S59" t="n">
         <v>10</v>
@@ -6732,14 +6722,14 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>126379466</v>
+        <v>126379471</v>
       </c>
       <c r="B60" t="n">
-        <v>79044</v>
+        <v>79327</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E60" t="n">
@@ -6767,10 +6757,10 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>718570</v>
+        <v>718115</v>
       </c>
       <c r="R60" t="n">
-        <v>7234643</v>
+        <v>7234496</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>
@@ -6803,6 +6793,11 @@
       <c r="AA60" t="inlineStr">
         <is>
           <t>2025-07-02</t>
+        </is>
+      </c>
+      <c r="AC60" t="inlineStr">
+        <is>
+          <t>Långa bålar</t>
         </is>
       </c>
       <c r="AD60" t="b">
@@ -6833,10 +6828,10 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>126379472</v>
+        <v>126379447</v>
       </c>
       <c r="B61" t="n">
-        <v>79044</v>
+        <v>80432</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -6844,21 +6839,21 @@
         </is>
       </c>
       <c r="E61" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
@@ -6868,10 +6863,10 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>718308</v>
+        <v>718536</v>
       </c>
       <c r="R61" t="n">
-        <v>7234404</v>
+        <v>7234545</v>
       </c>
       <c r="S61" t="n">
         <v>10</v>
@@ -6934,10 +6929,10 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>126379442</v>
+        <v>126379430</v>
       </c>
       <c r="B62" t="n">
-        <v>57887</v>
+        <v>57953</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -6945,21 +6940,21 @@
         </is>
       </c>
       <c r="E62" t="n">
-        <v>103021</v>
+        <v>100109</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
@@ -6967,7 +6962,7 @@
       <c r="L62" t="inlineStr"/>
       <c r="M62" t="inlineStr">
         <is>
-          <t>upprörd, varnande</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N62" t="inlineStr"/>
@@ -6977,10 +6972,10 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>718338</v>
+        <v>718154</v>
       </c>
       <c r="R62" t="n">
-        <v>7234424</v>
+        <v>7234509</v>
       </c>
       <c r="S62" t="n">
         <v>10</v>
@@ -7013,6 +7008,11 @@
       <c r="AA62" t="inlineStr">
         <is>
           <t>2025-07-02</t>
+        </is>
+      </c>
+      <c r="AC62" t="inlineStr">
+        <is>
+          <t>Färskt ringhack</t>
         </is>
       </c>
       <c r="AD62" t="b">
@@ -7043,10 +7043,10 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>126379459</v>
+        <v>126379432</v>
       </c>
       <c r="B63" t="n">
-        <v>79044</v>
+        <v>57953</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -7054,34 +7054,42 @@
         </is>
       </c>
       <c r="E63" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
+      <c r="K63" t="inlineStr"/>
+      <c r="L63" t="inlineStr"/>
+      <c r="M63" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N63" t="inlineStr"/>
       <c r="P63" t="inlineStr">
         <is>
           <t>Bergmyran, Vb</t>
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>718274</v>
+        <v>718387</v>
       </c>
       <c r="R63" t="n">
-        <v>7234439</v>
+        <v>7234490</v>
       </c>
       <c r="S63" t="n">
         <v>10</v>
@@ -7114,6 +7122,11 @@
       <c r="AA63" t="inlineStr">
         <is>
           <t>2025-07-02</t>
+        </is>
+      </c>
+      <c r="AC63" t="inlineStr">
+        <is>
+          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD63" t="b">
@@ -7144,10 +7157,10 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>126379464</v>
+        <v>126379433</v>
       </c>
       <c r="B64" t="n">
-        <v>79044</v>
+        <v>57953</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -7155,34 +7168,42 @@
         </is>
       </c>
       <c r="E64" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
+      <c r="K64" t="inlineStr"/>
+      <c r="L64" t="inlineStr"/>
+      <c r="M64" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N64" t="inlineStr"/>
       <c r="P64" t="inlineStr">
         <is>
           <t>Bergmyran, Vb</t>
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>718427</v>
+        <v>718308</v>
       </c>
       <c r="R64" t="n">
-        <v>7234679</v>
+        <v>7234486</v>
       </c>
       <c r="S64" t="n">
         <v>10</v>
@@ -7217,6 +7238,11 @@
           <t>2025-07-02</t>
         </is>
       </c>
+      <c r="AC64" t="inlineStr">
+        <is>
+          <t>Äldre ringhack</t>
+        </is>
+      </c>
       <c r="AD64" t="b">
         <v>0</v>
       </c>
@@ -7238,226 +7264,6 @@
         </is>
       </c>
       <c r="AY64" t="inlineStr">
-        <is>
-          <t>Naturskyddsföreningen i Västerbottens naturvärdesinventeringar 2025</t>
-        </is>
-      </c>
-    </row>
-    <row r="65">
-      <c r="A65" t="n">
-        <v>126379462</v>
-      </c>
-      <c r="B65" t="n">
-        <v>79044</v>
-      </c>
-      <c r="D65" t="inlineStr">
-        <is>
-          <t>NT</t>
-        </is>
-      </c>
-      <c r="E65" t="n">
-        <v>6425</v>
-      </c>
-      <c r="F65" t="inlineStr">
-        <is>
-          <t>Garnlav</t>
-        </is>
-      </c>
-      <c r="G65" t="inlineStr">
-        <is>
-          <t>Alectoria sarmentosa</t>
-        </is>
-      </c>
-      <c r="H65" t="inlineStr">
-        <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I65" t="inlineStr"/>
-      <c r="P65" t="inlineStr">
-        <is>
-          <t>Bergmyran, Vb</t>
-        </is>
-      </c>
-      <c r="Q65" t="n">
-        <v>718535</v>
-      </c>
-      <c r="R65" t="n">
-        <v>7234587</v>
-      </c>
-      <c r="S65" t="n">
-        <v>10</v>
-      </c>
-      <c r="T65" t="inlineStr">
-        <is>
-          <t>Västerbotten</t>
-        </is>
-      </c>
-      <c r="U65" t="inlineStr">
-        <is>
-          <t>Skellefteå</t>
-        </is>
-      </c>
-      <c r="V65" t="inlineStr">
-        <is>
-          <t>Västerbotten</t>
-        </is>
-      </c>
-      <c r="W65" t="inlineStr">
-        <is>
-          <t>Jörn</t>
-        </is>
-      </c>
-      <c r="Y65" t="inlineStr">
-        <is>
-          <t>2025-07-02</t>
-        </is>
-      </c>
-      <c r="AA65" t="inlineStr">
-        <is>
-          <t>2025-07-02</t>
-        </is>
-      </c>
-      <c r="AC65" t="inlineStr">
-        <is>
-          <t>Rikligt</t>
-        </is>
-      </c>
-      <c r="AD65" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE65" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG65" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT65" t="inlineStr"/>
-      <c r="AW65" t="inlineStr">
-        <is>
-          <t>Anton Lundberg</t>
-        </is>
-      </c>
-      <c r="AX65" t="inlineStr">
-        <is>
-          <t>Anton Lundberg</t>
-        </is>
-      </c>
-      <c r="AY65" t="inlineStr">
-        <is>
-          <t>Naturskyddsföreningen i Västerbottens naturvärdesinventeringar 2025</t>
-        </is>
-      </c>
-    </row>
-    <row r="66">
-      <c r="A66" t="n">
-        <v>126379438</v>
-      </c>
-      <c r="B66" t="n">
-        <v>57727</v>
-      </c>
-      <c r="D66" t="inlineStr">
-        <is>
-          <t>NT</t>
-        </is>
-      </c>
-      <c r="E66" t="n">
-        <v>100109</v>
-      </c>
-      <c r="F66" t="inlineStr">
-        <is>
-          <t>Tretåig hackspett</t>
-        </is>
-      </c>
-      <c r="G66" t="inlineStr">
-        <is>
-          <t>Picoides tridactylus</t>
-        </is>
-      </c>
-      <c r="H66" t="inlineStr">
-        <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I66" t="inlineStr"/>
-      <c r="K66" t="inlineStr"/>
-      <c r="L66" t="inlineStr"/>
-      <c r="M66" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N66" t="inlineStr"/>
-      <c r="P66" t="inlineStr">
-        <is>
-          <t>Bergmyran, Vb</t>
-        </is>
-      </c>
-      <c r="Q66" t="n">
-        <v>718061</v>
-      </c>
-      <c r="R66" t="n">
-        <v>7234332</v>
-      </c>
-      <c r="S66" t="n">
-        <v>10</v>
-      </c>
-      <c r="T66" t="inlineStr">
-        <is>
-          <t>Västerbotten</t>
-        </is>
-      </c>
-      <c r="U66" t="inlineStr">
-        <is>
-          <t>Skellefteå</t>
-        </is>
-      </c>
-      <c r="V66" t="inlineStr">
-        <is>
-          <t>Västerbotten</t>
-        </is>
-      </c>
-      <c r="W66" t="inlineStr">
-        <is>
-          <t>Jörn</t>
-        </is>
-      </c>
-      <c r="Y66" t="inlineStr">
-        <is>
-          <t>2025-07-01</t>
-        </is>
-      </c>
-      <c r="AA66" t="inlineStr">
-        <is>
-          <t>2025-07-01</t>
-        </is>
-      </c>
-      <c r="AC66" t="inlineStr">
-        <is>
-          <t>Äldre ringhack</t>
-        </is>
-      </c>
-      <c r="AD66" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE66" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG66" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT66" t="inlineStr"/>
-      <c r="AW66" t="inlineStr">
-        <is>
-          <t>Anton Lundberg</t>
-        </is>
-      </c>
-      <c r="AX66" t="inlineStr">
-        <is>
-          <t>Anton Lundberg</t>
-        </is>
-      </c>
-      <c r="AY66" t="inlineStr">
         <is>
           <t>Naturskyddsföreningen i Västerbottens naturvärdesinventeringar 2025</t>
         </is>

--- a/artfynd/A 24579-2025 artfynd.xlsx
+++ b/artfynd/A 24579-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY64"/>
+  <dimension ref="A1:AZ64"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -773,6 +778,11 @@
           <t>Naturskyddsföreningen i Västerbottens naturvärdesinventeringar 2025</t>
         </is>
       </c>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126379423</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -874,6 +884,11 @@
           <t>Naturskyddsföreningen i Västerbottens naturvärdesinventeringar 2025</t>
         </is>
       </c>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126379488</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -975,6 +990,11 @@
           <t>Naturskyddsföreningen i Västerbottens naturvärdesinventeringar 2025</t>
         </is>
       </c>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126379489</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1076,6 +1096,11 @@
           <t>Naturskyddsföreningen i Västerbottens naturvärdesinventeringar 2025</t>
         </is>
       </c>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126379490</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1177,6 +1202,11 @@
           <t>Naturskyddsföreningen i Västerbottens naturvärdesinventeringar 2025</t>
         </is>
       </c>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126379491</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1278,6 +1308,11 @@
           <t>Naturskyddsföreningen i Västerbottens naturvärdesinventeringar 2025</t>
         </is>
       </c>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126379492</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1379,6 +1414,11 @@
           <t>Naturskyddsföreningen i Västerbottens naturvärdesinventeringar 2025</t>
         </is>
       </c>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126379424</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1480,6 +1520,11 @@
           <t>Naturskyddsföreningen i Västerbottens naturvärdesinventeringar 2025</t>
         </is>
       </c>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126379425</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1586,6 +1631,11 @@
           <t>Naturskyddsföreningen i Västerbottens naturvärdesinventeringar 2025</t>
         </is>
       </c>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126379454</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1687,6 +1737,11 @@
           <t>Naturskyddsföreningen i Västerbottens naturvärdesinventeringar 2025</t>
         </is>
       </c>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126379455</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1788,6 +1843,11 @@
           <t>Naturskyddsföreningen i Västerbottens naturvärdesinventeringar 2025</t>
         </is>
       </c>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126379456</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -1889,6 +1949,11 @@
           <t>Naturskyddsföreningen i Västerbottens naturvärdesinventeringar 2025</t>
         </is>
       </c>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126379457</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -1995,6 +2060,11 @@
           <t>Naturskyddsföreningen i Västerbottens naturvärdesinventeringar 2025</t>
         </is>
       </c>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126379458</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2096,6 +2166,11 @@
           <t>Naturskyddsföreningen i Västerbottens naturvärdesinventeringar 2025</t>
         </is>
       </c>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126379459</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2197,6 +2272,11 @@
           <t>Naturskyddsföreningen i Västerbottens naturvärdesinventeringar 2025</t>
         </is>
       </c>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126379460</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -2298,6 +2378,11 @@
           <t>Naturskyddsföreningen i Västerbottens naturvärdesinventeringar 2025</t>
         </is>
       </c>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126379461</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -2404,6 +2489,11 @@
           <t>Naturskyddsföreningen i Västerbottens naturvärdesinventeringar 2025</t>
         </is>
       </c>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126379462</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -2505,6 +2595,11 @@
           <t>Naturskyddsföreningen i Västerbottens naturvärdesinventeringar 2025</t>
         </is>
       </c>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126379463</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -2606,6 +2701,11 @@
           <t>Naturskyddsföreningen i Västerbottens naturvärdesinventeringar 2025</t>
         </is>
       </c>
+      <c r="AZ20" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126379464</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -2712,6 +2812,11 @@
           <t>Naturskyddsföreningen i Västerbottens naturvärdesinventeringar 2025</t>
         </is>
       </c>
+      <c r="AZ21" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126379465</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -2813,6 +2918,11 @@
           <t>Naturskyddsföreningen i Västerbottens naturvärdesinventeringar 2025</t>
         </is>
       </c>
+      <c r="AZ22" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126379466</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -2914,6 +3024,11 @@
           <t>Naturskyddsföreningen i Västerbottens naturvärdesinventeringar 2025</t>
         </is>
       </c>
+      <c r="AZ23" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126379467</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -3015,6 +3130,11 @@
           <t>Naturskyddsföreningen i Västerbottens naturvärdesinventeringar 2025</t>
         </is>
       </c>
+      <c r="AZ24" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126379468</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
@@ -3116,6 +3236,11 @@
           <t>Naturskyddsföreningen i Västerbottens naturvärdesinventeringar 2025</t>
         </is>
       </c>
+      <c r="AZ25" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126379469</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
@@ -3217,6 +3342,11 @@
           <t>Naturskyddsföreningen i Västerbottens naturvärdesinventeringar 2025</t>
         </is>
       </c>
+      <c r="AZ26" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126379470</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
@@ -3323,6 +3453,11 @@
           <t>Naturskyddsföreningen i Västerbottens naturvärdesinventeringar 2025</t>
         </is>
       </c>
+      <c r="AZ27" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126379471</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
@@ -3424,6 +3559,11 @@
           <t>Naturskyddsföreningen i Västerbottens naturvärdesinventeringar 2025</t>
         </is>
       </c>
+      <c r="AZ28" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126379472</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
@@ -3525,6 +3665,11 @@
           <t>Naturskyddsföreningen i Västerbottens naturvärdesinventeringar 2025</t>
         </is>
       </c>
+      <c r="AZ29" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126379473</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
@@ -3626,6 +3771,11 @@
           <t>Naturskyddsföreningen i Västerbottens naturvärdesinventeringar 2025</t>
         </is>
       </c>
+      <c r="AZ30" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126379474</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
@@ -3727,6 +3877,11 @@
           <t>Naturskyddsföreningen i Västerbottens naturvärdesinventeringar 2025</t>
         </is>
       </c>
+      <c r="AZ31" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126379475</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
@@ -3833,6 +3988,11 @@
           <t>Naturskyddsföreningen i Västerbottens naturvärdesinventeringar 2025</t>
         </is>
       </c>
+      <c r="AZ32" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126379476</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
@@ -3939,6 +4099,11 @@
           <t>Naturskyddsföreningen i Västerbottens naturvärdesinventeringar 2025</t>
         </is>
       </c>
+      <c r="AZ33" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126379478</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
@@ -4040,6 +4205,11 @@
           <t>Naturskyddsföreningen i Västerbottens naturvärdesinventeringar 2025</t>
         </is>
       </c>
+      <c r="AZ34" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126379479</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
@@ -4141,6 +4311,11 @@
           <t>Naturskyddsföreningen i Västerbottens naturvärdesinventeringar 2025</t>
         </is>
       </c>
+      <c r="AZ35" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126379480</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
@@ -4242,6 +4417,11 @@
           <t>Naturskyddsföreningen i Västerbottens naturvärdesinventeringar 2025</t>
         </is>
       </c>
+      <c r="AZ36" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126379481</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="n">
@@ -4348,6 +4528,11 @@
           <t>Naturskyddsföreningen i Västerbottens naturvärdesinventeringar 2025</t>
         </is>
       </c>
+      <c r="AZ37" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126379482</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" t="n">
@@ -4454,6 +4639,11 @@
           <t>Naturskyddsföreningen i Västerbottens naturvärdesinventeringar 2025</t>
         </is>
       </c>
+      <c r="AZ38" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126379483</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" t="n">
@@ -4560,6 +4750,11 @@
           <t>Naturskyddsföreningen i Västerbottens naturvärdesinventeringar 2025</t>
         </is>
       </c>
+      <c r="AZ39" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126379484</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" t="n">
@@ -4666,6 +4861,11 @@
           <t>Naturskyddsföreningen i Västerbottens naturvärdesinventeringar 2025</t>
         </is>
       </c>
+      <c r="AZ40" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126379485</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" t="n">
@@ -4767,6 +4967,11 @@
           <t>Naturskyddsföreningen i Västerbottens naturvärdesinventeringar 2025</t>
         </is>
       </c>
+      <c r="AZ41" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126379486</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" t="n">
@@ -4873,6 +5078,11 @@
           <t>Naturskyddsföreningen i Västerbottens naturvärdesinventeringar 2025</t>
         </is>
       </c>
+      <c r="AZ42" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126379487</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" t="n">
@@ -4974,6 +5184,11 @@
           <t>Naturskyddsföreningen i Västerbottens naturvärdesinventeringar 2025</t>
         </is>
       </c>
+      <c r="AZ43" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126379426</t>
+        </is>
+      </c>
     </row>
     <row r="44">
       <c r="A44" t="n">
@@ -5075,6 +5290,11 @@
           <t>Naturskyddsföreningen i Västerbottens naturvärdesinventeringar 2025</t>
         </is>
       </c>
+      <c r="AZ44" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126379427</t>
+        </is>
+      </c>
     </row>
     <row r="45">
       <c r="A45" t="n">
@@ -5176,6 +5396,11 @@
           <t>Naturskyddsföreningen i Västerbottens naturvärdesinventeringar 2025</t>
         </is>
       </c>
+      <c r="AZ45" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126379428</t>
+        </is>
+      </c>
     </row>
     <row r="46">
       <c r="A46" t="n">
@@ -5277,6 +5502,11 @@
           <t>Naturskyddsföreningen i Västerbottens naturvärdesinventeringar 2025</t>
         </is>
       </c>
+      <c r="AZ46" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126379447</t>
+        </is>
+      </c>
     </row>
     <row r="47">
       <c r="A47" t="n">
@@ -5378,6 +5608,11 @@
           <t>Naturskyddsföreningen i Västerbottens naturvärdesinventeringar 2025</t>
         </is>
       </c>
+      <c r="AZ47" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126379446</t>
+        </is>
+      </c>
     </row>
     <row r="48">
       <c r="A48" t="n">
@@ -5479,6 +5714,11 @@
           <t>Naturskyddsföreningen i Västerbottens naturvärdesinventeringar 2025</t>
         </is>
       </c>
+      <c r="AZ48" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126379448</t>
+        </is>
+      </c>
     </row>
     <row r="49">
       <c r="A49" t="n">
@@ -5593,6 +5833,11 @@
           <t>Naturskyddsföreningen i Västerbottens naturvärdesinventeringar 2025</t>
         </is>
       </c>
+      <c r="AZ49" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126379430</t>
+        </is>
+      </c>
     </row>
     <row r="50">
       <c r="A50" t="n">
@@ -5699,6 +5944,11 @@
           <t>Naturskyddsföreningen i Västerbottens naturvärdesinventeringar 2025</t>
         </is>
       </c>
+      <c r="AZ50" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126379431</t>
+        </is>
+      </c>
     </row>
     <row r="51">
       <c r="A51" t="n">
@@ -5813,6 +6063,11 @@
           <t>Naturskyddsföreningen i Västerbottens naturvärdesinventeringar 2025</t>
         </is>
       </c>
+      <c r="AZ51" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126379432</t>
+        </is>
+      </c>
     </row>
     <row r="52">
       <c r="A52" t="n">
@@ -5927,6 +6182,11 @@
           <t>Naturskyddsföreningen i Västerbottens naturvärdesinventeringar 2025</t>
         </is>
       </c>
+      <c r="AZ52" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126379433</t>
+        </is>
+      </c>
     </row>
     <row r="53">
       <c r="A53" t="n">
@@ -6041,6 +6301,11 @@
           <t>Naturskyddsföreningen i Västerbottens naturvärdesinventeringar 2025</t>
         </is>
       </c>
+      <c r="AZ53" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126379434</t>
+        </is>
+      </c>
     </row>
     <row r="54">
       <c r="A54" t="n">
@@ -6155,6 +6420,11 @@
           <t>Naturskyddsföreningen i Västerbottens naturvärdesinventeringar 2025</t>
         </is>
       </c>
+      <c r="AZ54" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126379435</t>
+        </is>
+      </c>
     </row>
     <row r="55">
       <c r="A55" t="n">
@@ -6269,6 +6539,11 @@
           <t>Naturskyddsföreningen i Västerbottens naturvärdesinventeringar 2025</t>
         </is>
       </c>
+      <c r="AZ55" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126379436</t>
+        </is>
+      </c>
     </row>
     <row r="56">
       <c r="A56" t="n">
@@ -6383,6 +6658,11 @@
           <t>Naturskyddsföreningen i Västerbottens naturvärdesinventeringar 2025</t>
         </is>
       </c>
+      <c r="AZ56" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126379437</t>
+        </is>
+      </c>
     </row>
     <row r="57">
       <c r="A57" t="n">
@@ -6497,6 +6777,11 @@
           <t>Naturskyddsföreningen i Västerbottens naturvärdesinventeringar 2025</t>
         </is>
       </c>
+      <c r="AZ57" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126379438</t>
+        </is>
+      </c>
     </row>
     <row r="58">
       <c r="A58" t="n">
@@ -6611,6 +6896,11 @@
           <t>Naturskyddsföreningen i Västerbottens naturvärdesinventeringar 2025</t>
         </is>
       </c>
+      <c r="AZ58" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126379439</t>
+        </is>
+      </c>
     </row>
     <row r="59">
       <c r="A59" t="n">
@@ -6725,6 +7015,11 @@
           <t>Naturskyddsföreningen i Västerbottens naturvärdesinventeringar 2025</t>
         </is>
       </c>
+      <c r="AZ59" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126379440</t>
+        </is>
+      </c>
     </row>
     <row r="60">
       <c r="A60" t="n">
@@ -6839,6 +7134,11 @@
           <t>Naturskyddsföreningen i Västerbottens naturvärdesinventeringar 2025</t>
         </is>
       </c>
+      <c r="AZ60" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126379441</t>
+        </is>
+      </c>
     </row>
     <row r="61">
       <c r="A61" t="n">
@@ -6948,6 +7248,11 @@
           <t>Naturskyddsföreningen i Västerbottens naturvärdesinventeringar 2025</t>
         </is>
       </c>
+      <c r="AZ61" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126379442</t>
+        </is>
+      </c>
     </row>
     <row r="62">
       <c r="A62" t="n">
@@ -7057,6 +7362,11 @@
           <t>Naturskyddsföreningen i Västerbottens naturvärdesinventeringar 2025</t>
         </is>
       </c>
+      <c r="AZ62" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126379443</t>
+        </is>
+      </c>
     </row>
     <row r="63">
       <c r="A63" t="n">
@@ -7156,6 +7466,11 @@
       <c r="AY63" t="inlineStr">
         <is>
           <t>Naturskyddsföreningen i Västerbottens naturvärdesinventeringar 2025</t>
+        </is>
+      </c>
+      <c r="AZ63" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126379444</t>
         </is>
       </c>
     </row>
@@ -7268,8 +7583,78 @@
           <t>Naturskyddsföreningen i Västerbottens naturvärdesinventeringar 2025</t>
         </is>
       </c>
+      <c r="AZ64" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126379451</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ21" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ22" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ23" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ24" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ25" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ26" r:id="rId25"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ27" r:id="rId26"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ28" r:id="rId27"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ29" r:id="rId28"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ30" r:id="rId29"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ31" r:id="rId30"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ32" r:id="rId31"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ33" r:id="rId32"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ34" r:id="rId33"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ35" r:id="rId34"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ36" r:id="rId35"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ37" r:id="rId36"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ38" r:id="rId37"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ39" r:id="rId38"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ40" r:id="rId39"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ41" r:id="rId40"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ42" r:id="rId41"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ43" r:id="rId42"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ44" r:id="rId43"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ45" r:id="rId44"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ46" r:id="rId45"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ47" r:id="rId46"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ48" r:id="rId47"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ49" r:id="rId48"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ50" r:id="rId49"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ51" r:id="rId50"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ52" r:id="rId51"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ53" r:id="rId52"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ54" r:id="rId53"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ55" r:id="rId54"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ56" r:id="rId55"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ57" r:id="rId56"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ58" r:id="rId57"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ59" r:id="rId58"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ60" r:id="rId59"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ61" r:id="rId60"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ62" r:id="rId61"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ63" r:id="rId62"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ64" r:id="rId63"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>